--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -3645,7 +3645,7 @@
     <t>1.2</t>
   </si>
   <si>
-    <t>En permettant la durée de vie des équipements, même au-delà de leur amortissement comptable et en valorisant les gains et le ROI pour chacune des parties prenantes</t>
+    <t>En allongeant la durée d’usage des équipements, même au-delà de leur amortissement comptable</t>
   </si>
   <si>
     <t>1.3</t>

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -3651,7 +3651,7 @@
     <t>1.3</t>
   </si>
   <si>
-    <t>En permettant de concevoir de manière responsable les services numériques et en intégrant des technologies ou des dispositifs proactifs vis-à-vis des ODD.</t>
+    <t>En éco-concevant les services numériques, et en choisissant des technologies qui contribuent aux Objectifs de développement durable (ODD)</t>
   </si>
   <si>
     <t>1.4</t>

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -3690,7 +3690,7 @@
     <t>2.2</t>
   </si>
   <si>
-    <t>En permettant des applications accessibles à tous - en mesurant le niveau de conformité RGAA et en accompagnant les entreprises du territoire à se conformer à la règlementation</t>
+    <t>En rendant nos services numériques accessibles à toutes et tous, et en mesurant leur conformité au RGAA</t>
   </si>
   <si>
     <t>2.3</t>

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -3702,7 +3702,7 @@
     <t>2.4</t>
   </si>
   <si>
-    <t>En associant l’utilisateur à la conception pour éviter des outils surdimensionnés et améliorer progressivement le niveau de conformité des services en ligne.</t>
+    <t>En concevant les services avec celles et ceux qui les utiliseront, pour livrer ce dont ils ont besoin et rien de plus</t>
   </si>
   <si>
     <t xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </t>

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -9457,7 +9457,7 @@
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Résultats synthèse de la priorisation des cibles des ODD</a:t>
+              <a:t>Résultats synthèse de la priorisation des cibles des ONR : Ensemble des 28 cibles</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -9786,6 +9786,2901 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C002D58}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="48678400"/>
+        <c:axId val="48684416"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48678400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48684416"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48684416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-CA" sz="1800">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Nombre de cibles</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48678400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CA" sz="1600">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>ONR 1 : Sobriété</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000258}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000258}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000258}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000258}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000258}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000258}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000258}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000258}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$G$1:$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Urgentes</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>À moyen terme</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>À long terme</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>À consolider</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Non prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Non pertinentes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Résultats synthèse'!$G$4:$M$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000258}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="48678400"/>
+        <c:axId val="48684416"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48678400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48684416"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48684416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-CA" sz="1800">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Nombre de cibles</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48678400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CA" sz="1600">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>ONR 2 : Inclusion</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000358}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000358}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000358}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000358}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000358}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000358}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000358}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000358}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$G$1:$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Urgentes</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>À moyen terme</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>À long terme</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>À consolider</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Non prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Non pertinentes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Résultats synthèse'!$G$5:$M$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000358}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="48678400"/>
+        <c:axId val="48684416"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48678400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48684416"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48684416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-CA" sz="1800">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Nombre de cibles</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48678400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CA" sz="1600">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>ONR 3 : RSE</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000458}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000458}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000458}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000458}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000458}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000458}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000458}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000458}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$G$1:$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Urgentes</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>À moyen terme</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>À long terme</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>À consolider</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Non prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Non pertinentes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Résultats synthèse'!$G$6:$M$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000458}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="48678400"/>
+        <c:axId val="48684416"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48678400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48684416"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48684416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-CA" sz="1800">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Nombre de cibles</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48678400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CA" sz="1600">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>ONR 4 : Résilience et stratégie</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000558}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000558}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000558}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000558}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000558}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000558}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000558}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000558}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$G$1:$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Urgentes</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>À moyen terme</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>À long terme</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>À consolider</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Non prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Non pertinentes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Résultats synthèse'!$G$7:$M$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000558}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="48678400"/>
+        <c:axId val="48684416"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48678400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48684416"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48684416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-CA" sz="1800">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Nombre de cibles</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48678400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CA" sz="1600">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>ONR 5 : Management</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000658}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000658}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000658}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000658}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000658}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000658}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000658}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000658}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$G$1:$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Urgentes</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>À moyen terme</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>À long terme</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>À consolider</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Non prioritaires</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Non pertinentes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Résultats synthèse'!$G$8:$M$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000658}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13746,6 +16641,166 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Graphique 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Graphique 5"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Graphique 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -10001,18 +10001,10 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -10021,21 +10013,15 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="fr-CA" sz="1600">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="fr-FR" sz="1400"/>
               <a:t>ONR 1 : Sobriété</a:t>
             </a:r>
           </a:p>
@@ -10047,206 +10033,124 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ONR 1 : Sobriété</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:dPt>
             <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000258}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000258}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000258}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000258}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="92D050"/>
+                <a:srgbClr val="70AD47"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000258}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:srgbClr val="BFBFBF"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000258}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="404040"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000258}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000258}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -10254,54 +10158,24 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr sz="1000" b="1"/>
                 </a:pPr>
                 <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -10362,236 +10236,56 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000258}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="48678400"/>
-        <c:axId val="48684416"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="48678400"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48684416"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48684416"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="fr-CA" sz="1800">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Nombre de cibles</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48678400"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -10600,21 +10294,15 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="fr-CA" sz="1600">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="fr-FR" sz="1400"/>
               <a:t>ONR 2 : Inclusion</a:t>
             </a:r>
           </a:p>
@@ -10626,206 +10314,124 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ONR 2 : Inclusion</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:dPt>
             <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000358}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000358}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000358}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000358}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="92D050"/>
+                <a:srgbClr val="70AD47"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000358}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:srgbClr val="BFBFBF"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000358}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="404040"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000358}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000358}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -10833,54 +10439,24 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr sz="1000" b="1"/>
                 </a:pPr>
                 <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -10941,236 +10517,56 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000358}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="48678400"/>
-        <c:axId val="48684416"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="48678400"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48684416"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48684416"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="fr-CA" sz="1800">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Nombre de cibles</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48678400"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -11179,21 +10575,15 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="fr-CA" sz="1600">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="fr-FR" sz="1400"/>
               <a:t>ONR 3 : RSE</a:t>
             </a:r>
           </a:p>
@@ -11205,206 +10595,124 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ONR 3 : RSE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:dPt>
             <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000458}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000458}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000458}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000458}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="92D050"/>
+                <a:srgbClr val="70AD47"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000458}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:srgbClr val="BFBFBF"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000458}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="404040"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000458}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000458}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -11412,54 +10720,24 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr sz="1000" b="1"/>
                 </a:pPr>
                 <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -11520,236 +10798,56 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000458}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="48678400"/>
-        <c:axId val="48684416"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="48678400"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48684416"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48684416"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="fr-CA" sz="1800">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Nombre de cibles</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48678400"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -11758,21 +10856,15 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="fr-CA" sz="1600">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="fr-FR" sz="1400"/>
               <a:t>ONR 4 : Résilience et stratégie</a:t>
             </a:r>
           </a:p>
@@ -11784,206 +10876,124 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ONR 4 : Résilience et stratégie</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:dPt>
             <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000558}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000558}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000558}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000558}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="92D050"/>
+                <a:srgbClr val="70AD47"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000558}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:srgbClr val="BFBFBF"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000558}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="404040"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000558}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000558}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -11991,54 +11001,24 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr sz="1000" b="1"/>
                 </a:pPr>
                 <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -12099,236 +11079,56 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000558}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="48678400"/>
-        <c:axId val="48684416"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="48678400"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48684416"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48684416"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="fr-CA" sz="1800">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Nombre de cibles</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48678400"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -12337,21 +11137,15 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="fr-CA" sz="1600">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="fr-FR" sz="1400"/>
               <a:t>ONR 5 : Management</a:t>
             </a:r>
           </a:p>
@@ -12363,206 +11157,124 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Résultats synthèse'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ONR 5 : Management</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:dPt>
             <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5519-41AC-BC43-67BE7C000658}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5519-41AC-BC43-67BE7C000658}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5519-41AC-BC43-67BE7C000658}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5519-41AC-BC43-67BE7C000658}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="92D050"/>
+                <a:srgbClr val="70AD47"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-5519-41AC-BC43-67BE7C000658}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:srgbClr val="BFBFBF"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-5519-41AC-BC43-67BE7C000658}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="404040"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-5519-41AC-BC43-67BE7C000658}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-5519-41AC-BC43-67BE7C000658}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -12570,54 +11282,24 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr sz="1000" b="1"/>
                 </a:pPr>
                 <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -12678,220 +11360,48 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-5519-41AC-BC43-67BE7C000658}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="48678400"/>
-        <c:axId val="48684416"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="48678400"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48684416"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48684416"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="fr-CA" sz="1800">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Nombre de cibles</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48678400"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -17350,11 +15860,11 @@
         <v xml:space="preserve">ONR 1  -   SOBRIÉTÉ : S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation					</v>
       </c>
       <c r="AC4" s="116">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD4" s="116">
         <f>AC4-AE4</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="117">
         <f t="shared" ref="AE4:AL4" si="0">SUM(AE5:AE11)</f>
@@ -19996,11 +18506,11 @@
         <v>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
       </c>
       <c r="AC25" s="116">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD25" s="116">
         <f>AC25-AE25</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE25" s="117">
         <f t="shared" ref="AE25:AL25" si="78">SUM(AE26:AE29)</f>
@@ -20610,11 +19120,11 @@
         <v>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
       </c>
       <c r="AC30" s="116">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD30" s="116">
         <f>AC30-AE30</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="117">
         <f>SUM(AE31:AE36)</f>
@@ -21987,7 +20497,7 @@
       <c r="C3" s="389"/>
       <c r="D3" s="45">
         <f t="shared" ref="D3:M3" si="0">SUM(D4:D8)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="65">
         <f t="shared" si="0"/>
@@ -22034,11 +20544,11 @@
       </c>
       <c r="D4" s="44">
         <f>IF('Résultats détaillés'!AC4=0,"",'Résultats détaillés'!AC4)</f>
-        <v>6</v>
-      </c>
-      <c r="E4" s="66">
+        <v>7</v>
+      </c>
+      <c r="E4" s="66" t="str">
         <f>IF('Résultats détaillés'!AD4=0,"",'Résultats détaillés'!AD4)</f>
-        <v>-1</v>
+        <v/>
       </c>
       <c r="F4" s="64">
         <f>IF('Résultats détaillés'!AE4=0,"",'Résultats détaillés'!AE4)</f>
@@ -22175,11 +20685,11 @@
       </c>
       <c r="D7" s="44">
         <f>IF('Résultats détaillés'!AC25=0,"",'Résultats détaillés'!AC25)</f>
-        <v>3</v>
-      </c>
-      <c r="E7" s="66">
+        <v>4</v>
+      </c>
+      <c r="E7" s="66" t="str">
         <f>IF('Résultats détaillés'!AD25=0,"",'Résultats détaillés'!AD25)</f>
-        <v>-1</v>
+        <v/>
       </c>
       <c r="F7" s="64">
         <f>IF('Résultats détaillés'!AE25=0,"",'Résultats détaillés'!AE25)</f>
@@ -22222,11 +20732,11 @@
       </c>
       <c r="D8" s="44">
         <f>IF('Résultats détaillés'!AC30=0,"",'Résultats détaillés'!AC30)</f>
-        <v>7</v>
-      </c>
-      <c r="E8" s="66">
+        <v>6</v>
+      </c>
+      <c r="E8" s="66" t="str">
         <f>IF('Résultats détaillés'!AD30=0,"",'Résultats détaillés'!AD30)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F8" s="44">
         <f>IF('Résultats détaillés'!AE30=0,"",'Résultats détaillés'!AE30)</f>

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -15860,6 +15860,7 @@
         <v xml:space="preserve">ONR 1  -   SOBRIÉTÉ : S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation					</v>
       </c>
       <c r="AC4" s="116">
+        <f>SUMPRODUCT(--(B5:B11&lt;&gt;""))</f>
         <v>7</v>
       </c>
       <c r="AD4" s="116">
@@ -16879,6 +16880,7 @@
         <v>ONR 2  -   INCLUSION : S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
       </c>
       <c r="AC12" s="116">
+        <f>SUMPRODUCT(--(B13:B16&lt;&gt;""))</f>
         <v>4</v>
       </c>
       <c r="AD12" s="116">
@@ -17493,6 +17495,7 @@
         <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
       </c>
       <c r="AC17" s="116">
+        <f>SUMPRODUCT(--(B18:B24&lt;&gt;""))</f>
         <v>7</v>
       </c>
       <c r="AD17" s="116">
@@ -18506,6 +18509,7 @@
         <v>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
       </c>
       <c r="AC25" s="116">
+        <f>SUMPRODUCT(--(B26:B29&lt;&gt;""))</f>
         <v>4</v>
       </c>
       <c r="AD25" s="116">
@@ -19120,6 +19124,7 @@
         <v>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
       </c>
       <c r="AC30" s="116">
+        <f>SUMPRODUCT(--(B31:B36&lt;&gt;""))</f>
         <v>6</v>
       </c>
       <c r="AD30" s="116">

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -9457,7 +9457,7 @@
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Résultats synthèse de la priorisation des cibles des ONR : Ensemble des 28 cibles</a:t>
+              <a:t>Résultats synthèse de la priorisation des cibles des ONR : Ensemble des 32 cibles</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -15630,7 +15630,7 @@
   <sheetPr codeName="Feuil10">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL36"/>
+  <dimension ref="A1:AL40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="1.5" style="57" customWidth="1"/>
@@ -15860,7 +15860,7 @@
         <v xml:space="preserve">ONR 1  -   SOBRIÉTÉ : S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation					</v>
       </c>
       <c r="AC4" s="116">
-        <f>SUMPRODUCT(--(B5:B11&lt;&gt;""))</f>
+        <f>SUMPRODUCT(--(B5:B12&lt;&gt;""))</f>
         <v>7</v>
       </c>
       <c r="AD4" s="116">
@@ -15868,35 +15868,35 @@
         <v>0</v>
       </c>
       <c r="AE4" s="117">
-        <f t="shared" ref="AE4:AL4" si="0">SUM(AE5:AE11)</f>
+        <f>SUM(AE5:AE12)</f>
         <v>7</v>
       </c>
       <c r="AF4" s="117">
-        <f t="shared" si="0"/>
+        <f>SUM(AF5:AF12)</f>
         <v>0</v>
       </c>
       <c r="AG4" s="117">
-        <f t="shared" si="0"/>
+        <f>SUM(AG5:AG12)</f>
         <v>0</v>
       </c>
       <c r="AH4" s="117">
-        <f t="shared" si="0"/>
+        <f>SUM(AH5:AH12)</f>
         <v>0</v>
       </c>
       <c r="AI4" s="117">
-        <f t="shared" si="0"/>
+        <f>SUM(AI5:AI12)</f>
         <v>0</v>
       </c>
       <c r="AJ4" s="117">
-        <f t="shared" si="0"/>
+        <f>SUM(AJ5:AJ12)</f>
         <v>0</v>
       </c>
       <c r="AK4" s="117">
-        <f t="shared" si="0"/>
+        <f>SUM(AK5:AK12)</f>
         <v>0</v>
       </c>
       <c r="AL4" s="117">
-        <f t="shared" si="0"/>
+        <f>SUM(AL5:AL12)</f>
         <v>0</v>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="229">
-        <f t="shared" ref="V5:V11" si="5">G5</f>
+        <f t="shared" ref="V5:V12" si="5">G5</f>
         <v>0</v>
       </c>
       <c r="W5" s="203">
@@ -15995,19 +15995,19 @@
         <v>0</v>
       </c>
       <c r="Y5" s="230">
-        <f t="shared" ref="Y5:Y11" si="6">I5</f>
+        <f t="shared" ref="Y5:Y12" si="6">I5</f>
         <v>0</v>
       </c>
       <c r="Z5" s="230">
-        <f t="shared" ref="Z5:Z11" si="7">D5</f>
+        <f t="shared" ref="Z5:Z12" si="7">D5</f>
         <v>0</v>
       </c>
       <c r="AE5" s="206">
-        <f t="shared" ref="AE5:AE11" si="8">IF(K5=0,1,0)</f>
+        <f t="shared" ref="AE5:AE12" si="8">IF(K5=0,1,0)</f>
         <v>1</v>
       </c>
       <c r="AF5" s="206">
-        <f t="shared" ref="AF5:AL11" si="9">IF(L5=TRUE,1,0)</f>
+        <f t="shared" ref="AF5:AL12" si="9">IF(L5=TRUE,1,0)</f>
         <v>0</v>
       </c>
       <c r="AG5" s="206">
@@ -16610,51 +16610,51 @@
         <v>0</v>
       </c>
       <c r="J10" s="232">
-        <f t="shared" ref="J10:J11" si="18">S10</f>
+        <f t="shared" ref="J10:J12" si="18">S10</f>
         <v>0</v>
       </c>
       <c r="K10" s="233">
-        <f t="shared" ref="K10:K11" si="19">E10*10+F10</f>
+        <f t="shared" ref="K10:K12" si="19">E10*10+F10</f>
         <v>0</v>
       </c>
       <c r="L10" s="233" t="b">
-        <f t="shared" ref="L10:L11" si="20">OR(K10=31)</f>
+        <f t="shared" ref="L10:L12" si="20">OR(K10=31)</f>
         <v>0</v>
       </c>
       <c r="M10" s="233" t="b">
-        <f t="shared" ref="M10:M11" si="21">OR(K10=21,K10=32)</f>
+        <f t="shared" ref="M10:M12" si="21">OR(K10=21,K10=32)</f>
         <v>0</v>
       </c>
       <c r="N10" s="233" t="b">
-        <f t="shared" ref="N10:N11" si="22">OR(K10=22,K10=33)</f>
+        <f t="shared" ref="N10:N12" si="22">OR(K10=22,K10=33)</f>
         <v>0</v>
       </c>
       <c r="O10" s="233" t="b">
-        <f t="shared" ref="O10:O11" si="23">OR(K10=11,K10=12)</f>
+        <f t="shared" ref="O10:O12" si="23">OR(K10=11,K10=12)</f>
         <v>0</v>
       </c>
       <c r="P10" s="233" t="b">
-        <f t="shared" ref="P10:P11" si="24">OR(K10=23,K10=34)</f>
+        <f t="shared" ref="P10:P12" si="24">OR(K10=23,K10=34)</f>
         <v>0</v>
       </c>
       <c r="Q10" s="233" t="b">
-        <f t="shared" ref="Q10:Q11" si="25">OR(K10=13,K10=14,K10=24)</f>
+        <f t="shared" ref="Q10:Q12" si="25">OR(K10=13,K10=14,K10=24)</f>
         <v>0</v>
       </c>
       <c r="R10" s="233" t="b">
-        <f t="shared" ref="R10:R11" si="26">OR(K10=1,K10=2,K10=3,K10=4)</f>
+        <f t="shared" ref="R10:R12" si="26">OR(K10=1,K10=2,K10=3,K10=4)</f>
         <v>0</v>
       </c>
       <c r="S10" s="234">
-        <f t="shared" ref="S10:S11" si="27">IF(COUNTA(E10:F10)&lt;2,"",(IF(L10=TRUE,$L$3,IF(M10=TRUE,$M$3,IF(N10=TRUE,$N$3,IF(O10=TRUE,$O$3,IF(P10=TRUE,$P$3,IF(Q10=TRUE,$Q$3,IF(R10=TRUE,$R$3,0)))))))))</f>
+        <f t="shared" ref="S10:S12" si="27">IF(COUNTA(E10:F10)&lt;2,"",(IF(L10=TRUE,$L$3,IF(M10=TRUE,$M$3,IF(N10=TRUE,$N$3,IF(O10=TRUE,$O$3,IF(P10=TRUE,$P$3,IF(Q10=TRUE,$Q$3,IF(R10=TRUE,$R$3,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="T10" s="232">
-        <f t="shared" ref="T10:T11" si="28">IF(COUNTA(E10:F10)&lt;2,"",(IF(L10=TRUE,6,IF(M10=TRUE,5,IF(N10=TRUE,4,IF(O10=TRUE,3,IF(P10=TRUE,2,IF(Q10=TRUE,1,IF(R10=TRUE,0,0)))))))))</f>
+        <f t="shared" ref="T10:T12" si="28">IF(COUNTA(E10:F10)&lt;2,"",(IF(L10=TRUE,6,IF(M10=TRUE,5,IF(N10=TRUE,4,IF(O10=TRUE,3,IF(P10=TRUE,2,IF(Q10=TRUE,1,IF(R10=TRUE,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="U10" s="233">
-        <f t="shared" ref="U10:U11" si="29">T10*10+H10</f>
+        <f t="shared" ref="U10:U12" si="29">T10*10+H10</f>
         <v>0</v>
       </c>
       <c r="V10" s="241">
@@ -16845,296 +16845,296 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" s="116" customFormat="1" ht="23" thickBot="1">
-      <c r="A12" s="115"/>
-      <c r="B12" s="362" t="str">
+    <row r="12" spans="1:38" s="205" customFormat="1" ht="39" thickBot="1">
+      <c r="A12" s="199"/>
+      <c r="B12" s="219" t="str">
+        <f>'ONR 1'!B14</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="219" t="str">
+        <f>'ONR 1'!C14</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="240">
+        <f>'ONR 1'!D14</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="270">
+        <f>'ONR 1'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="277">
+        <f>'ONR 1'!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="211">
+        <f>'ONR 1'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="212">
+        <f>'ONR 1'!H14</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="225">
+        <f>'ONR 1'!I14</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="232">
+        <f>S12</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="233">
+        <f>E12*10+F12</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="233" t="b">
+        <f>OR(K12=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="233" t="b">
+        <f>OR(K12=21,K12=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="233" t="b">
+        <f>OR(K12=22,K12=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="233" t="b">
+        <f>OR(K12=11,K12=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="233" t="b">
+        <f>OR(K12=23,K12=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="233" t="b">
+        <f>OR(K12=13,K12=14,K12=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="233" t="b">
+        <f>OR(K12=1,K12=2,K12=3,K12=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="234">
+        <f>IF(COUNTA(E12:F12)&lt;2,"",(IF(L12=TRUE,$L$3,IF(M12=TRUE,$M$3,IF(N12=TRUE,$N$3,IF(O12=TRUE,$O$3,IF(P12=TRUE,$P$3,IF(Q12=TRUE,$Q$3,IF(R12=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="232">
+        <f>IF(COUNTA(E12:F12)&lt;2,"",(IF(L12=TRUE,6,IF(M12=TRUE,5,IF(N12=TRUE,4,IF(O12=TRUE,3,IF(P12=TRUE,2,IF(Q12=TRUE,1,IF(R12=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="233">
+        <f>T12*10+H12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="241">
+        <f>G12</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="241">
+        <f>'ONR 1'!V14</f>
+        <v>0</v>
+      </c>
+      <c r="X12" s="204">
+        <f>'ONR 1'!W14</f>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="236">
+        <f>I12</f>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="236">
+        <f>D12</f>
+        <v>0</v>
+      </c>
+      <c r="AE12" s="206">
+        <f>IF(K12=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="206">
+        <f>IF(L12=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG12" s="206">
+        <f>IF(L12=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH12" s="206">
+        <f>IF(L12=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="206">
+        <f>IF(L12=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="206">
+        <f>IF(L12=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK12" s="206">
+        <f>IF(L12=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL12" s="206">
+        <f>IF(L12=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" s="116" customFormat="1" ht="23" thickBot="1">
+      <c r="A13" s="115"/>
+      <c r="B13" s="362" t="str">
         <f>'ONR 2'!B2</f>
         <v>ONR 2  -   INCLUSION : S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
       </c>
-      <c r="C12" s="363"/>
-      <c r="D12" s="363"/>
-      <c r="E12" s="363"/>
-      <c r="F12" s="363"/>
-      <c r="G12" s="363"/>
-      <c r="H12" s="363"/>
-      <c r="I12" s="363"/>
-      <c r="J12" s="363"/>
-      <c r="K12" s="363"/>
-      <c r="L12" s="363"/>
-      <c r="M12" s="363"/>
-      <c r="N12" s="363"/>
-      <c r="O12" s="363"/>
-      <c r="P12" s="363"/>
-      <c r="Q12" s="363"/>
-      <c r="R12" s="363"/>
-      <c r="S12" s="363"/>
-      <c r="T12" s="363"/>
-      <c r="U12" s="363"/>
-      <c r="V12" s="363"/>
-      <c r="W12" s="363"/>
-      <c r="X12" s="363"/>
-      <c r="Y12" s="363"/>
-      <c r="Z12" s="380"/>
-      <c r="AB12" s="116" t="str">
-        <f>B12</f>
+      <c r="C13" s="363"/>
+      <c r="D13" s="363"/>
+      <c r="E13" s="363"/>
+      <c r="F13" s="363"/>
+      <c r="G13" s="363"/>
+      <c r="H13" s="363"/>
+      <c r="I13" s="363"/>
+      <c r="J13" s="363"/>
+      <c r="K13" s="363"/>
+      <c r="L13" s="363"/>
+      <c r="M13" s="363"/>
+      <c r="N13" s="363"/>
+      <c r="O13" s="363"/>
+      <c r="P13" s="363"/>
+      <c r="Q13" s="363"/>
+      <c r="R13" s="363"/>
+      <c r="S13" s="363"/>
+      <c r="T13" s="363"/>
+      <c r="U13" s="363"/>
+      <c r="V13" s="363"/>
+      <c r="W13" s="363"/>
+      <c r="X13" s="363"/>
+      <c r="Y13" s="363"/>
+      <c r="Z13" s="380"/>
+      <c r="AB13" s="116" t="str">
+        <f>B13</f>
         <v>ONR 2  -   INCLUSION : S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
       </c>
-      <c r="AC12" s="116">
-        <f>SUMPRODUCT(--(B13:B16&lt;&gt;""))</f>
+      <c r="AC13" s="116">
+        <f>SUMPRODUCT(--(B14:B18&lt;&gt;""))</f>
         <v>4</v>
       </c>
-      <c r="AD12" s="116">
-        <f>AC12-AE12</f>
-        <v>0</v>
-      </c>
-      <c r="AE12" s="117">
-        <f t="shared" ref="AE12:AL12" si="30">SUM(AE13:AE16)</f>
+      <c r="AD13" s="116">
+        <f>AC13-AE13</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="117">
+        <f>SUM(AE14:AE18)</f>
         <v>4</v>
       </c>
-      <c r="AF12" s="117">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AG12" s="117">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AH12" s="117">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AI12" s="117">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="117">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AK12" s="117">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AL12" s="117">
-        <f t="shared" si="30"/>
+      <c r="AF13" s="117">
+        <f>SUM(AF14:AF18)</f>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="117">
+        <f>SUM(AG14:AG18)</f>
+        <v>0</v>
+      </c>
+      <c r="AH13" s="117">
+        <f>SUM(AH14:AH18)</f>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="117">
+        <f>SUM(AI14:AI18)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="117">
+        <f>SUM(AJ14:AJ18)</f>
+        <v>0</v>
+      </c>
+      <c r="AK13" s="117">
+        <f>SUM(AK14:AK18)</f>
+        <v>0</v>
+      </c>
+      <c r="AL13" s="117">
+        <f>SUM(AL14:AL18)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" s="205" customFormat="1" ht="38">
-      <c r="A13" s="199"/>
-      <c r="B13" s="218" t="str">
+    <row r="14" spans="1:38" s="205" customFormat="1" ht="38">
+      <c r="A14" s="199"/>
+      <c r="B14" s="218" t="str">
         <f>'ONR 2'!B7</f>
         <v>2.1</v>
       </c>
-      <c r="C13" s="221" t="str">
+      <c r="C14" s="221" t="str">
         <f>'ONR 2'!C7</f>
         <v>En généralisant une démarche d’achats responsables avec l’adoption de clauses sociétales et environnementales.</v>
       </c>
-      <c r="D13" s="223">
+      <c r="D14" s="223">
         <f>'ONR 2'!D7</f>
         <v>0</v>
       </c>
-      <c r="E13" s="267">
+      <c r="E14" s="267">
         <f>'ONR 2'!E7</f>
         <v>0</v>
       </c>
-      <c r="F13" s="274">
+      <c r="F14" s="274">
         <f>'ONR 2'!F7</f>
         <v>0</v>
       </c>
-      <c r="G13" s="200">
+      <c r="G14" s="200">
         <f>'ONR 2'!G7</f>
         <v>0</v>
       </c>
-      <c r="H13" s="202">
+      <c r="H14" s="202">
         <f>'ONR 2'!H7</f>
         <v>0</v>
       </c>
-      <c r="I13" s="225">
+      <c r="I14" s="225">
         <f>'ONR 2'!I7</f>
         <v>0</v>
       </c>
-      <c r="J13" s="218">
-        <f>S13</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="227">
-        <f t="shared" ref="K13" si="31">E13*10+F13</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="227" t="b">
-        <f>OR(K13=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="227" t="b">
-        <f>OR(K13=21,K13=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="227" t="b">
-        <f>OR(K13=22,K13=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="227" t="b">
-        <f>OR(K13=11,K13=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P13" s="227" t="b">
-        <f>OR(K13=23,K13=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="227" t="b">
-        <f>OR(K13=13,K13=14,K13=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="227" t="b">
-        <f>OR(K13=1,K13=2,K13=3,K13=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S13" s="228">
-        <f t="shared" ref="S13" si="32">IF(COUNTA(E13:F13)&lt;2,"",(IF(L13=TRUE,$L$3,IF(M13=TRUE,$M$3,IF(N13=TRUE,$N$3,IF(O13=TRUE,$O$3,IF(P13=TRUE,$P$3,IF(Q13=TRUE,$Q$3,IF(R13=TRUE,$R$3,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="T13" s="226">
-        <f t="shared" ref="T13" si="33">IF(COUNTA(E13:F13)&lt;2,"",(IF(L13=TRUE,6,IF(M13=TRUE,5,IF(N13=TRUE,4,IF(O13=TRUE,3,IF(P13=TRUE,2,IF(Q13=TRUE,1,IF(R13=TRUE,0,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="U13" s="242">
-        <f t="shared" ref="U13" si="34">T13*10+H13</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="229">
-        <f>G13</f>
-        <v>0</v>
-      </c>
-      <c r="W13" s="229">
-        <f>'ONR 2'!V7</f>
-        <v>0</v>
-      </c>
-      <c r="X13" s="204">
-        <f>'ONR 2'!W7</f>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="230">
-        <f>I13</f>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="230">
-        <f>D13</f>
-        <v>0</v>
-      </c>
-      <c r="AE13" s="206">
-        <f>IF(K13=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF13" s="206">
-        <f t="shared" ref="AF13:AL16" si="35">IF(L13=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG13" s="206">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AH13" s="206">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AI13" s="206">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="206">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AK13" s="206">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL13" s="206">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:38" s="205" customFormat="1" ht="57">
-      <c r="A14" s="199"/>
-      <c r="B14" s="218" t="str">
-        <f>'ONR 2'!B8</f>
-        <v>2.2</v>
-      </c>
-      <c r="C14" s="221" t="str">
-        <f>'ONR 2'!C8</f>
-        <v>En permettant des applications accessibles à tous - en mesurant le niveau de conformité RGAA et en accompagnat les entreprises du territoire à se conformer à la règlementation</v>
-      </c>
-      <c r="D14" s="223">
-        <f>'ONR 2'!D8</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="267">
-        <f>'ONR 2'!E8</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="274">
-        <f>'ONR 2'!F8</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="200">
-        <f>'ONR 2'!G8</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="202">
-        <f>'ONR 2'!H8</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="225">
-        <f>'ONR 2'!I8</f>
-        <v>0</v>
-      </c>
       <c r="J14" s="218">
-        <f t="shared" ref="J14:J16" si="36">S14</f>
+        <f>S14</f>
         <v>0</v>
       </c>
       <c r="K14" s="227">
-        <f t="shared" ref="K14:K16" si="37">E14*10+F14</f>
+        <f t="shared" ref="K14" si="31">E14*10+F14</f>
         <v>0</v>
       </c>
       <c r="L14" s="227" t="b">
-        <f t="shared" ref="L14:L16" si="38">OR(K14=31)</f>
+        <f>OR(K14=31)</f>
         <v>0</v>
       </c>
       <c r="M14" s="227" t="b">
-        <f t="shared" ref="M14:M16" si="39">OR(K14=21,K14=32)</f>
+        <f>OR(K14=21,K14=32)</f>
         <v>0</v>
       </c>
       <c r="N14" s="227" t="b">
-        <f t="shared" ref="N14:N16" si="40">OR(K14=22,K14=33)</f>
+        <f>OR(K14=22,K14=33)</f>
         <v>0</v>
       </c>
       <c r="O14" s="227" t="b">
-        <f t="shared" ref="O14:O16" si="41">OR(K14=11,K14=12)</f>
+        <f>OR(K14=11,K14=12)</f>
         <v>0</v>
       </c>
       <c r="P14" s="227" t="b">
-        <f t="shared" ref="P14:P16" si="42">OR(K14=23,K14=34)</f>
+        <f>OR(K14=23,K14=34)</f>
         <v>0</v>
       </c>
       <c r="Q14" s="227" t="b">
-        <f t="shared" ref="Q14:Q16" si="43">OR(K14=13,K14=14,K14=24)</f>
+        <f>OR(K14=13,K14=14,K14=24)</f>
         <v>0</v>
       </c>
       <c r="R14" s="227" t="b">
-        <f t="shared" ref="R14:R16" si="44">OR(K14=1,K14=2,K14=3,K14=4)</f>
+        <f>OR(K14=1,K14=2,K14=3,K14=4)</f>
         <v>0</v>
       </c>
       <c r="S14" s="228">
-        <f t="shared" ref="S14:S16" si="45">IF(COUNTA(E14:F14)&lt;2,"",(IF(L14=TRUE,$L$3,IF(M14=TRUE,$M$3,IF(N14=TRUE,$N$3,IF(O14=TRUE,$O$3,IF(P14=TRUE,$P$3,IF(Q14=TRUE,$Q$3,IF(R14=TRUE,$R$3,0)))))))))</f>
+        <f t="shared" ref="S14" si="32">IF(COUNTA(E14:F14)&lt;2,"",(IF(L14=TRUE,$L$3,IF(M14=TRUE,$M$3,IF(N14=TRUE,$N$3,IF(O14=TRUE,$O$3,IF(P14=TRUE,$P$3,IF(Q14=TRUE,$Q$3,IF(R14=TRUE,$R$3,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="T14" s="226">
-        <f t="shared" ref="T14:T16" si="46">IF(COUNTA(E14:F14)&lt;2,"",(IF(L14=TRUE,6,IF(M14=TRUE,5,IF(N14=TRUE,4,IF(O14=TRUE,3,IF(P14=TRUE,2,IF(Q14=TRUE,1,IF(R14=TRUE,0,0)))))))))</f>
+        <f t="shared" ref="T14" si="33">IF(COUNTA(E14:F14)&lt;2,"",(IF(L14=TRUE,6,IF(M14=TRUE,5,IF(N14=TRUE,4,IF(O14=TRUE,3,IF(P14=TRUE,2,IF(Q14=TRUE,1,IF(R14=TRUE,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="U14" s="242">
-        <f t="shared" ref="U14:U16" si="47">T14*10+H14</f>
+        <f t="shared" ref="U14" si="34">T14*10+H14</f>
         <v>0</v>
       </c>
       <c r="V14" s="229">
@@ -17142,11 +17142,11 @@
         <v>0</v>
       </c>
       <c r="W14" s="229">
-        <f>'ONR 2'!V8</f>
+        <f>'ONR 2'!V7</f>
         <v>0</v>
       </c>
       <c r="X14" s="204">
-        <f>'ONR 2'!W8</f>
+        <f>'ONR 2'!W7</f>
         <v>0</v>
       </c>
       <c r="Y14" s="230">
@@ -17162,7 +17162,7 @@
         <v>1</v>
       </c>
       <c r="AF14" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="AF14:AL18" si="35">IF(L14=TRUE,1,0)</f>
         <v>0</v>
       </c>
       <c r="AG14" s="206">
@@ -17193,83 +17193,83 @@
     <row r="15" spans="1:38" s="205" customFormat="1" ht="57">
       <c r="A15" s="199"/>
       <c r="B15" s="218" t="str">
-        <f>'ONR 2'!B9</f>
-        <v>2.3</v>
+        <f>'ONR 2'!B8</f>
+        <v>2.2</v>
       </c>
       <c r="C15" s="221" t="str">
-        <f>'ONR 2'!C9</f>
-        <v>En déployant les applications autour des 3 U : Utiles, Utilisables, Utilisées pour en simplifier l’usage en intégrant l’accessibilité universelle pour réussir l’e-inclusion de tous</v>
+        <f>'ONR 2'!C8</f>
+        <v>En permettant des applications accessibles à tous - en mesurant le niveau de conformité RGAA et en accompagnat les entreprises du territoire à se conformer à la règlementation</v>
       </c>
       <c r="D15" s="223">
-        <f>'ONR 2'!D9</f>
+        <f>'ONR 2'!D8</f>
         <v>0</v>
       </c>
       <c r="E15" s="267">
-        <f>'ONR 2'!E9</f>
+        <f>'ONR 2'!E8</f>
         <v>0</v>
       </c>
       <c r="F15" s="274">
-        <f>'ONR 2'!F9</f>
+        <f>'ONR 2'!F8</f>
         <v>0</v>
       </c>
       <c r="G15" s="200">
-        <f>'ONR 2'!G9</f>
+        <f>'ONR 2'!G8</f>
         <v>0</v>
       </c>
       <c r="H15" s="202">
-        <f>'ONR 2'!H9</f>
+        <f>'ONR 2'!H8</f>
         <v>0</v>
       </c>
       <c r="I15" s="225">
-        <f>'ONR 2'!I9</f>
+        <f>'ONR 2'!I8</f>
         <v>0</v>
       </c>
       <c r="J15" s="218">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="J15:J18" si="36">S15</f>
         <v>0</v>
       </c>
       <c r="K15" s="227">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="K15:K18" si="37">E15*10+F15</f>
         <v>0</v>
       </c>
       <c r="L15" s="227" t="b">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="L15:L18" si="38">OR(K15=31)</f>
         <v>0</v>
       </c>
       <c r="M15" s="227" t="b">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="M15:M18" si="39">OR(K15=21,K15=32)</f>
         <v>0</v>
       </c>
       <c r="N15" s="227" t="b">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="N15:N18" si="40">OR(K15=22,K15=33)</f>
         <v>0</v>
       </c>
       <c r="O15" s="227" t="b">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="O15:O18" si="41">OR(K15=11,K15=12)</f>
         <v>0</v>
       </c>
       <c r="P15" s="227" t="b">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="P15:P18" si="42">OR(K15=23,K15=34)</f>
         <v>0</v>
       </c>
       <c r="Q15" s="227" t="b">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="Q15:Q18" si="43">OR(K15=13,K15=14,K15=24)</f>
         <v>0</v>
       </c>
       <c r="R15" s="227" t="b">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="R15:R18" si="44">OR(K15=1,K15=2,K15=3,K15=4)</f>
         <v>0</v>
       </c>
       <c r="S15" s="228">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="S15:S18" si="45">IF(COUNTA(E15:F15)&lt;2,"",(IF(L15=TRUE,$L$3,IF(M15=TRUE,$M$3,IF(N15=TRUE,$N$3,IF(O15=TRUE,$O$3,IF(P15=TRUE,$P$3,IF(Q15=TRUE,$Q$3,IF(R15=TRUE,$R$3,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="T15" s="226">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="T15:T18" si="46">IF(COUNTA(E15:F15)&lt;2,"",(IF(L15=TRUE,6,IF(M15=TRUE,5,IF(N15=TRUE,4,IF(O15=TRUE,3,IF(P15=TRUE,2,IF(Q15=TRUE,1,IF(R15=TRUE,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="U15" s="242">
-        <f t="shared" si="47"/>
+        <f t="shared" ref="U15:U18" si="47">T15*10+H15</f>
         <v>0</v>
       </c>
       <c r="V15" s="229">
@@ -17277,11 +17277,11 @@
         <v>0</v>
       </c>
       <c r="W15" s="229">
-        <f>'ONR 2'!V9</f>
+        <f>'ONR 2'!V8</f>
         <v>0</v>
       </c>
       <c r="X15" s="204">
-        <f>'ONR 2'!W9</f>
+        <f>'ONR 2'!W8</f>
         <v>0</v>
       </c>
       <c r="Y15" s="230">
@@ -17328,95 +17328,95 @@
     <row r="16" spans="1:38" s="205" customFormat="1" ht="57">
       <c r="A16" s="199"/>
       <c r="B16" s="218" t="str">
-        <f>'ONR 2'!B10</f>
-        <v>2.4</v>
+        <f>'ONR 2'!B9</f>
+        <v>2.3</v>
       </c>
       <c r="C16" s="221" t="str">
-        <f>'ONR 2'!C10</f>
-        <v>En associant l’utilisateur à la conception pour éviter des outils surdimensionnés et améliorer progressivement le niveau de conformité des services en ligne.</v>
+        <f>'ONR 2'!C9</f>
+        <v>En déployant les applications autour des 3 U : Utiles, Utilisables, Utilisées pour en simplifier l’usage en intégrant l’accessibilité universelle pour réussir l’e-inclusion de tous</v>
       </c>
       <c r="D16" s="223">
-        <f>'ONR 2'!D10</f>
+        <f>'ONR 2'!D9</f>
         <v>0</v>
       </c>
       <c r="E16" s="267">
-        <f>'ONR 2'!E10</f>
+        <f>'ONR 2'!E9</f>
         <v>0</v>
       </c>
       <c r="F16" s="274">
-        <f>'ONR 2'!F10</f>
+        <f>'ONR 2'!F9</f>
         <v>0</v>
       </c>
       <c r="G16" s="200">
-        <f>'ONR 2'!G10</f>
+        <f>'ONR 2'!G9</f>
         <v>0</v>
       </c>
       <c r="H16" s="202">
-        <f>'ONR 2'!H10</f>
+        <f>'ONR 2'!H9</f>
         <v>0</v>
       </c>
       <c r="I16" s="225">
-        <f>'ONR 2'!I10</f>
+        <f>'ONR 2'!I9</f>
         <v>0</v>
       </c>
       <c r="J16" s="218">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="K16" s="227">
+      <c r="K17" s="227">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="L16" s="227" t="b">
+      <c r="L17" s="227" t="b">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="M16" s="227" t="b">
+      <c r="M17" s="227" t="b">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N16" s="227" t="b">
+      <c r="N17" s="227" t="b">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="O16" s="227" t="b">
+      <c r="O17" s="227" t="b">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="P16" s="227" t="b">
+      <c r="P17" s="227" t="b">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="227" t="b">
+      <c r="Q17" s="227" t="b">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="R16" s="227" t="b">
+      <c r="R17" s="227" t="b">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="S16" s="228">
+      <c r="S17" s="228">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="T16" s="226">
+      <c r="T17" s="226">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="U16" s="242">
+      <c r="U17" s="242">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
-      <c r="V16" s="229">
+      <c r="V17" s="229">
         <f>G16</f>
         <v>0</v>
       </c>
       <c r="W16" s="229">
-        <f>'ONR 2'!V10</f>
+        <f>'ONR 2'!V9</f>
         <v>0</v>
       </c>
       <c r="X16" s="204">
-        <f>'ONR 2'!W10</f>
+        <f>'ONR 2'!W9</f>
         <v>0</v>
       </c>
       <c r="Y16" s="230">
@@ -17460,578 +17460,581 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" s="116" customFormat="1" ht="22">
-      <c r="A17" s="115"/>
-      <c r="B17" s="381" t="str">
-        <f>'ONR 3'!B2:C2</f>
-        <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
-      </c>
-      <c r="C17" s="381"/>
-      <c r="D17" s="381"/>
-      <c r="E17" s="381"/>
-      <c r="F17" s="381"/>
-      <c r="G17" s="381"/>
-      <c r="H17" s="381"/>
-      <c r="I17" s="381"/>
-      <c r="J17" s="381"/>
-      <c r="K17" s="381"/>
-      <c r="L17" s="381"/>
-      <c r="M17" s="381"/>
-      <c r="N17" s="381"/>
-      <c r="O17" s="381"/>
-      <c r="P17" s="381"/>
-      <c r="Q17" s="381"/>
-      <c r="R17" s="381"/>
-      <c r="S17" s="381"/>
-      <c r="T17" s="381"/>
-      <c r="U17" s="381"/>
-      <c r="V17" s="381"/>
-      <c r="W17" s="381"/>
-      <c r="X17" s="381"/>
-      <c r="Y17" s="381"/>
-      <c r="Z17" s="381"/>
-      <c r="AB17" s="116" t="str">
-        <f>B17</f>
-        <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
-      </c>
-      <c r="AC17" s="116">
-        <f>SUMPRODUCT(--(B18:B24&lt;&gt;""))</f>
-        <v>7</v>
-      </c>
-      <c r="AD17" s="116">
-        <f>AC17-AE17</f>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="117">
-        <f t="shared" ref="AE17:AL17" si="48">SUM(AE18:AE24)</f>
-        <v>7</v>
-      </c>
-      <c r="AF17" s="117">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AG17" s="117">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AH17" s="117">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AI17" s="117">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="117">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AK17" s="117">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AL17" s="117">
-        <f t="shared" si="48"/>
+    <row r="17" spans="1:38" s="205" customFormat="1" ht="57">
+      <c r="A17" s="199"/>
+      <c r="B17" s="218" t="str">
+        <f>'ONR 2'!B10</f>
+        <v>2.4</v>
+      </c>
+      <c r="C17" s="221" t="str">
+        <f>'ONR 2'!C10</f>
+        <v>En associant l’utilisateur à la conception pour éviter des outils surdimensionnés et améliorer progressivement le niveau de conformité des services en ligne.</v>
+      </c>
+      <c r="D17" s="223">
+        <f>'ONR 2'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="267">
+        <f>'ONR 2'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="274">
+        <f>'ONR 2'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="200">
+        <f>'ONR 2'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="202">
+        <f>'ONR 2'!H10</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="225">
+        <f>'ONR 2'!I10</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="218">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="227">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="227" t="b">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="227" t="b">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="227" t="b">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="227" t="b">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="227" t="b">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="227" t="b">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="227" t="b">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="228">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="226">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="242">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="229">
+        <f>G17</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="229">
+        <f>'ONR 2'!V10</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="204">
+        <f>'ONR 2'!W10</f>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="230">
+        <f>I17</f>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="230">
+        <f>D17</f>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="206">
+        <f>IF(K17=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF17" s="206">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="206">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="206">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="206">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="206">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="206">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="206">
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:38" s="205" customFormat="1" ht="57">
       <c r="A18" s="199"/>
-      <c r="B18" s="219" t="str">
+      <c r="B18" s="218" t="str">
+        <f>'ONR 2'!B11</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="221" t="str">
+        <f>'ONR 2'!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="223">
+        <f>'ONR 2'!D11</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="267">
+        <f>'ONR 2'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="274">
+        <f>'ONR 2'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="200">
+        <f>'ONR 2'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="202">
+        <f>'ONR 2'!H11</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="225">
+        <f>'ONR 2'!I11</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="218">
+        <f>S18</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="227">
+        <f>E18*10+F18</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="227" t="b">
+        <f>OR(K18=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="227" t="b">
+        <f>OR(K18=21,K18=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="227" t="b">
+        <f>OR(K18=22,K18=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="227" t="b">
+        <f>OR(K18=11,K18=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="227" t="b">
+        <f>OR(K18=23,K18=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="227" t="b">
+        <f>OR(K18=13,K18=14,K18=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="227" t="b">
+        <f>OR(K18=1,K18=2,K18=3,K18=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="228">
+        <f>IF(COUNTA(E18:F18)&lt;2,"",(IF(L18=TRUE,$L$3,IF(M18=TRUE,$M$3,IF(N18=TRUE,$N$3,IF(O18=TRUE,$O$3,IF(P18=TRUE,$P$3,IF(Q18=TRUE,$Q$3,IF(R18=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="226">
+        <f>IF(COUNTA(E18:F18)&lt;2,"",(IF(L18=TRUE,6,IF(M18=TRUE,5,IF(N18=TRUE,4,IF(O18=TRUE,3,IF(P18=TRUE,2,IF(Q18=TRUE,1,IF(R18=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="242">
+        <f>T18*10+H18</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="229">
+        <f>G18</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="229">
+        <f>'ONR 2'!V11</f>
+        <v>0</v>
+      </c>
+      <c r="X18" s="204">
+        <f>'ONR 2'!W11</f>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="230">
+        <f>I18</f>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="230">
+        <f>D18</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="206">
+        <f>IF(K18=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="206">
+        <f>IF(L18=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="206">
+        <f>IF(L18=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="206">
+        <f>IF(L18=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="206">
+        <f>IF(L18=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="206">
+        <f>IF(L18=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="206">
+        <f>IF(L18=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="206">
+        <f>IF(L18=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" s="116" customFormat="1" ht="22">
+      <c r="A19" s="115"/>
+      <c r="B19" s="381" t="str">
+        <f>'ONR 3'!B2:C2</f>
+        <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
+      </c>
+      <c r="C19" s="381"/>
+      <c r="D19" s="381"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
+      <c r="G19" s="381"/>
+      <c r="H19" s="381"/>
+      <c r="I19" s="381"/>
+      <c r="J19" s="381"/>
+      <c r="K19" s="381"/>
+      <c r="L19" s="381"/>
+      <c r="M19" s="381"/>
+      <c r="N19" s="381"/>
+      <c r="O19" s="381"/>
+      <c r="P19" s="381"/>
+      <c r="Q19" s="381"/>
+      <c r="R19" s="381"/>
+      <c r="S19" s="381"/>
+      <c r="T19" s="381"/>
+      <c r="U19" s="381"/>
+      <c r="V19" s="381"/>
+      <c r="W19" s="381"/>
+      <c r="X19" s="381"/>
+      <c r="Y19" s="381"/>
+      <c r="Z19" s="381"/>
+      <c r="AB19" s="116" t="str">
+        <f>B19</f>
+        <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
+      </c>
+      <c r="AC19" s="116">
+        <f>SUMPRODUCT(--(B20:B27&lt;&gt;""))</f>
+        <v>7</v>
+      </c>
+      <c r="AD19" s="116">
+        <f>AC19-AE19</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="117">
+        <f>SUM(AE20:AE27)</f>
+        <v>7</v>
+      </c>
+      <c r="AF19" s="117">
+        <f>SUM(AF20:AF27)</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="117">
+        <f>SUM(AG20:AG27)</f>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="117">
+        <f>SUM(AH20:AH27)</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="117">
+        <f>SUM(AI20:AI27)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="117">
+        <f>SUM(AJ20:AJ27)</f>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="117">
+        <f>SUM(AK20:AK27)</f>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="117">
+        <f>SUM(AL20:AL27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" s="205" customFormat="1" ht="57">
+      <c r="A20" s="199"/>
+      <c r="B20" s="219" t="str">
         <f>'ONR 3'!B7</f>
         <v>3.1</v>
       </c>
-      <c r="C18" s="219" t="str">
+      <c r="C20" s="219" t="str">
         <f>'ONR 3'!C7</f>
         <v>En développant des usages raisonnés des données et services dans une démarche éthique vis-à-vis des impacts sur l’environnement et les populations.</v>
       </c>
-      <c r="D18" s="244">
+      <c r="D20" s="244">
         <f>'ONR 3'!D7</f>
         <v>0</v>
       </c>
-      <c r="E18" s="271">
+      <c r="E20" s="271">
         <f>'ONR 3'!E7</f>
         <v>0</v>
       </c>
-      <c r="F18" s="278">
+      <c r="F20" s="278">
         <f>'ONR 3'!F7</f>
         <v>0</v>
       </c>
-      <c r="G18" s="213">
+      <c r="G20" s="213">
         <f>'ONR 3'!G7</f>
         <v>0</v>
       </c>
-      <c r="H18" s="214">
+      <c r="H20" s="214">
         <f>'ONR 3'!H7</f>
         <v>0</v>
       </c>
-      <c r="I18" s="245">
+      <c r="I20" s="245">
         <f>'ONR 3'!I7</f>
         <v>0</v>
       </c>
-      <c r="J18" s="246">
-        <f t="shared" ref="J18:J23" si="49">S18</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="247">
-        <f t="shared" ref="K18:K23" si="50">E18*10+F18</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="247" t="b">
-        <f t="shared" ref="L18:L23" si="51">OR(K18=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="247" t="b">
-        <f t="shared" ref="M18:M23" si="52">OR(K18=21,K18=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="247" t="b">
-        <f t="shared" ref="N18:N23" si="53">OR(K18=22,K18=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="247" t="b">
-        <f t="shared" ref="O18:O23" si="54">OR(K18=11,K18=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="247" t="b">
-        <f t="shared" ref="P18:P23" si="55">OR(K18=23,K18=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="247" t="b">
-        <f t="shared" ref="Q18:Q23" si="56">OR(K18=13,K18=14,K18=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="247" t="b">
-        <f t="shared" ref="R18:R23" si="57">OR(K18=1,K18=2,K18=3,K18=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="248">
-        <f t="shared" ref="S18:S23" si="58">IF(COUNTA(E18:F18)&lt;2,"",(IF(L18=TRUE,$L$3,IF(M18=TRUE,$M$3,IF(N18=TRUE,$N$3,IF(O18=TRUE,$O$3,IF(P18=TRUE,$P$3,IF(Q18=TRUE,$Q$3,IF(R18=TRUE,$R$3,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="T18" s="249">
-        <f t="shared" ref="T18:T23" si="59">IF(COUNTA(E18:F18)&lt;2,"",(IF(L18=TRUE,6,IF(M18=TRUE,5,IF(N18=TRUE,4,IF(O18=TRUE,3,IF(P18=TRUE,2,IF(Q18=TRUE,1,IF(R18=TRUE,0,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="U18" s="250">
-        <f t="shared" ref="U18:U23" si="60">T18*10+H18</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="235">
-        <f t="shared" ref="V18:V24" si="61">G18</f>
-        <v>0</v>
-      </c>
-      <c r="W18" s="235">
+      <c r="J20" s="246">
+        <f t="shared" ref="J20:J25" si="49">S20</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="247">
+        <f t="shared" ref="K20:K25" si="50">E20*10+F20</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="247" t="b">
+        <f t="shared" ref="L20:L25" si="51">OR(K20=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="247" t="b">
+        <f t="shared" ref="M20:M25" si="52">OR(K20=21,K20=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="247" t="b">
+        <f t="shared" ref="N20:N25" si="53">OR(K20=22,K20=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="247" t="b">
+        <f t="shared" ref="O20:O25" si="54">OR(K20=11,K20=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="247" t="b">
+        <f t="shared" ref="P20:P25" si="55">OR(K20=23,K20=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="247" t="b">
+        <f t="shared" ref="Q20:Q25" si="56">OR(K20=13,K20=14,K20=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="247" t="b">
+        <f t="shared" ref="R20:R25" si="57">OR(K20=1,K20=2,K20=3,K20=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="248">
+        <f t="shared" ref="S20:S25" si="58">IF(COUNTA(E20:F20)&lt;2,"",(IF(L20=TRUE,$L$3,IF(M20=TRUE,$M$3,IF(N20=TRUE,$N$3,IF(O20=TRUE,$O$3,IF(P20=TRUE,$P$3,IF(Q20=TRUE,$Q$3,IF(R20=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="249">
+        <f t="shared" ref="T20:T25" si="59">IF(COUNTA(E20:F20)&lt;2,"",(IF(L20=TRUE,6,IF(M20=TRUE,5,IF(N20=TRUE,4,IF(O20=TRUE,3,IF(P20=TRUE,2,IF(Q20=TRUE,1,IF(R20=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="250">
+        <f t="shared" ref="U20:U25" si="60">T20*10+H20</f>
+        <v>0</v>
+      </c>
+      <c r="V20" s="235">
+        <f t="shared" ref="V20:V27" si="61">G20</f>
+        <v>0</v>
+      </c>
+      <c r="W20" s="235">
         <f>'ONR 3'!V7</f>
         <v>0</v>
       </c>
-      <c r="X18" s="183">
+      <c r="X20" s="183">
         <f>'ONR 3'!W7</f>
         <v>0</v>
       </c>
-      <c r="Y18" s="236">
-        <f t="shared" ref="Y18:Y24" si="62">I18</f>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="236">
-        <f t="shared" ref="Z18:Z24" si="63">D18</f>
-        <v>0</v>
-      </c>
-      <c r="AE18" s="206">
-        <f t="shared" ref="AE18:AE24" si="64">IF(K18=0,1,0)</f>
+      <c r="Y20" s="236">
+        <f t="shared" ref="Y20:Y27" si="62">I20</f>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="236">
+        <f t="shared" ref="Z20:Z27" si="63">D20</f>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="206">
+        <f t="shared" ref="AE20:AE27" si="64">IF(K20=0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AF18" s="206">
-        <f t="shared" ref="AF18:AL24" si="65">IF(L18=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG18" s="206">
+      <c r="AF20" s="206">
+        <f t="shared" ref="AF20:AL27" si="65">IF(L20=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="206">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="206">
+      <c r="AH20" s="206">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AI18" s="206">
+      <c r="AI20" s="206">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AJ18" s="206">
+      <c r="AJ20" s="206">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="206">
+      <c r="AK20" s="206">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AL18" s="206">
+      <c r="AL20" s="206">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" s="205" customFormat="1" ht="57">
-      <c r="A19" s="199"/>
-      <c r="B19" s="219" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="219" t="str">
+    <row r="21" spans="1:38" s="205" customFormat="1" ht="57">
+      <c r="A21" s="199"/>
+      <c r="B21" s="219" t="str">
+        <f>'ONR 3'!B8</f>
+        <v>3.2</v>
+      </c>
+      <c r="C21" s="219" t="str">
         <f>'ONR 3'!C8</f>
         <v>En luttant contre les pratiques trompeuses et présence de dark pattern dans les sites internet et en permettant de se conformer à la réglementation</v>
       </c>
-      <c r="D19" s="244">
+      <c r="D21" s="244">
         <f>'ONR 3'!D8</f>
         <v>0</v>
       </c>
-      <c r="E19" s="271">
+      <c r="E21" s="271">
         <f>'ONR 3'!E8</f>
         <v>0</v>
       </c>
-      <c r="F19" s="278">
+      <c r="F21" s="278">
         <f>'ONR 3'!F8</f>
         <v>0</v>
       </c>
-      <c r="G19" s="213">
+      <c r="G21" s="213">
         <f>'ONR 3'!G8</f>
         <v>0</v>
       </c>
-      <c r="H19" s="214">
+      <c r="H21" s="214">
         <f>'ONR 3'!H8</f>
         <v>0</v>
       </c>
-      <c r="I19" s="245">
+      <c r="I21" s="245">
         <f>'ONR 3'!I8</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="246">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="247">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="247" t="b">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="247" t="b">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="247" t="b">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="247" t="b">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="247" t="b">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="247" t="b">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="247" t="b">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="248">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="T19" s="249">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="250">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="235">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="235">
-        <f>'ONR 3'!V8</f>
-        <v>0</v>
-      </c>
-      <c r="X19" s="183">
-        <f>'ONR 3'!W8</f>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="236">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="251">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="206">
-        <f t="shared" si="64"/>
-        <v>1</v>
-      </c>
-      <c r="AF19" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AG19" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AH19" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AI19" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:38" s="205" customFormat="1" ht="76">
-      <c r="A20" s="199"/>
-      <c r="B20" s="219" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="219" t="str">
-        <f>'ONR 3'!C9</f>
-        <v>En ne collectant que les données utiles et nécessaires au service des utilisateurs, afin de limiter les risques en matière de vie privée et impacts environnementaux en conformité avec le Règlement Général sur la Protection des Données (RGPD).</v>
-      </c>
-      <c r="D20" s="244">
-        <f>'ONR 3'!D9</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="271">
-        <f>'ONR 3'!E9</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="278">
-        <f>'ONR 3'!F9</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="213">
-        <f>'ONR 3'!G9</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="214">
-        <f>'ONR 3'!H9</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="245">
-        <f>'ONR 3'!I9</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="246">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="247">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="247" t="b">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="247" t="b">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="247" t="b">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="247" t="b">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="247" t="b">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="247" t="b">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="247" t="b">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="248">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="249">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="250">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="235">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="235">
-        <f>'ONR 3'!V9</f>
-        <v>0</v>
-      </c>
-      <c r="X20" s="183">
-        <f>'ONR 3'!W9</f>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="236">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="251">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AE20" s="206">
-        <f t="shared" si="64"/>
-        <v>1</v>
-      </c>
-      <c r="AF20" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AG20" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AH20" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AI20" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AK20" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AL20" s="206">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:38" s="205" customFormat="1" ht="19">
-      <c r="A21" s="199"/>
-      <c r="B21" s="238" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="219" t="str">
-        <f>'ONR 3'!C10</f>
-        <v>En favorisant la diversité des recrutements des métiers du numérique</v>
-      </c>
-      <c r="D21" s="244">
-        <f>'ONR 3'!D10</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="271">
-        <f>'ONR 3'!E10</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="278">
-        <f>'ONR 3'!F10</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="213">
-        <f>'ONR 3'!G10</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="214">
-        <f>'ONR 3'!H10</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="245">
-        <f>'ONR 3'!I10</f>
         <v>0</v>
       </c>
       <c r="J21" s="246">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="K21" s="247">
+      <c r="K23" s="247">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="L21" s="247" t="b">
+      <c r="L23" s="247" t="b">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="M21" s="247" t="b">
+      <c r="M23" s="247" t="b">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="N21" s="247" t="b">
+      <c r="N23" s="247" t="b">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="O21" s="247" t="b">
+      <c r="O23" s="247" t="b">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="P21" s="247" t="b">
+      <c r="P23" s="247" t="b">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="247" t="b">
+      <c r="Q23" s="247" t="b">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="R21" s="247" t="b">
+      <c r="R23" s="247" t="b">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S23" s="248">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="T21" s="249">
+      <c r="T23" s="249">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="U21" s="250">
+      <c r="U23" s="250">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="V21" s="252">
+      <c r="V23" s="235">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="W21" s="252">
-        <f>'ONR 3'!V10</f>
+      <c r="W23" s="235">
+        <f>'ONR 3'!V8</f>
         <v>0</v>
       </c>
       <c r="X21" s="183">
-        <f>'ONR 3'!W10</f>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="253">
+        <f>'ONR 3'!W8</f>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="236">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
@@ -18072,100 +18075,101 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" s="205" customFormat="1" ht="19">
+    <row r="22" spans="1:38" s="205" customFormat="1" ht="76">
       <c r="A22" s="199"/>
-      <c r="B22" s="238" t="s">
-        <v>67</v>
+      <c r="B22" s="219" t="str">
+        <f>'ONR 3'!B9</f>
+        <v>3.3</v>
       </c>
       <c r="C22" s="219" t="str">
-        <f>'ONR 3'!C11</f>
-        <v>En améliorant les conditions des travailleurs du numérique</v>
+        <f>'ONR 3'!C9</f>
+        <v>En ne collectant que les données utiles et nécessaires au service des utilisateurs, afin de limiter les risques en matière de vie privée et impacts environnementaux en conformité avec le Règlement Général sur la Protection des Données (RGPD).</v>
       </c>
       <c r="D22" s="244">
-        <f>'ONR 3'!D11</f>
+        <f>'ONR 3'!D9</f>
         <v>0</v>
       </c>
       <c r="E22" s="271">
-        <f>'ONR 3'!E11</f>
+        <f>'ONR 3'!E9</f>
         <v>0</v>
       </c>
       <c r="F22" s="278">
-        <f>'ONR 3'!F11</f>
+        <f>'ONR 3'!F9</f>
         <v>0</v>
       </c>
       <c r="G22" s="213">
-        <f>'ONR 3'!G11</f>
+        <f>'ONR 3'!G9</f>
         <v>0</v>
       </c>
       <c r="H22" s="214">
-        <f>'ONR 3'!H11</f>
+        <f>'ONR 3'!H9</f>
         <v>0</v>
       </c>
       <c r="I22" s="245">
-        <f>'ONR 3'!I11</f>
+        <f>'ONR 3'!I9</f>
         <v>0</v>
       </c>
       <c r="J22" s="246">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="K22" s="247">
+      <c r="K24" s="247">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="L22" s="247" t="b">
+      <c r="L24" s="247" t="b">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="M22" s="247" t="b">
+      <c r="M24" s="247" t="b">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="N22" s="247" t="b">
+      <c r="N24" s="247" t="b">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="O22" s="247" t="b">
+      <c r="O24" s="247" t="b">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="P22" s="247" t="b">
+      <c r="P24" s="247" t="b">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="247" t="b">
+      <c r="Q24" s="247" t="b">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="R22" s="247" t="b">
+      <c r="R24" s="247" t="b">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="S22" s="248">
+      <c r="S24" s="248">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="T22" s="249">
+      <c r="T24" s="249">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="U22" s="250">
+      <c r="U24" s="250">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="V22" s="252">
+      <c r="V24" s="235">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="W22" s="145">
-        <f>'ONR 3'!V11</f>
+      <c r="W24" s="235">
+        <f>'ONR 3'!V9</f>
         <v>0</v>
       </c>
       <c r="X22" s="183">
-        <f>'ONR 3'!W11</f>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="253">
+        <f>'ONR 3'!W9</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="236">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
@@ -18206,100 +18210,101 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" s="205" customFormat="1" ht="57">
+    <row r="23" spans="1:38" s="205" customFormat="1" ht="19">
       <c r="A23" s="199"/>
-      <c r="B23" s="219" t="s">
-        <v>69</v>
+      <c r="B23" s="238" t="str">
+        <f>'ONR 3'!B10</f>
+        <v>3.4</v>
       </c>
       <c r="C23" s="219" t="str">
-        <f>'ONR 3'!C12</f>
-        <v>En s’inscrivant résolument dans des dispositifs d’éthique algorithmique sur l’utilisation et la protection des données, notamment au regard de l’intelligence artificielle</v>
+        <f>'ONR 3'!C10</f>
+        <v>En favorisant la diversité des recrutements des métiers du numérique</v>
       </c>
       <c r="D23" s="244">
-        <f>'ONR 3'!D12</f>
+        <f>'ONR 3'!D10</f>
         <v>0</v>
       </c>
       <c r="E23" s="271">
-        <f>'ONR 3'!E12</f>
+        <f>'ONR 3'!E10</f>
         <v>0</v>
       </c>
       <c r="F23" s="278">
-        <f>'ONR 3'!F12</f>
+        <f>'ONR 3'!F10</f>
         <v>0</v>
       </c>
       <c r="G23" s="213">
-        <f>'ONR 3'!G12</f>
+        <f>'ONR 3'!G10</f>
         <v>0</v>
       </c>
       <c r="H23" s="214">
-        <f>'ONR 3'!H12</f>
+        <f>'ONR 3'!H10</f>
         <v>0</v>
       </c>
       <c r="I23" s="245">
-        <f>'ONR 3'!I12</f>
+        <f>'ONR 3'!I10</f>
         <v>0</v>
       </c>
       <c r="J23" s="246">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="K23" s="247">
+      <c r="K25" s="247">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="L23" s="247" t="b">
+      <c r="L25" s="247" t="b">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="M23" s="247" t="b">
+      <c r="M25" s="247" t="b">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="N23" s="247" t="b">
+      <c r="N25" s="247" t="b">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="O23" s="247" t="b">
+      <c r="O25" s="247" t="b">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="P23" s="247" t="b">
+      <c r="P25" s="247" t="b">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="247" t="b">
+      <c r="Q25" s="247" t="b">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="R23" s="247" t="b">
+      <c r="R25" s="247" t="b">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="S23" s="248">
+      <c r="S25" s="248">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="T23" s="249">
+      <c r="T25" s="249">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="U23" s="250">
+      <c r="U25" s="250">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="V23" s="241">
+      <c r="V25" s="252">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="W23" s="148">
-        <f>'ONR 3'!V12</f>
+      <c r="W25" s="252">
+        <f>'ONR 3'!V10</f>
         <v>0</v>
       </c>
       <c r="X23" s="183">
-        <f>'ONR 3'!W12</f>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="254">
+        <f>'ONR 3'!W10</f>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="253">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
@@ -18340,100 +18345,101 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" s="205" customFormat="1" ht="20" thickBot="1">
+    <row r="24" spans="1:38" s="205" customFormat="1" ht="19">
       <c r="A24" s="199"/>
-      <c r="B24" s="220" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="220" t="str">
-        <f>'ONR 3'!C13</f>
-        <v>En déployant et valorisant la démarche RSE</v>
+      <c r="B24" s="238" t="str">
+        <f>'ONR 3'!B11</f>
+        <v>3.5</v>
+      </c>
+      <c r="C24" s="219" t="str">
+        <f>'ONR 3'!C11</f>
+        <v>En améliorant les conditions des travailleurs du numérique</v>
       </c>
       <c r="D24" s="244">
-        <f>'ONR 3'!D13</f>
+        <f>'ONR 3'!D11</f>
         <v>0</v>
       </c>
       <c r="E24" s="271">
-        <f>'ONR 3'!E13</f>
+        <f>'ONR 3'!E11</f>
         <v>0</v>
       </c>
       <c r="F24" s="278">
-        <f>'ONR 3'!F13</f>
+        <f>'ONR 3'!F11</f>
         <v>0</v>
       </c>
       <c r="G24" s="213">
-        <f>'ONR 3'!G13</f>
+        <f>'ONR 3'!G11</f>
         <v>0</v>
       </c>
       <c r="H24" s="214">
-        <f>'ONR 3'!H13</f>
+        <f>'ONR 3'!H11</f>
         <v>0</v>
       </c>
       <c r="I24" s="245">
-        <f>'ONR 3'!I13</f>
+        <f>'ONR 3'!I11</f>
         <v>0</v>
       </c>
       <c r="J24" s="246">
-        <f t="shared" ref="J24" si="66">S24</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="247">
-        <f t="shared" ref="K24" si="67">E24*10+F24</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="247" t="b">
-        <f t="shared" ref="L24" si="68">OR(K24=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="247" t="b">
-        <f t="shared" ref="M24" si="69">OR(K24=21,K24=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="247" t="b">
-        <f t="shared" ref="N24" si="70">OR(K24=22,K24=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="247" t="b">
-        <f t="shared" ref="O24" si="71">OR(K24=11,K24=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P24" s="247" t="b">
-        <f t="shared" ref="P24" si="72">OR(K24=23,K24=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="247" t="b">
-        <f t="shared" ref="Q24" si="73">OR(K24=13,K24=14,K24=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="247" t="b">
-        <f t="shared" ref="R24" si="74">OR(K24=1,K24=2,K24=3,K24=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S24" s="248">
-        <f t="shared" ref="S24" si="75">IF(COUNTA(E24:F24)&lt;2,"",(IF(L24=TRUE,$L$3,IF(M24=TRUE,$M$3,IF(N24=TRUE,$N$3,IF(O24=TRUE,$O$3,IF(P24=TRUE,$P$3,IF(Q24=TRUE,$Q$3,IF(R24=TRUE,$R$3,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="T24" s="249">
-        <f t="shared" ref="T24" si="76">IF(COUNTA(E24:F24)&lt;2,"",(IF(L24=TRUE,6,IF(M24=TRUE,5,IF(N24=TRUE,4,IF(O24=TRUE,3,IF(P24=TRUE,2,IF(Q24=TRUE,1,IF(R24=TRUE,0,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="U24" s="250">
-        <f t="shared" ref="U24" si="77">T24*10+H24</f>
-        <v>0</v>
-      </c>
-      <c r="V24" s="255">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="247">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="247" t="b">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="247" t="b">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="247" t="b">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="247" t="b">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="247" t="b">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="247" t="b">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="247" t="b">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="248">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="249">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="250">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="252">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="W24" s="215">
-        <f>'ONR 3'!V13</f>
+      <c r="W26" s="145">
+        <f>'ONR 3'!V11</f>
         <v>0</v>
       </c>
       <c r="X24" s="183">
-        <f>'ONR 3'!W13</f>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="251">
+        <f>'ONR 3'!W11</f>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="253">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
@@ -18474,585 +18480,585 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" s="116" customFormat="1" ht="23" thickBot="1">
-      <c r="A25" s="115"/>
-      <c r="B25" s="362" t="str">
+    <row r="25" spans="1:38" s="205" customFormat="1" ht="57">
+      <c r="A25" s="199"/>
+      <c r="B25" s="219" t="str">
+        <f>'ONR 3'!B12</f>
+        <v>3.6</v>
+      </c>
+      <c r="C25" s="219" t="str">
+        <f>'ONR 3'!C12</f>
+        <v>En s’inscrivant résolument dans des dispositifs d’éthique algorithmique sur l’utilisation et la protection des données, notamment au regard de l’intelligence artificielle</v>
+      </c>
+      <c r="D25" s="244">
+        <f>'ONR 3'!D12</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="271">
+        <f>'ONR 3'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="278">
+        <f>'ONR 3'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="213">
+        <f>'ONR 3'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="214">
+        <f>'ONR 3'!H12</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="245">
+        <f>'ONR 3'!I12</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="246">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="247">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="247" t="b">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="247" t="b">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="247" t="b">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="247" t="b">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="247" t="b">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="247" t="b">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="247" t="b">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="248">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="249">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="250">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="241">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="148">
+        <f>'ONR 3'!V12</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="183">
+        <f>'ONR 3'!W12</f>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="254">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="251">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="206">
+        <f t="shared" si="64"/>
+        <v>1</v>
+      </c>
+      <c r="AF25" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" s="205" customFormat="1" ht="20" thickBot="1">
+      <c r="A26" s="199"/>
+      <c r="B26" s="220" t="str">
+        <f>'ONR 3'!B13</f>
+        <v>3.7</v>
+      </c>
+      <c r="C26" s="220" t="str">
+        <f>'ONR 3'!C13</f>
+        <v>En déployant et valorisant la démarche RSE</v>
+      </c>
+      <c r="D26" s="244">
+        <f>'ONR 3'!D13</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="271">
+        <f>'ONR 3'!E13</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="278">
+        <f>'ONR 3'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="213">
+        <f>'ONR 3'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="214">
+        <f>'ONR 3'!H13</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="245">
+        <f>'ONR 3'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="246">
+        <f t="shared" ref="J26" si="66">S26</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="247">
+        <f t="shared" ref="K26" si="67">E26*10+F26</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="247" t="b">
+        <f t="shared" ref="L26" si="68">OR(K26=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="247" t="b">
+        <f t="shared" ref="M26" si="69">OR(K26=21,K26=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="247" t="b">
+        <f t="shared" ref="N26" si="70">OR(K26=22,K26=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="247" t="b">
+        <f t="shared" ref="O26" si="71">OR(K26=11,K26=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="247" t="b">
+        <f t="shared" ref="P26" si="72">OR(K26=23,K26=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="247" t="b">
+        <f t="shared" ref="Q26" si="73">OR(K26=13,K26=14,K26=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="247" t="b">
+        <f t="shared" ref="R26" si="74">OR(K26=1,K26=2,K26=3,K26=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="248">
+        <f t="shared" ref="S26" si="75">IF(COUNTA(E26:F26)&lt;2,"",(IF(L26=TRUE,$L$3,IF(M26=TRUE,$M$3,IF(N26=TRUE,$N$3,IF(O26=TRUE,$O$3,IF(P26=TRUE,$P$3,IF(Q26=TRUE,$Q$3,IF(R26=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T26" s="249">
+        <f t="shared" ref="T26" si="76">IF(COUNTA(E26:F26)&lt;2,"",(IF(L26=TRUE,6,IF(M26=TRUE,5,IF(N26=TRUE,4,IF(O26=TRUE,3,IF(P26=TRUE,2,IF(Q26=TRUE,1,IF(R26=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U26" s="250">
+        <f t="shared" ref="U26" si="77">T26*10+H26</f>
+        <v>0</v>
+      </c>
+      <c r="V26" s="255">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="215">
+        <f>'ONR 3'!V13</f>
+        <v>0</v>
+      </c>
+      <c r="X26" s="183">
+        <f>'ONR 3'!W13</f>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="251">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="251">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="AE26" s="206">
+        <f t="shared" si="64"/>
+        <v>1</v>
+      </c>
+      <c r="AF26" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AG26" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AH26" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AI26" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AK26" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AL26" s="206">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" s="205" customFormat="1" ht="20" thickBot="1">
+      <c r="A27" s="199"/>
+      <c r="B27" s="220" t="str">
+        <f>'ONR 3'!B14</f>
+        <v>3.8</v>
+      </c>
+      <c r="C27" s="220" t="str">
+        <f>'ONR 3'!C14</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="244">
+        <f>'ONR 3'!D14</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="271">
+        <f>'ONR 3'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="278">
+        <f>'ONR 3'!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="213">
+        <f>'ONR 3'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="214">
+        <f>'ONR 3'!H14</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="245">
+        <f>'ONR 3'!I14</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="246">
+        <f>S27</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="247">
+        <f>E27*10+F27</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="247" t="b">
+        <f>OR(K27=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="247" t="b">
+        <f>OR(K27=21,K27=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="247" t="b">
+        <f>OR(K27=22,K27=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="247" t="b">
+        <f>OR(K27=11,K27=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="247" t="b">
+        <f>OR(K27=23,K27=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="247" t="b">
+        <f>OR(K27=13,K27=14,K27=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="247" t="b">
+        <f>OR(K27=1,K27=2,K27=3,K27=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="248">
+        <f>IF(COUNTA(E27:F27)&lt;2,"",(IF(L27=TRUE,$L$3,IF(M27=TRUE,$M$3,IF(N27=TRUE,$N$3,IF(O27=TRUE,$O$3,IF(P27=TRUE,$P$3,IF(Q27=TRUE,$Q$3,IF(R27=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T27" s="249">
+        <f>IF(COUNTA(E27:F27)&lt;2,"",(IF(L27=TRUE,6,IF(M27=TRUE,5,IF(N27=TRUE,4,IF(O27=TRUE,3,IF(P27=TRUE,2,IF(Q27=TRUE,1,IF(R27=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U27" s="250">
+        <f>T27*10+H27</f>
+        <v>0</v>
+      </c>
+      <c r="V27" s="255">
+        <f>G27</f>
+        <v>0</v>
+      </c>
+      <c r="W27" s="215">
+        <f>'ONR 3'!V14</f>
+        <v>0</v>
+      </c>
+      <c r="X27" s="183">
+        <f>'ONR 3'!W14</f>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="251">
+        <f>I27</f>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="251">
+        <f>D27</f>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="206">
+        <f>IF(K27=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF27" s="206">
+        <f>IF(L27=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG27" s="206">
+        <f>IF(L27=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="206">
+        <f>IF(L27=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI27" s="206">
+        <f>IF(L27=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="206">
+        <f>IF(L27=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK27" s="206">
+        <f>IF(L27=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL27" s="206">
+        <f>IF(L27=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" s="116" customFormat="1" ht="23" thickBot="1">
+      <c r="A28" s="115"/>
+      <c r="B28" s="362" t="str">
         <f>'ONR 4'!B2:C2</f>
         <v>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
       </c>
-      <c r="C25" s="363"/>
-      <c r="D25" s="363"/>
-      <c r="E25" s="363"/>
-      <c r="F25" s="363"/>
-      <c r="G25" s="363"/>
-      <c r="H25" s="363"/>
-      <c r="I25" s="363"/>
-      <c r="J25" s="363"/>
-      <c r="K25" s="363"/>
-      <c r="L25" s="363"/>
-      <c r="M25" s="363"/>
-      <c r="N25" s="363"/>
-      <c r="O25" s="363"/>
-      <c r="P25" s="363"/>
-      <c r="Q25" s="363"/>
-      <c r="R25" s="363"/>
-      <c r="S25" s="363"/>
-      <c r="T25" s="363"/>
-      <c r="U25" s="363"/>
-      <c r="V25" s="363"/>
-      <c r="W25" s="363"/>
-      <c r="X25" s="363"/>
-      <c r="Y25" s="363"/>
-      <c r="Z25" s="380"/>
-      <c r="AB25" s="116" t="str">
-        <f>B25</f>
+      <c r="C28" s="363"/>
+      <c r="D28" s="363"/>
+      <c r="E28" s="363"/>
+      <c r="F28" s="363"/>
+      <c r="G28" s="363"/>
+      <c r="H28" s="363"/>
+      <c r="I28" s="363"/>
+      <c r="J28" s="363"/>
+      <c r="K28" s="363"/>
+      <c r="L28" s="363"/>
+      <c r="M28" s="363"/>
+      <c r="N28" s="363"/>
+      <c r="O28" s="363"/>
+      <c r="P28" s="363"/>
+      <c r="Q28" s="363"/>
+      <c r="R28" s="363"/>
+      <c r="S28" s="363"/>
+      <c r="T28" s="363"/>
+      <c r="U28" s="363"/>
+      <c r="V28" s="363"/>
+      <c r="W28" s="363"/>
+      <c r="X28" s="363"/>
+      <c r="Y28" s="363"/>
+      <c r="Z28" s="380"/>
+      <c r="AB28" s="116" t="str">
+        <f>B28</f>
         <v>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
       </c>
-      <c r="AC25" s="116">
-        <f>SUMPRODUCT(--(B26:B29&lt;&gt;""))</f>
+      <c r="AC28" s="116">
+        <f>SUMPRODUCT(--(B29:B32&lt;&gt;""))</f>
         <v>4</v>
       </c>
-      <c r="AD25" s="116">
-        <f>AC25-AE25</f>
-        <v>0</v>
-      </c>
-      <c r="AE25" s="117">
-        <f t="shared" ref="AE25:AL25" si="78">SUM(AE26:AE29)</f>
+      <c r="AD28" s="116">
+        <f>AC28-AE28</f>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="117">
+        <f>SUM(AE29:AE32)</f>
         <v>4</v>
       </c>
-      <c r="AF25" s="117">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AG25" s="117">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AH25" s="117">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI25" s="117">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="117">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AK25" s="117">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AL25" s="117">
-        <f t="shared" si="78"/>
+      <c r="AF28" s="117">
+        <f>SUM(AF29:AF32)</f>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="117">
+        <f>SUM(AG29:AG32)</f>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="117">
+        <f>SUM(AH29:AH32)</f>
+        <v>0</v>
+      </c>
+      <c r="AI28" s="117">
+        <f>SUM(AI29:AI32)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="117">
+        <f>SUM(AJ29:AJ32)</f>
+        <v>0</v>
+      </c>
+      <c r="AK28" s="117">
+        <f>SUM(AK29:AK32)</f>
+        <v>0</v>
+      </c>
+      <c r="AL28" s="117">
+        <f>SUM(AL29:AL32)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" s="205" customFormat="1" ht="57">
-      <c r="A26" s="199"/>
-      <c r="B26" s="218" t="str">
+    <row r="29" spans="1:38" s="205" customFormat="1" ht="57">
+      <c r="A29" s="199"/>
+      <c r="B29" s="218" t="str">
         <f>'ONR 4'!B7</f>
         <v>4.1</v>
       </c>
-      <c r="C26" s="218" t="str">
+      <c r="C29" s="218" t="str">
         <f>'ONR 4'!C7</f>
         <v>En respectant l'application des normes communes pour collecter, rassembler, analyser et partager les données sur les impacts des Technologie de l’Information et de la Communication (TIC) .</v>
       </c>
-      <c r="D26" s="223">
+      <c r="D29" s="223">
         <f>'ONR 4'!D7</f>
         <v>0</v>
       </c>
-      <c r="E26" s="267">
+      <c r="E29" s="267">
         <f>'ONR 4'!E7</f>
         <v>0</v>
       </c>
-      <c r="F26" s="274">
+      <c r="F29" s="274">
         <f>'ONR 4'!F7</f>
         <v>0</v>
       </c>
-      <c r="G26" s="200">
+      <c r="G29" s="200">
         <f>'ONR 4'!G7</f>
         <v>0</v>
       </c>
-      <c r="H26" s="202">
+      <c r="H29" s="202">
         <f>'ONR 4'!H7</f>
         <v>0</v>
       </c>
-      <c r="I26" s="225">
+      <c r="I29" s="225">
         <f>'ONR 4'!I7</f>
         <v>0</v>
       </c>
-      <c r="J26" s="218">
-        <f>S26</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="227">
-        <f t="shared" ref="K26:K27" si="79">E26*10+F26</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="227" t="b">
-        <f>OR(K26=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="227" t="b">
-        <f>OR(K26=21,K26=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="227" t="b">
-        <f>OR(K26=22,K26=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="227" t="b">
-        <f>OR(K26=11,K26=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P26" s="227" t="b">
-        <f>OR(K26=23,K26=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="227" t="b">
-        <f>OR(K26=13,K26=14,K26=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="227" t="b">
-        <f>OR(K26=1,K26=2,K26=3,K26=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S26" s="228">
-        <f t="shared" ref="S26:S27" si="80">IF(COUNTA(E26:F26)&lt;2,"",(IF(L26=TRUE,$L$3,IF(M26=TRUE,$M$3,IF(N26=TRUE,$N$3,IF(O26=TRUE,$O$3,IF(P26=TRUE,$P$3,IF(Q26=TRUE,$Q$3,IF(R26=TRUE,$R$3,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="T26" s="226">
-        <f t="shared" ref="T26:T27" si="81">IF(COUNTA(E26:F26)&lt;2,"",(IF(L26=TRUE,6,IF(M26=TRUE,5,IF(N26=TRUE,4,IF(O26=TRUE,3,IF(P26=TRUE,2,IF(Q26=TRUE,1,IF(R26=TRUE,0,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="U26" s="242">
-        <f t="shared" ref="U26:U27" si="82">T26*10+H26</f>
-        <v>0</v>
-      </c>
-      <c r="V26" s="229">
-        <f>G26</f>
-        <v>0</v>
-      </c>
-      <c r="W26" s="203">
+      <c r="J29" s="218">
+        <f>S29</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="227">
+        <f t="shared" ref="K29:K30" si="79">E29*10+F29</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="227" t="b">
+        <f>OR(K29=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="227" t="b">
+        <f>OR(K29=21,K29=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="227" t="b">
+        <f>OR(K29=22,K29=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="227" t="b">
+        <f>OR(K29=11,K29=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="227" t="b">
+        <f>OR(K29=23,K29=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="227" t="b">
+        <f>OR(K29=13,K29=14,K29=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="227" t="b">
+        <f>OR(K29=1,K29=2,K29=3,K29=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S29" s="228">
+        <f t="shared" ref="S29:S30" si="80">IF(COUNTA(E29:F29)&lt;2,"",(IF(L29=TRUE,$L$3,IF(M29=TRUE,$M$3,IF(N29=TRUE,$N$3,IF(O29=TRUE,$O$3,IF(P29=TRUE,$P$3,IF(Q29=TRUE,$Q$3,IF(R29=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T29" s="226">
+        <f t="shared" ref="T29:T30" si="81">IF(COUNTA(E29:F29)&lt;2,"",(IF(L29=TRUE,6,IF(M29=TRUE,5,IF(N29=TRUE,4,IF(O29=TRUE,3,IF(P29=TRUE,2,IF(Q29=TRUE,1,IF(R29=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U29" s="242">
+        <f t="shared" ref="U29:U30" si="82">T29*10+H29</f>
+        <v>0</v>
+      </c>
+      <c r="V29" s="229">
+        <f>G29</f>
+        <v>0</v>
+      </c>
+      <c r="W29" s="203">
         <f>'ONR 4'!V7</f>
         <v>0</v>
       </c>
-      <c r="X26" s="204">
+      <c r="X29" s="204">
         <f>'ONR 4'!W7</f>
         <v>0</v>
       </c>
-      <c r="Y26" s="230">
-        <f>I26</f>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="230">
-        <f>D26</f>
-        <v>0</v>
-      </c>
-      <c r="AE26" s="206">
-        <f>IF(K26=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF26" s="206">
-        <f t="shared" ref="AF26:AL29" si="83">IF(L26=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG26" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AH26" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AI26" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AK26" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AL26" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:38" s="205" customFormat="1" ht="57">
-      <c r="A27" s="199"/>
-      <c r="B27" s="219" t="str">
-        <f>'ONR 4'!B8</f>
-        <v>4.2</v>
-      </c>
-      <c r="C27" s="219" t="str">
-        <f>'ONR 4'!C8</f>
-        <v>En participant à une démarche collaborative de conception et d’évaluation des services numériques en adéquation avec les réels besoins.</v>
-      </c>
-      <c r="D27" s="231">
-        <f>'ONR 4'!D8</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="268">
-        <f>'ONR 4'!E8</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="275">
-        <f>'ONR 4'!F8</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="207">
-        <f>'ONR 4'!G8</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="201">
-        <f>'ONR 4'!H8</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="224">
-        <f>'ONR 4'!I8</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="219">
-        <f t="shared" ref="J27:J35" si="84">S27</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="233">
-        <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="233" t="b">
-        <f t="shared" ref="L27" si="85">OR(K27=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="233" t="b">
-        <f t="shared" ref="M27" si="86">OR(K27=21,K27=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="233" t="b">
-        <f t="shared" ref="N27" si="87">OR(K27=22,K27=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="233" t="b">
-        <f t="shared" ref="O27" si="88">OR(K27=11,K27=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P27" s="233" t="b">
-        <f t="shared" ref="P27" si="89">OR(K27=23,K27=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="233" t="b">
-        <f t="shared" ref="Q27" si="90">OR(K27=13,K27=14,K27=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R27" s="233" t="b">
-        <f t="shared" ref="R27" si="91">OR(K27=1,K27=2,K27=3,K27=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S27" s="234">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="232">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="243">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="235">
-        <f>G27</f>
-        <v>0</v>
-      </c>
-      <c r="W27" s="142">
-        <f>'ONR 4'!V8</f>
-        <v>0</v>
-      </c>
-      <c r="X27" s="204">
-        <f>'ONR 4'!W8</f>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="236">
-        <f>I27</f>
-        <v>0</v>
-      </c>
-      <c r="Z27" s="236">
-        <f>D27</f>
-        <v>0</v>
-      </c>
-      <c r="AE27" s="206">
-        <f>IF(K27=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF27" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AG27" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AH27" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AI27" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AK27" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AL27" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:38" s="205" customFormat="1" ht="57">
-      <c r="A28" s="199"/>
-      <c r="B28" s="219" t="str">
-        <f>'ONR 4'!B9</f>
-        <v>4.3</v>
-      </c>
-      <c r="C28" s="219" t="str">
-        <f>'ONR 4'!C9</f>
-        <v>En restant innovant dans l’utilisation de nouveaux outils numériques et assurer leur analyse d'impact avec transparence et visibilité pour les utilisatuer</v>
-      </c>
-      <c r="D28" s="231">
-        <f>'ONR 4'!D9</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="268">
-        <f>'ONR 4'!E9</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="275">
-        <f>'ONR 4'!F9</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="207">
-        <f>'ONR 4'!G9</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="201">
-        <f>'ONR 4'!H9</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="224">
-        <f>'ONR 4'!I9</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="219">
-        <f t="shared" ref="J28:J29" si="92">S28</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="233">
-        <f t="shared" ref="K28:K29" si="93">E28*10+F28</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="233" t="b">
-        <f t="shared" ref="L28:L29" si="94">OR(K28=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="233" t="b">
-        <f t="shared" ref="M28:M29" si="95">OR(K28=21,K28=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N28" s="233" t="b">
-        <f t="shared" ref="N28:N29" si="96">OR(K28=22,K28=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="233" t="b">
-        <f t="shared" ref="O28:O29" si="97">OR(K28=11,K28=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P28" s="233" t="b">
-        <f t="shared" ref="P28:P29" si="98">OR(K28=23,K28=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="233" t="b">
-        <f t="shared" ref="Q28:Q29" si="99">OR(K28=13,K28=14,K28=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="233" t="b">
-        <f t="shared" ref="R28:R29" si="100">OR(K28=1,K28=2,K28=3,K28=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S28" s="234">
-        <f t="shared" ref="S28:S29" si="101">IF(COUNTA(E28:F28)&lt;2,"",(IF(L28=TRUE,$L$3,IF(M28=TRUE,$M$3,IF(N28=TRUE,$N$3,IF(O28=TRUE,$O$3,IF(P28=TRUE,$P$3,IF(Q28=TRUE,$Q$3,IF(R28=TRUE,$R$3,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="T28" s="232">
-        <f t="shared" ref="T28:T29" si="102">IF(COUNTA(E28:F28)&lt;2,"",(IF(L28=TRUE,6,IF(M28=TRUE,5,IF(N28=TRUE,4,IF(O28=TRUE,3,IF(P28=TRUE,2,IF(Q28=TRUE,1,IF(R28=TRUE,0,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="U28" s="243">
-        <f t="shared" ref="U28:U29" si="103">T28*10+H28</f>
-        <v>0</v>
-      </c>
-      <c r="V28" s="235">
-        <f>G28</f>
-        <v>0</v>
-      </c>
-      <c r="W28" s="142">
-        <f>'ONR 4'!V9</f>
-        <v>0</v>
-      </c>
-      <c r="X28" s="204">
-        <f>'ONR 4'!W9</f>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="236">
-        <f>I28</f>
-        <v>0</v>
-      </c>
-      <c r="Z28" s="236">
-        <f>D28</f>
-        <v>0</v>
-      </c>
-      <c r="AE28" s="206">
-        <f>IF(K28=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF28" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AH28" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AI28" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AK28" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="AL28" s="206">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:38" s="205" customFormat="1" ht="20" thickBot="1">
-      <c r="A29" s="199"/>
-      <c r="B29" s="219" t="str">
-        <f>'ONR 4'!B10</f>
-        <v>4.4</v>
-      </c>
-      <c r="C29" s="219" t="str">
-        <f>'ONR 4'!C10</f>
-        <v>En permettant et en garrantissant plus de souveraineté numérique</v>
-      </c>
-      <c r="D29" s="231">
-        <f>'ONR 4'!D10</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="268">
-        <f>'ONR 4'!E10</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="275">
-        <f>'ONR 4'!F10</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="207">
-        <f>'ONR 4'!G10</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="201">
-        <f>'ONR 4'!H10</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="224">
-        <f>'ONR 4'!I10</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="219">
-        <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="233">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="233" t="b">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="233" t="b">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="233" t="b">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="233" t="b">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="233" t="b">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="233" t="b">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="R29" s="233" t="b">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="234">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="232">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="243">
-        <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="V29" s="235">
-        <f>G29</f>
-        <v>0</v>
-      </c>
-      <c r="W29" s="142">
-        <f>'ONR 4'!V10</f>
-        <v>0</v>
-      </c>
-      <c r="X29" s="204">
-        <f>'ONR 4'!W10</f>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="236">
+      <c r="Y29" s="230">
         <f>I29</f>
         <v>0</v>
       </c>
-      <c r="Z29" s="236">
+      <c r="Z29" s="230">
         <f>D29</f>
         <v>0</v>
       </c>
@@ -19061,7 +19067,7 @@
         <v>1</v>
       </c>
       <c r="AF29" s="206">
-        <f t="shared" si="83"/>
+        <f t="shared" ref="AF29:AL32" si="83">IF(L29=TRUE,1,0)</f>
         <v>0</v>
       </c>
       <c r="AG29" s="206">
@@ -19089,721 +19095,721 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" s="116" customFormat="1" ht="23" thickBot="1">
-      <c r="A30" s="115"/>
-      <c r="B30" s="362" t="str">
+    <row r="30" spans="1:38" s="205" customFormat="1" ht="57">
+      <c r="A30" s="199"/>
+      <c r="B30" s="219" t="str">
+        <f>'ONR 4'!B8</f>
+        <v>4.2</v>
+      </c>
+      <c r="C30" s="219" t="str">
+        <f>'ONR 4'!C8</f>
+        <v>En participant à une démarche collaborative de conception et d’évaluation des services numériques en adéquation avec les réels besoins.</v>
+      </c>
+      <c r="D30" s="231">
+        <f>'ONR 4'!D8</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="268">
+        <f>'ONR 4'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="275">
+        <f>'ONR 4'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="207">
+        <f>'ONR 4'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="201">
+        <f>'ONR 4'!H8</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="224">
+        <f>'ONR 4'!I8</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="219">
+        <f t="shared" ref="J30:J38" si="84">S30</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="233">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="233" t="b">
+        <f t="shared" ref="L33" si="85">OR(K30=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="233" t="b">
+        <f t="shared" ref="M30" si="86">OR(K30=21,K30=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="233" t="b">
+        <f t="shared" ref="N30" si="87">OR(K30=22,K30=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="233" t="b">
+        <f t="shared" ref="O30" si="88">OR(K30=11,K30=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="233" t="b">
+        <f t="shared" ref="P30" si="89">OR(K30=23,K30=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="233" t="b">
+        <f t="shared" ref="Q30" si="90">OR(K30=13,K30=14,K30=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="233" t="b">
+        <f t="shared" ref="R30" si="91">OR(K30=1,K30=2,K30=3,K30=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="234">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="232">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="243">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="235">
+        <f>G30</f>
+        <v>0</v>
+      </c>
+      <c r="W30" s="142">
+        <f>'ONR 4'!V8</f>
+        <v>0</v>
+      </c>
+      <c r="X30" s="204">
+        <f>'ONR 4'!W8</f>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="236">
+        <f>I30</f>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="236">
+        <f>D30</f>
+        <v>0</v>
+      </c>
+      <c r="AE30" s="206">
+        <f>IF(K30=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF30" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AH30" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AI30" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AK30" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AL30" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" s="205" customFormat="1" ht="57">
+      <c r="A31" s="199"/>
+      <c r="B31" s="219" t="str">
+        <f>'ONR 4'!B9</f>
+        <v>4.3</v>
+      </c>
+      <c r="C31" s="219" t="str">
+        <f>'ONR 4'!C9</f>
+        <v>En restant innovant dans l’utilisation de nouveaux outils numériques et assurer leur analyse d'impact avec transparence et visibilité pour les utilisatuer</v>
+      </c>
+      <c r="D31" s="231">
+        <f>'ONR 4'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="268">
+        <f>'ONR 4'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="275">
+        <f>'ONR 4'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="207">
+        <f>'ONR 4'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="201">
+        <f>'ONR 4'!H9</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="224">
+        <f>'ONR 4'!I9</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="219">
+        <f t="shared" ref="J31:J32" si="92">S31</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="233">
+        <f t="shared" ref="K31:K32" si="93">E31*10+F31</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="233" t="b">
+        <f t="shared" ref="L31:L32" si="94">OR(K31=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="233" t="b">
+        <f t="shared" ref="M31:M32" si="95">OR(K31=21,K31=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="233" t="b">
+        <f t="shared" ref="N31:N32" si="96">OR(K31=22,K31=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="233" t="b">
+        <f t="shared" ref="O31:O32" si="97">OR(K31=11,K31=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="233" t="b">
+        <f t="shared" ref="P31:P32" si="98">OR(K31=23,K31=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="233" t="b">
+        <f t="shared" ref="Q31:Q32" si="99">OR(K31=13,K31=14,K31=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R31" s="233" t="b">
+        <f t="shared" ref="R31:R32" si="100">OR(K31=1,K31=2,K31=3,K31=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="234">
+        <f t="shared" ref="S31:S32" si="101">IF(COUNTA(E31:F31)&lt;2,"",(IF(L31=TRUE,$L$3,IF(M31=TRUE,$M$3,IF(N31=TRUE,$N$3,IF(O31=TRUE,$O$3,IF(P31=TRUE,$P$3,IF(Q31=TRUE,$Q$3,IF(R31=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T31" s="232">
+        <f t="shared" ref="T31:T32" si="102">IF(COUNTA(E31:F31)&lt;2,"",(IF(L31=TRUE,6,IF(M31=TRUE,5,IF(N31=TRUE,4,IF(O31=TRUE,3,IF(P31=TRUE,2,IF(Q31=TRUE,1,IF(R31=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U31" s="243">
+        <f t="shared" ref="U31:U32" si="103">T31*10+H31</f>
+        <v>0</v>
+      </c>
+      <c r="V31" s="235">
+        <f>G31</f>
+        <v>0</v>
+      </c>
+      <c r="W31" s="142">
+        <f>'ONR 4'!V9</f>
+        <v>0</v>
+      </c>
+      <c r="X31" s="204">
+        <f>'ONR 4'!W9</f>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="236">
+        <f>I31</f>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="236">
+        <f>D31</f>
+        <v>0</v>
+      </c>
+      <c r="AE31" s="206">
+        <f>IF(K31=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF31" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AG31" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AH31" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AI31" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AK31" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AL31" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" s="205" customFormat="1" ht="20" thickBot="1">
+      <c r="A32" s="199"/>
+      <c r="B32" s="219" t="str">
+        <f>'ONR 4'!B10</f>
+        <v>4.4</v>
+      </c>
+      <c r="C32" s="219" t="str">
+        <f>'ONR 4'!C10</f>
+        <v>En permettant et en garrantissant plus de souveraineté numérique</v>
+      </c>
+      <c r="D32" s="231">
+        <f>'ONR 4'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="268">
+        <f>'ONR 4'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="275">
+        <f>'ONR 4'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="207">
+        <f>'ONR 4'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="201">
+        <f>'ONR 4'!H10</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="224">
+        <f>'ONR 4'!I10</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="219">
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="233">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="233" t="b">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="233" t="b">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="233" t="b">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="233" t="b">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="233" t="b">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="233" t="b">
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="233" t="b">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="234">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="232">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="243">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="235">
+        <f>G32</f>
+        <v>0</v>
+      </c>
+      <c r="W32" s="142">
+        <f>'ONR 4'!V10</f>
+        <v>0</v>
+      </c>
+      <c r="X32" s="204">
+        <f>'ONR 4'!W10</f>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="236">
+        <f>I32</f>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="236">
+        <f>D32</f>
+        <v>0</v>
+      </c>
+      <c r="AE32" s="206">
+        <f>IF(K32=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF32" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AG32" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AH32" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AI32" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AK32" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="AL32" s="206">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" s="116" customFormat="1" ht="23" thickBot="1">
+      <c r="A33" s="115"/>
+      <c r="B33" s="362" t="str">
         <f>'ONR 5'!B2:C2</f>
         <v>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
       </c>
-      <c r="C30" s="363"/>
-      <c r="D30" s="363"/>
-      <c r="E30" s="363"/>
-      <c r="F30" s="363"/>
-      <c r="G30" s="363"/>
-      <c r="H30" s="363"/>
-      <c r="I30" s="363"/>
-      <c r="J30" s="363"/>
-      <c r="K30" s="363"/>
-      <c r="L30" s="363"/>
-      <c r="M30" s="363"/>
-      <c r="N30" s="363"/>
-      <c r="O30" s="363"/>
-      <c r="P30" s="363"/>
-      <c r="Q30" s="363"/>
-      <c r="R30" s="363"/>
-      <c r="S30" s="363"/>
-      <c r="T30" s="363"/>
-      <c r="U30" s="363"/>
-      <c r="V30" s="363"/>
-      <c r="W30" s="363"/>
-      <c r="X30" s="363"/>
-      <c r="Y30" s="363"/>
-      <c r="Z30" s="364"/>
-      <c r="AB30" s="116" t="str">
-        <f>B30</f>
+      <c r="C33" s="363"/>
+      <c r="D33" s="363"/>
+      <c r="E33" s="363"/>
+      <c r="F33" s="363"/>
+      <c r="G33" s="363"/>
+      <c r="H33" s="363"/>
+      <c r="I33" s="363"/>
+      <c r="J33" s="363"/>
+      <c r="K33" s="363"/>
+      <c r="L33" s="363"/>
+      <c r="M33" s="363"/>
+      <c r="N33" s="363"/>
+      <c r="O33" s="363"/>
+      <c r="P33" s="363"/>
+      <c r="Q33" s="363"/>
+      <c r="R33" s="363"/>
+      <c r="S33" s="363"/>
+      <c r="T33" s="363"/>
+      <c r="U33" s="363"/>
+      <c r="V33" s="363"/>
+      <c r="W33" s="363"/>
+      <c r="X33" s="363"/>
+      <c r="Y33" s="363"/>
+      <c r="Z33" s="364"/>
+      <c r="AB33" s="116" t="str">
+        <f>B33</f>
         <v>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
       </c>
-      <c r="AC30" s="116">
-        <f>SUMPRODUCT(--(B31:B36&lt;&gt;""))</f>
+      <c r="AC33" s="116">
+        <f>SUMPRODUCT(--(B34:B40&lt;&gt;""))</f>
         <v>6</v>
       </c>
-      <c r="AD30" s="116">
-        <f>AC30-AE30</f>
-        <v>0</v>
-      </c>
-      <c r="AE30" s="117">
-        <f>SUM(AE31:AE36)</f>
+      <c r="AD33" s="116">
+        <f>AC33-AE33</f>
+        <v>0</v>
+      </c>
+      <c r="AE33" s="117">
+        <f>SUM(AE34:AE40)</f>
         <v>6</v>
       </c>
-      <c r="AF30" s="117">
-        <f t="shared" ref="AF30:AL30" si="104">SUM(AF31:AF36)</f>
-        <v>0</v>
-      </c>
-      <c r="AG30" s="117">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="AH30" s="117">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="AI30" s="117">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="117">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="AK30" s="117">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="AL30" s="117">
-        <f t="shared" si="104"/>
+      <c r="AF33" s="117">
+        <f>SUM(AF34:AF40)</f>
+        <v>0</v>
+      </c>
+      <c r="AG33" s="117">
+        <f>SUM(AG34:AG40)</f>
+        <v>0</v>
+      </c>
+      <c r="AH33" s="117">
+        <f>SUM(AH34:AH40)</f>
+        <v>0</v>
+      </c>
+      <c r="AI33" s="117">
+        <f>SUM(AI34:AI40)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="117">
+        <f>SUM(AJ34:AJ40)</f>
+        <v>0</v>
+      </c>
+      <c r="AK33" s="117">
+        <f>SUM(AK34:AK40)</f>
+        <v>0</v>
+      </c>
+      <c r="AL33" s="117">
+        <f>SUM(AL34:AL40)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" s="205" customFormat="1" ht="38">
-      <c r="A31" s="199"/>
-      <c r="B31" s="218" t="str">
+    <row r="34" spans="1:38" s="205" customFormat="1" ht="38">
+      <c r="A34" s="199"/>
+      <c r="B34" s="218" t="str">
         <f>'ONR 5'!B7</f>
         <v>5.1</v>
       </c>
-      <c r="C31" s="218" t="str">
+      <c r="C34" s="218" t="str">
         <f>'ONR 5'!C7</f>
         <v>En incluant l’innovation sociale dans la définition de nouveaux systèmes et services numériques.</v>
       </c>
-      <c r="D31" s="223">
+      <c r="D34" s="223">
         <f>'ONR 5'!D7</f>
         <v>0</v>
       </c>
-      <c r="E31" s="272">
+      <c r="E34" s="272">
         <f>'ONR 5'!E7</f>
         <v>0</v>
       </c>
-      <c r="F31" s="279">
+      <c r="F34" s="279">
         <f>'ONR 5'!F7</f>
         <v>0</v>
       </c>
-      <c r="G31" s="200">
+      <c r="G34" s="200">
         <f>'ONR 5'!G7</f>
         <v>0</v>
       </c>
-      <c r="H31" s="216">
+      <c r="H34" s="216">
         <f>'ONR 5'!H7</f>
         <v>0</v>
       </c>
-      <c r="I31" s="225">
+      <c r="I34" s="225">
         <f>'ONR 5'!I7</f>
         <v>0</v>
       </c>
-      <c r="J31" s="220">
+      <c r="J34" s="220">
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="K31" s="227">
-        <f t="shared" ref="K31:K35" si="105">E31*10+F31</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="227" t="b">
-        <f>OR(K31=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="227" t="b">
-        <f>OR(K31=21,K31=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N31" s="227" t="b">
-        <f>OR(K31=22,K31=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O31" s="227" t="b">
-        <f>OR(K31=11,K31=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="227" t="b">
-        <f>OR(K31=23,K31=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="227" t="b">
-        <f>OR(K31=13,K31=14,K31=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="227" t="b">
-        <f>OR(K31=1,K31=2,K31=3,K31=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S31" s="228">
-        <f t="shared" ref="S31:S35" si="106">IF(COUNTA(E31:F31)&lt;2,"",(IF(L31=TRUE,$L$3,IF(M31=TRUE,$M$3,IF(N31=TRUE,$N$3,IF(O31=TRUE,$O$3,IF(P31=TRUE,$P$3,IF(Q31=TRUE,$Q$3,IF(R31=TRUE,$R$3,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="T31" s="226">
-        <f t="shared" ref="T31:T35" si="107">IF(COUNTA(E31:F31)&lt;2,"",(IF(L31=TRUE,6,IF(M31=TRUE,5,IF(N31=TRUE,4,IF(O31=TRUE,3,IF(P31=TRUE,2,IF(Q31=TRUE,1,IF(R31=TRUE,0,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="U31" s="242">
-        <f t="shared" ref="U31:U35" si="108">T31*10+H31</f>
-        <v>0</v>
-      </c>
-      <c r="V31" s="229">
-        <f t="shared" ref="V31:V35" si="109">G31</f>
-        <v>0</v>
-      </c>
-      <c r="W31" s="203">
+      <c r="K37" s="227">
+        <f t="shared" ref="K37:K38" si="105">E34*10+F34</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="227" t="b">
+        <f>OR(K34=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="227" t="b">
+        <f>OR(K34=21,K34=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="227" t="b">
+        <f>OR(K34=22,K34=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="227" t="b">
+        <f>OR(K34=11,K34=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="227" t="b">
+        <f>OR(K34=23,K34=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="227" t="b">
+        <f>OR(K34=13,K34=14,K34=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="227" t="b">
+        <f>OR(K34=1,K34=2,K34=3,K34=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S34" s="228">
+        <f t="shared" ref="S34:S38" si="106">IF(COUNTA(E34:F34)&lt;2,"",(IF(L34=TRUE,$L$3,IF(M34=TRUE,$M$3,IF(N34=TRUE,$N$3,IF(O34=TRUE,$O$3,IF(P34=TRUE,$P$3,IF(Q34=TRUE,$Q$3,IF(R34=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T34" s="226">
+        <f t="shared" ref="T34:T38" si="107">IF(COUNTA(E34:F34)&lt;2,"",(IF(L34=TRUE,6,IF(M34=TRUE,5,IF(N34=TRUE,4,IF(O34=TRUE,3,IF(P34=TRUE,2,IF(Q34=TRUE,1,IF(R34=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U34" s="242">
+        <f t="shared" ref="U34:U38" si="108">T34*10+H34</f>
+        <v>0</v>
+      </c>
+      <c r="V34" s="229">
+        <f t="shared" ref="V34:V38" si="109">G34</f>
+        <v>0</v>
+      </c>
+      <c r="W34" s="203">
         <f>'ONR 5'!V7</f>
         <v>0</v>
       </c>
-      <c r="X31" s="204">
+      <c r="X34" s="204">
         <f>'ONR 5'!W7</f>
         <v>0</v>
       </c>
-      <c r="Y31" s="257">
-        <f t="shared" ref="Y31:Y35" si="110">I31</f>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="256">
-        <f>D31</f>
-        <v>0</v>
-      </c>
-      <c r="AE31" s="206">
-        <f t="shared" ref="AE31:AE35" si="111">IF(K31=0,1,0)</f>
+      <c r="Y34" s="257">
+        <f t="shared" ref="Y34:Y38" si="110">I34</f>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="256">
+        <f>D34</f>
+        <v>0</v>
+      </c>
+      <c r="AE34" s="206">
+        <f t="shared" ref="AE34:AE38" si="111">IF(K34=0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AF31" s="206">
-        <f t="shared" ref="AF31:AF35" si="112">IF(L31=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="206">
-        <f t="shared" ref="AG31:AG35" si="113">IF(M31=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AH31" s="206">
-        <f t="shared" ref="AH31:AH35" si="114">IF(N31=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI31" s="206">
-        <f t="shared" ref="AI31:AI35" si="115">IF(O31=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="206">
-        <f t="shared" ref="AJ31:AJ35" si="116">IF(P31=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AK31" s="206">
-        <f t="shared" ref="AK31:AK35" si="117">IF(Q31=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL31" s="206">
-        <f t="shared" ref="AL31:AL35" si="118">IF(R31=TRUE,1,0)</f>
+      <c r="AF34" s="206">
+        <f t="shared" ref="AF34:AF38" si="112">IF(L34=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG34" s="206">
+        <f t="shared" ref="AG34:AG38" si="113">IF(M34=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH34" s="206">
+        <f t="shared" ref="AH34:AH38" si="114">IF(N34=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI34" s="206">
+        <f t="shared" ref="AI34:AI38" si="115">IF(O34=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="206">
+        <f t="shared" ref="AJ34:AJ38" si="116">IF(P34=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK34" s="206">
+        <f t="shared" ref="AK34:AK38" si="117">IF(Q34=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL34" s="206">
+        <f t="shared" ref="AL34:AL38" si="118">IF(R34=TRUE,1,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" s="205" customFormat="1" ht="38">
-      <c r="A32" s="199"/>
-      <c r="B32" s="219" t="str">
+    <row r="35" spans="1:38" s="205" customFormat="1" ht="38">
+      <c r="A35" s="199"/>
+      <c r="B35" s="219" t="str">
         <f>'ONR 5'!B8</f>
         <v>5.2</v>
       </c>
-      <c r="C32" s="218" t="str">
+      <c r="C35" s="218" t="str">
         <f>'ONR 5'!C8</f>
         <v>En valorisant les initiatives internes qui mobilisent l’organisation, favorisent les collaborations transversales et le bien-être au travail.</v>
       </c>
-      <c r="D32" s="231">
+      <c r="D35" s="231">
         <f>'ONR 5'!D8</f>
         <v>0</v>
       </c>
-      <c r="E32" s="272">
+      <c r="E35" s="272">
         <f>'ONR 5'!E8</f>
         <v>0</v>
       </c>
-      <c r="F32" s="279">
+      <c r="F35" s="279">
         <f>'ONR 5'!F8</f>
         <v>0</v>
       </c>
-      <c r="G32" s="207">
+      <c r="G35" s="207">
         <f>'ONR 5'!G8</f>
         <v>0</v>
       </c>
-      <c r="H32" s="216">
+      <c r="H35" s="216">
         <f>'ONR 5'!H8</f>
         <v>0</v>
       </c>
-      <c r="I32" s="224">
+      <c r="I35" s="224">
         <f>'ONR 5'!I8</f>
         <v>0</v>
       </c>
-      <c r="J32" s="220">
+      <c r="J35" s="220">
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="K32" s="233">
+      <c r="K38" s="233">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="L32" s="233" t="b">
-        <f t="shared" ref="L32:L35" si="119">OR(K32=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="233" t="b">
-        <f t="shared" ref="M32:M35" si="120">OR(K32=21,K32=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N32" s="233" t="b">
-        <f t="shared" ref="N32:N35" si="121">OR(K32=22,K32=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O32" s="233" t="b">
-        <f t="shared" ref="O32:O35" si="122">OR(K32=11,K32=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="233" t="b">
-        <f t="shared" ref="P32:P35" si="123">OR(K32=23,K32=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="233" t="b">
-        <f t="shared" ref="Q32:Q35" si="124">OR(K32=13,K32=14,K32=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="233" t="b">
-        <f t="shared" ref="R32:R35" si="125">OR(K32=1,K32=2,K32=3,K32=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S32" s="234">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="T32" s="232">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="243">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="V32" s="235">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="142">
-        <f>'ONR 5'!V8</f>
-        <v>0</v>
-      </c>
-      <c r="X32" s="204">
-        <f>'ONR 5'!W8</f>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="258">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="Z32" s="256">
-        <f t="shared" ref="Z32:Z35" si="126">D32</f>
-        <v>0</v>
-      </c>
-      <c r="AE32" s="206">
-        <f t="shared" si="111"/>
-        <v>1</v>
-      </c>
-      <c r="AF32" s="206">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="AG32" s="206">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="AH32" s="206">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="AI32" s="206">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="206">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="AK32" s="206">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="AL32" s="206">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:38" s="205" customFormat="1" ht="38">
-      <c r="A33" s="199"/>
-      <c r="B33" s="219" t="str">
-        <f>'ONR 5'!B9</f>
-        <v>5.3</v>
-      </c>
-      <c r="C33" s="218" t="str">
-        <f>'ONR 5'!C9</f>
-        <v>En sollicitant l’engagement et l’expertise des parties prenantes (sur les sujets environnementaux, sociaux et sociétaux)</v>
-      </c>
-      <c r="D33" s="231">
-        <f>'ONR 5'!D9</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="272">
-        <f>'ONR 5'!E9</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="279">
-        <f>'ONR 5'!F9</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="207">
-        <f>'ONR 5'!G9</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="216">
-        <f>'ONR 5'!H9</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="224">
-        <f>'ONR 5'!I9</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="220">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="233">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="233" t="b">
-        <f t="shared" si="119"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="233" t="b">
-        <f t="shared" si="120"/>
-        <v>0</v>
-      </c>
-      <c r="N33" s="233" t="b">
-        <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O33" s="233" t="b">
-        <f t="shared" si="122"/>
-        <v>0</v>
-      </c>
-      <c r="P33" s="233" t="b">
-        <f t="shared" si="123"/>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="233" t="b">
-        <f t="shared" si="124"/>
-        <v>0</v>
-      </c>
-      <c r="R33" s="233" t="b">
-        <f t="shared" si="125"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="234">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="T33" s="232">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="243">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="V33" s="235">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="142">
-        <f>'ONR 5'!V9</f>
-        <v>0</v>
-      </c>
-      <c r="X33" s="204">
-        <f>'ONR 5'!W9</f>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="258">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="Z33" s="256">
-        <f t="shared" si="126"/>
-        <v>0</v>
-      </c>
-      <c r="AE33" s="206">
-        <f t="shared" si="111"/>
-        <v>1</v>
-      </c>
-      <c r="AF33" s="206">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="AG33" s="206">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="AH33" s="206">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="AI33" s="206">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="206">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="AK33" s="206">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="AL33" s="206">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:38" s="205" customFormat="1" ht="57">
-      <c r="A34" s="199"/>
-      <c r="B34" s="219" t="str">
-        <f>'ONR 5'!B10</f>
-        <v>5.4</v>
-      </c>
-      <c r="C34" s="218" t="str">
-        <f>'ONR 5'!C10</f>
-        <v>En permettant aux générations futures d’innover pour construire un monde ouvert à l’autre soucieux de l’équilibre des écosystèmes et du bien-vivre ensemble.</v>
-      </c>
-      <c r="D34" s="231">
-        <f>'ONR 5'!D10</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="272">
-        <f>'ONR 5'!E10</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="279">
-        <f>'ONR 5'!F10</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="207">
-        <f>'ONR 5'!G10</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="216">
-        <f>'ONR 5'!H10</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="224">
-        <f>'ONR 5'!I10</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="220">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="233">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="233" t="b">
-        <f t="shared" si="119"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="233" t="b">
-        <f t="shared" si="120"/>
-        <v>0</v>
-      </c>
-      <c r="N34" s="233" t="b">
-        <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="233" t="b">
-        <f t="shared" si="122"/>
-        <v>0</v>
-      </c>
-      <c r="P34" s="233" t="b">
-        <f t="shared" si="123"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="233" t="b">
-        <f t="shared" si="124"/>
-        <v>0</v>
-      </c>
-      <c r="R34" s="233" t="b">
-        <f t="shared" si="125"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="234">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="T34" s="232">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-      <c r="U34" s="243">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="V34" s="235">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="W34" s="142">
-        <f>'ONR 5'!V10</f>
-        <v>0</v>
-      </c>
-      <c r="X34" s="204">
-        <f>'ONR 5'!W10</f>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="258">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="Z34" s="256">
-        <f t="shared" si="126"/>
-        <v>0</v>
-      </c>
-      <c r="AE34" s="206">
-        <f t="shared" si="111"/>
-        <v>1</v>
-      </c>
-      <c r="AF34" s="206">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="AG34" s="206">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="AH34" s="206">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="AI34" s="206">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="206">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="AK34" s="206">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="AL34" s="206">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:38" s="205" customFormat="1" ht="19">
-      <c r="A35" s="199"/>
-      <c r="B35" s="219" t="str">
-        <f>'ONR 5'!B11</f>
-        <v>5.5</v>
-      </c>
-      <c r="C35" s="218" t="str">
-        <f>'ONR 5'!C11</f>
-        <v>En suivant les indicateurs de performances et de conformité</v>
-      </c>
-      <c r="D35" s="231">
-        <f>'ONR 5'!D11</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="268">
-        <f>'ONR 5'!E11</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="275">
-        <f>'ONR 5'!F11</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="207">
-        <f>'ONR 5'!G11</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="201">
-        <f>'ONR 5'!H11</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="224">
-        <f>'ONR 5'!I11</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="219">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="233">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="233" t="b">
-        <f t="shared" si="119"/>
+      <c r="L38" s="233" t="b">
+        <f t="shared" ref="L38:L38" si="119">OR(K35=31)</f>
         <v>0</v>
       </c>
       <c r="M35" s="233" t="b">
-        <f t="shared" si="120"/>
+        <f t="shared" ref="M35:M38" si="120">OR(K35=21,K35=32)</f>
         <v>0</v>
       </c>
       <c r="N35" s="233" t="b">
-        <f t="shared" si="121"/>
+        <f t="shared" ref="N35:N38" si="121">OR(K35=22,K35=33)</f>
         <v>0</v>
       </c>
       <c r="O35" s="233" t="b">
-        <f t="shared" si="122"/>
+        <f t="shared" ref="O35:O38" si="122">OR(K35=11,K35=12)</f>
         <v>0</v>
       </c>
       <c r="P35" s="233" t="b">
-        <f t="shared" si="123"/>
+        <f t="shared" ref="P35:P38" si="123">OR(K35=23,K35=34)</f>
         <v>0</v>
       </c>
       <c r="Q35" s="233" t="b">
-        <f t="shared" si="124"/>
+        <f t="shared" ref="Q35:Q38" si="124">OR(K35=13,K35=14,K35=24)</f>
         <v>0</v>
       </c>
       <c r="R35" s="233" t="b">
-        <f t="shared" si="125"/>
+        <f t="shared" ref="R35:R38" si="125">OR(K35=1,K35=2,K35=3,K35=4)</f>
         <v>0</v>
       </c>
       <c r="S35" s="234">
         <f t="shared" si="106"/>
         <v>0</v>
       </c>
-      <c r="T35" s="232">
+      <c r="T38" s="232">
         <f t="shared" si="107"/>
         <v>0</v>
       </c>
-      <c r="U35" s="243">
+      <c r="U38" s="243">
         <f t="shared" si="108"/>
         <v>0</v>
       </c>
-      <c r="V35" s="235">
+      <c r="V38" s="235">
         <f t="shared" si="109"/>
         <v>0</v>
       </c>
-      <c r="W35" s="142">
-        <f>'ONR 5'!V11</f>
+      <c r="W38" s="142">
+        <f>'ONR 5'!V8</f>
         <v>0</v>
       </c>
       <c r="X35" s="204">
-        <f>'ONR 5'!W11</f>
+        <f>'ONR 5'!W8</f>
         <v>0</v>
       </c>
       <c r="Y35" s="258">
         <f t="shared" si="110"/>
         <v>0</v>
       </c>
-      <c r="Z35" s="236">
-        <f t="shared" si="126"/>
+      <c r="Z38" s="256">
+        <f t="shared" ref="Z38:Z38" si="126">D35</f>
         <v>0</v>
       </c>
       <c r="AE35" s="206">
@@ -19839,152 +19845,691 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" ht="38">
+    <row r="36" spans="1:38" s="205" customFormat="1" ht="38">
+      <c r="A36" s="199"/>
       <c r="B36" s="219" t="str">
+        <f>'ONR 5'!B9</f>
+        <v>5.3</v>
+      </c>
+      <c r="C36" s="218" t="str">
+        <f>'ONR 5'!C9</f>
+        <v>En sollicitant l’engagement et l’expertise des parties prenantes (sur les sujets environnementaux, sociaux et sociétaux)</v>
+      </c>
+      <c r="D36" s="231">
+        <f>'ONR 5'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="272">
+        <f>'ONR 5'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="279">
+        <f>'ONR 5'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="207">
+        <f>'ONR 5'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="216">
+        <f>'ONR 5'!H9</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="224">
+        <f>'ONR 5'!I9</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="220">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="233">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="233" t="b">
+        <f t="shared" si="119"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="233" t="b">
+        <f t="shared" si="120"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="233" t="b">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="O39" s="233" t="b">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="233" t="b">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="233" t="b">
+        <f t="shared" si="124"/>
+        <v>0</v>
+      </c>
+      <c r="R39" s="233" t="b">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="234">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="232">
+        <f t="shared" si="107"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="243">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="V39" s="235">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="142">
+        <f>'ONR 5'!V9</f>
+        <v>0</v>
+      </c>
+      <c r="X36" s="204">
+        <f>'ONR 5'!W9</f>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="258">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="256">
+        <f t="shared" si="126"/>
+        <v>0</v>
+      </c>
+      <c r="AE36" s="206">
+        <f t="shared" si="111"/>
+        <v>1</v>
+      </c>
+      <c r="AF36" s="206">
+        <f t="shared" si="112"/>
+        <v>0</v>
+      </c>
+      <c r="AG36" s="206">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AH36" s="206">
+        <f t="shared" si="114"/>
+        <v>0</v>
+      </c>
+      <c r="AI36" s="206">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="206">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="AK36" s="206">
+        <f t="shared" si="117"/>
+        <v>0</v>
+      </c>
+      <c r="AL36" s="206">
+        <f t="shared" si="118"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" s="205" customFormat="1" ht="57">
+      <c r="A37" s="199"/>
+      <c r="B37" s="219" t="str">
+        <f>'ONR 5'!B10</f>
+        <v>5.4</v>
+      </c>
+      <c r="C37" s="218" t="str">
+        <f>'ONR 5'!C10</f>
+        <v>En permettant aux générations futures d’innover pour construire un monde ouvert à l’autre soucieux de l’équilibre des écosystèmes et du bien-vivre ensemble.</v>
+      </c>
+      <c r="D37" s="231">
+        <f>'ONR 5'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="272">
+        <f>'ONR 5'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="279">
+        <f>'ONR 5'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="207">
+        <f>'ONR 5'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="216">
+        <f>'ONR 5'!H10</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="224">
+        <f>'ONR 5'!I10</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="220">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="233">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="233" t="b">
+        <f t="shared" si="119"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="233" t="b">
+        <f t="shared" si="120"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="233" t="b">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="233" t="b">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="233" t="b">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="233" t="b">
+        <f t="shared" si="124"/>
+        <v>0</v>
+      </c>
+      <c r="R37" s="233" t="b">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="234">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="232">
+        <f t="shared" si="107"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="243">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="235">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="142">
+        <f>'ONR 5'!V10</f>
+        <v>0</v>
+      </c>
+      <c r="X37" s="204">
+        <f>'ONR 5'!W10</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="258">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="256">
+        <f t="shared" si="126"/>
+        <v>0</v>
+      </c>
+      <c r="AE37" s="206">
+        <f t="shared" si="111"/>
+        <v>1</v>
+      </c>
+      <c r="AF37" s="206">
+        <f t="shared" si="112"/>
+        <v>0</v>
+      </c>
+      <c r="AG37" s="206">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AH37" s="206">
+        <f t="shared" si="114"/>
+        <v>0</v>
+      </c>
+      <c r="AI37" s="206">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="206">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="AK37" s="206">
+        <f t="shared" si="117"/>
+        <v>0</v>
+      </c>
+      <c r="AL37" s="206">
+        <f t="shared" si="118"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" s="205" customFormat="1" ht="19">
+      <c r="A38" s="199"/>
+      <c r="B38" s="219" t="str">
+        <f>'ONR 5'!B11</f>
+        <v>5.5</v>
+      </c>
+      <c r="C38" s="218" t="str">
+        <f>'ONR 5'!C11</f>
+        <v>En suivant les indicateurs de performances et de conformité</v>
+      </c>
+      <c r="D38" s="231">
+        <f>'ONR 5'!D11</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="268">
+        <f>'ONR 5'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="275">
+        <f>'ONR 5'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="207">
+        <f>'ONR 5'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="201">
+        <f>'ONR 5'!H11</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="224">
+        <f>'ONR 5'!I11</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="219">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="233">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="233" t="b">
+        <f t="shared" si="119"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="233" t="b">
+        <f t="shared" si="120"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="233" t="b">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="233" t="b">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="233" t="b">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="233" t="b">
+        <f t="shared" si="124"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="233" t="b">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="234">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="232">
+        <f t="shared" si="107"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="243">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="235">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="W38" s="142">
+        <f>'ONR 5'!V11</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="204">
+        <f>'ONR 5'!W11</f>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="258">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="236">
+        <f t="shared" si="126"/>
+        <v>0</v>
+      </c>
+      <c r="AE38" s="206">
+        <f t="shared" si="111"/>
+        <v>1</v>
+      </c>
+      <c r="AF38" s="206">
+        <f t="shared" si="112"/>
+        <v>0</v>
+      </c>
+      <c r="AG38" s="206">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AH38" s="206">
+        <f t="shared" si="114"/>
+        <v>0</v>
+      </c>
+      <c r="AI38" s="206">
+        <f t="shared" si="115"/>
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="206">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="AK38" s="206">
+        <f t="shared" si="117"/>
+        <v>0</v>
+      </c>
+      <c r="AL38" s="206">
+        <f t="shared" si="118"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38" ht="38">
+      <c r="B39" s="219" t="str">
         <f>'ONR 5'!B12</f>
         <v>5.6</v>
       </c>
-      <c r="C36" s="218" t="str">
+      <c r="C39" s="218" t="str">
         <f>'ONR 5'!C12</f>
         <v>En proposant des axes d’amélioration et d'innovation autour du NR ( y compris s'ils ne sont pas numériques )</v>
       </c>
-      <c r="D36" s="231">
+      <c r="D39" s="231">
         <f>'ONR 5'!D12</f>
         <v>0</v>
       </c>
-      <c r="E36" s="268">
+      <c r="E39" s="268">
         <f>'ONR 5'!E12</f>
         <v>0</v>
       </c>
-      <c r="F36" s="275">
+      <c r="F39" s="275">
         <f>'ONR 5'!F12</f>
         <v>0</v>
       </c>
-      <c r="G36" s="207">
+      <c r="G39" s="207">
         <f>'ONR 5'!G12</f>
         <v>0</v>
       </c>
-      <c r="H36" s="201">
+      <c r="H39" s="201">
         <f>'ONR 5'!H12</f>
         <v>0</v>
       </c>
-      <c r="I36" s="224">
+      <c r="I39" s="224">
         <f>'ONR 5'!I12</f>
         <v>0</v>
       </c>
-      <c r="J36" s="219">
-        <f t="shared" ref="J36" si="127">S36</f>
-        <v>0</v>
-      </c>
-      <c r="K36" s="233">
-        <f t="shared" ref="K36" si="128">E36*10+F36</f>
-        <v>0</v>
-      </c>
-      <c r="L36" s="233" t="b">
-        <f t="shared" ref="L36" si="129">OR(K36=31)</f>
-        <v>0</v>
-      </c>
-      <c r="M36" s="233" t="b">
-        <f t="shared" ref="M36" si="130">OR(K36=21,K36=32)</f>
-        <v>0</v>
-      </c>
-      <c r="N36" s="233" t="b">
-        <f t="shared" ref="N36" si="131">OR(K36=22,K36=33)</f>
-        <v>0</v>
-      </c>
-      <c r="O36" s="233" t="b">
-        <f t="shared" ref="O36" si="132">OR(K36=11,K36=12)</f>
-        <v>0</v>
-      </c>
-      <c r="P36" s="233" t="b">
-        <f t="shared" ref="P36" si="133">OR(K36=23,K36=34)</f>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="233" t="b">
-        <f t="shared" ref="Q36" si="134">OR(K36=13,K36=14,K36=24)</f>
-        <v>0</v>
-      </c>
-      <c r="R36" s="233" t="b">
-        <f t="shared" ref="R36" si="135">OR(K36=1,K36=2,K36=3,K36=4)</f>
-        <v>0</v>
-      </c>
-      <c r="S36" s="234">
-        <f t="shared" ref="S36" si="136">IF(COUNTA(E36:F36)&lt;2,"",(IF(L36=TRUE,$L$3,IF(M36=TRUE,$M$3,IF(N36=TRUE,$N$3,IF(O36=TRUE,$O$3,IF(P36=TRUE,$P$3,IF(Q36=TRUE,$Q$3,IF(R36=TRUE,$R$3,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="T36" s="232">
-        <f t="shared" ref="T36" si="137">IF(COUNTA(E36:F36)&lt;2,"",(IF(L36=TRUE,6,IF(M36=TRUE,5,IF(N36=TRUE,4,IF(O36=TRUE,3,IF(P36=TRUE,2,IF(Q36=TRUE,1,IF(R36=TRUE,0,0)))))))))</f>
-        <v>0</v>
-      </c>
-      <c r="U36" s="243">
-        <f t="shared" ref="U36" si="138">T36*10+H36</f>
-        <v>0</v>
-      </c>
-      <c r="V36" s="235">
-        <f t="shared" ref="V36" si="139">G36</f>
-        <v>0</v>
-      </c>
-      <c r="W36" s="142">
+      <c r="J39" s="219">
+        <f t="shared" ref="J39" si="127">S39</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="233">
+        <f t="shared" ref="K39" si="128">E39*10+F39</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="233" t="b">
+        <f t="shared" ref="L39" si="129">OR(K39=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="233" t="b">
+        <f t="shared" ref="M39" si="130">OR(K39=21,K39=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="233" t="b">
+        <f t="shared" ref="N39" si="131">OR(K39=22,K39=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O39" s="233" t="b">
+        <f t="shared" ref="O39" si="132">OR(K39=11,K39=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="233" t="b">
+        <f t="shared" ref="P39" si="133">OR(K39=23,K39=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="233" t="b">
+        <f t="shared" ref="Q39" si="134">OR(K39=13,K39=14,K39=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R39" s="233" t="b">
+        <f t="shared" ref="R39" si="135">OR(K39=1,K39=2,K39=3,K39=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S39" s="234">
+        <f t="shared" ref="S39" si="136">IF(COUNTA(E39:F39)&lt;2,"",(IF(L39=TRUE,$L$3,IF(M39=TRUE,$M$3,IF(N39=TRUE,$N$3,IF(O39=TRUE,$O$3,IF(P39=TRUE,$P$3,IF(Q39=TRUE,$Q$3,IF(R39=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T39" s="232">
+        <f t="shared" ref="T39" si="137">IF(COUNTA(E39:F39)&lt;2,"",(IF(L39=TRUE,6,IF(M39=TRUE,5,IF(N39=TRUE,4,IF(O39=TRUE,3,IF(P39=TRUE,2,IF(Q39=TRUE,1,IF(R39=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U39" s="243">
+        <f t="shared" ref="U39" si="138">T39*10+H39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="235">
+        <f t="shared" ref="V39" si="139">G39</f>
+        <v>0</v>
+      </c>
+      <c r="W39" s="142">
         <f>'ONR 5'!V12</f>
         <v>0</v>
       </c>
-      <c r="X36" s="204">
+      <c r="X39" s="204">
         <f>'ONR 5'!W12</f>
         <v>0</v>
       </c>
-      <c r="Y36" s="258">
-        <f t="shared" ref="Y36" si="140">I36</f>
-        <v>0</v>
-      </c>
-      <c r="Z36" s="236">
-        <f t="shared" ref="Z36" si="141">D36</f>
-        <v>0</v>
-      </c>
-      <c r="AE36" s="206">
-        <f t="shared" ref="AE36" si="142">IF(K36=0,1,0)</f>
+      <c r="Y39" s="258">
+        <f t="shared" ref="Y39" si="140">I39</f>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="236">
+        <f t="shared" ref="Z39" si="141">D39</f>
+        <v>0</v>
+      </c>
+      <c r="AE39" s="206">
+        <f t="shared" ref="AE39" si="142">IF(K39=0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AF36" s="206">
-        <f t="shared" ref="AF36" si="143">IF(L36=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG36" s="206">
-        <f t="shared" ref="AG36" si="144">IF(M36=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AH36" s="206">
-        <f t="shared" ref="AH36" si="145">IF(N36=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI36" s="206">
-        <f t="shared" ref="AI36" si="146">IF(O36=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="206">
-        <f t="shared" ref="AJ36" si="147">IF(P36=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AK36" s="206">
-        <f t="shared" ref="AK36" si="148">IF(Q36=TRUE,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL36" s="206">
-        <f t="shared" ref="AL36" si="149">IF(R36=TRUE,1,0)</f>
+      <c r="AF39" s="206">
+        <f t="shared" ref="AF39" si="143">IF(L39=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG39" s="206">
+        <f t="shared" ref="AG39" si="144">IF(M39=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH39" s="206">
+        <f t="shared" ref="AH39" si="145">IF(N39=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI39" s="206">
+        <f t="shared" ref="AI39" si="146">IF(O39=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="206">
+        <f t="shared" ref="AJ39" si="147">IF(P39=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK39" s="206">
+        <f t="shared" ref="AK39" si="148">IF(Q39=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL39" s="206">
+        <f t="shared" ref="AL39" si="149">IF(R39=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38" ht="38">
+      <c r="B40" s="219" t="str">
+        <f>'ONR 5'!B13</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="218" t="str">
+        <f>'ONR 5'!C13</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="231">
+        <f>'ONR 5'!D13</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="268">
+        <f>'ONR 5'!E13</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="275">
+        <f>'ONR 5'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="207">
+        <f>'ONR 5'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="201">
+        <f>'ONR 5'!H13</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="224">
+        <f>'ONR 5'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="219">
+        <f>S40</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="233">
+        <f>E40*10+F40</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="233" t="b">
+        <f>OR(K40=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="233" t="b">
+        <f>OR(K40=21,K40=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="233" t="b">
+        <f>OR(K40=22,K40=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O40" s="233" t="b">
+        <f>OR(K40=11,K40=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P40" s="233" t="b">
+        <f>OR(K40=23,K40=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="233" t="b">
+        <f>OR(K40=13,K40=14,K40=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R40" s="233" t="b">
+        <f>OR(K40=1,K40=2,K40=3,K40=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S40" s="234">
+        <f>IF(COUNTA(E40:F40)&lt;2,"",(IF(L40=TRUE,$L$3,IF(M40=TRUE,$M$3,IF(N40=TRUE,$N$3,IF(O40=TRUE,$O$3,IF(P40=TRUE,$P$3,IF(Q40=TRUE,$Q$3,IF(R40=TRUE,$R$3,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="T40" s="232">
+        <f>IF(COUNTA(E40:F40)&lt;2,"",(IF(L40=TRUE,6,IF(M40=TRUE,5,IF(N40=TRUE,4,IF(O40=TRUE,3,IF(P40=TRUE,2,IF(Q40=TRUE,1,IF(R40=TRUE,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="U40" s="243">
+        <f>T40*10+H40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="235">
+        <f>G40</f>
+        <v>0</v>
+      </c>
+      <c r="W40" s="142">
+        <f>'ONR 5'!V13</f>
+        <v>0</v>
+      </c>
+      <c r="X40" s="204">
+        <f>'ONR 5'!W13</f>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="258">
+        <f>I40</f>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="236">
+        <f>D40</f>
+        <v>0</v>
+      </c>
+      <c r="AE40" s="206">
+        <f>IF(K40=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF40" s="206">
+        <f>IF(L40=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG40" s="206">
+        <f>IF(M40=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH40" s="206">
+        <f>IF(N40=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI40" s="206">
+        <f>IF(O40=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="206">
+        <f>IF(P40=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK40" s="206">
+        <f>IF(Q40=TRUE,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL40" s="206">
+        <f>IF(R40=TRUE,1,0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B30:Z30"/>
+    <mergeCell ref="B33:Z33"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="V2:X2"/>
-    <mergeCell ref="B25:Z25"/>
-    <mergeCell ref="B17:Z17"/>
-    <mergeCell ref="B12:Z12"/>
+    <mergeCell ref="B28:Z28"/>
+    <mergeCell ref="B19:Z19"/>
+    <mergeCell ref="B13:Z13"/>
     <mergeCell ref="B4:Z4"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
@@ -20038,17 +20583,17 @@
       <formula>ISTEXT(A2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D11 D13:D16 D33:D36">
+  <conditionalFormatting sqref="D5:D12 D14:D18 D36:D40">
     <cfRule type="expression" dxfId="80" priority="5235">
       <formula>FIND("Conforter",F5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D11 D33:D36 V18:Z24 V26:Z29 D13:D16">
+  <conditionalFormatting sqref="D5:D12 D36:D40 V20:Z27 V29:Z32 D14:D18">
     <cfRule type="expression" dxfId="79" priority="5234" stopIfTrue="1">
       <formula>ISTEXT(D5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D11">
+  <conditionalFormatting sqref="D7:D12">
     <cfRule type="expression" dxfId="78" priority="5227">
       <formula>FIND("Conforter",F7)</formula>
     </cfRule>
@@ -20064,7 +20609,7 @@
       <formula>FIND("Conforter",F8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D13:D16 I13:I16 D18:D24 I18:I24 D26:D29 I26:I29 D31:D36 I31:I36">
+  <conditionalFormatting sqref="D14:D18 I14:I18 D20:D27 I20:I27 D29:D32 I29:I32 D34:D40 I34:I40">
     <cfRule type="expression" dxfId="74" priority="5554">
       <formula>FIND("Réagir",E13)</formula>
     </cfRule>
@@ -20072,7 +20617,7 @@
       <formula>FIND("Agir",E13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18">
+  <conditionalFormatting sqref="D20">
     <cfRule type="expression" dxfId="72" priority="5129">
       <formula>FIND("Conforter",F18)</formula>
     </cfRule>
@@ -20080,12 +20625,12 @@
       <formula>ISTEXT(D18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D24 D26:D29 D31:D36">
+  <conditionalFormatting sqref="D20:D27 D29:D32 D34:D40">
     <cfRule type="expression" dxfId="70" priority="5497">
       <formula>FIND("Conforter",F18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D24">
+  <conditionalFormatting sqref="D20:D27">
     <cfRule type="expression" dxfId="69" priority="5118" stopIfTrue="1">
       <formula>ISTEXT(D18)</formula>
     </cfRule>
@@ -20093,7 +20638,7 @@
       <formula>FIND("Conforter",F18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D23">
+  <conditionalFormatting sqref="D22:D25">
     <cfRule type="expression" dxfId="67" priority="5121">
       <formula>FIND("Conforter",F20)</formula>
     </cfRule>
@@ -20101,7 +20646,7 @@
       <formula>ISTEXT(D20)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D21">
+  <conditionalFormatting sqref="D23">
     <cfRule type="expression" dxfId="65" priority="4990" stopIfTrue="1">
       <formula>ISTEXT(D21)</formula>
     </cfRule>
@@ -20109,7 +20654,7 @@
       <formula>FIND("Conforter",F21)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D26">
+  <conditionalFormatting sqref="D29">
     <cfRule type="expression" dxfId="63" priority="4860" stopIfTrue="1">
       <formula>ISTEXT(D26)</formula>
     </cfRule>
@@ -20117,7 +20662,7 @@
       <formula>FIND("Conforter",F26)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D31">
+  <conditionalFormatting sqref="D34">
     <cfRule type="expression" dxfId="61" priority="4573">
       <formula>FIND("Conforter",F31)</formula>
     </cfRule>
@@ -20125,12 +20670,12 @@
       <formula>ISTEXT(D31)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D31:D36 D18:D24 D26:D29">
+  <conditionalFormatting sqref="D34:D40 D20:D27 D29:D32">
     <cfRule type="expression" dxfId="59" priority="5496" stopIfTrue="1">
       <formula>ISTEXT(D18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D35:D36">
+  <conditionalFormatting sqref="D38:D40">
     <cfRule type="expression" dxfId="58" priority="4435">
       <formula>FIND("Conforter",F35)</formula>
     </cfRule>
@@ -20138,12 +20683,12 @@
       <formula>ISTEXT(D35)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13:H16 F31:H36">
+  <conditionalFormatting sqref="F14:H18 F34:H40">
     <cfRule type="expression" dxfId="56" priority="7">
       <formula>FIND("Conforter",I13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18:H24 F26:H29">
+  <conditionalFormatting sqref="F20:H27 F29:H32">
     <cfRule type="expression" dxfId="55" priority="5547" stopIfTrue="1">
       <formula>ISTEXT(F18)</formula>
     </cfRule>
@@ -20151,12 +20696,12 @@
       <formula>FIND("Conforter",I18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:H36 F13:H16">
+  <conditionalFormatting sqref="F34:H40 F14:H18">
     <cfRule type="expression" dxfId="53" priority="6" stopIfTrue="1">
       <formula>ISTEXT(F13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13:H16 G26:H29 G31:H36 G18:H24">
+  <conditionalFormatting sqref="G14:H18 G29:H32 G34:H40 G20:H27">
     <cfRule type="expression" dxfId="52" priority="5545">
       <formula>FIND("Agir",I13)</formula>
     </cfRule>
@@ -20164,7 +20709,7 @@
       <formula>FIND("Réagir",I13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18:H24">
+  <conditionalFormatting sqref="G20:H27">
     <cfRule type="expression" dxfId="50" priority="5150" stopIfTrue="1">
       <formula>ISTEXT(G18)</formula>
     </cfRule>
@@ -20172,37 +20717,37 @@
       <formula>FIND("Conforter",J18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G31:H36 G13:H16 G26:H29">
+  <conditionalFormatting sqref="G34:H40 G14:H18 G29:H32">
     <cfRule type="expression" dxfId="48" priority="5544" stopIfTrue="1">
       <formula>ISTEXT(G13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G33:H36">
+  <conditionalFormatting sqref="G36:H40">
     <cfRule type="expression" dxfId="47" priority="5393">
       <formula>FIND("Conforter",J33)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G35:H36">
+  <conditionalFormatting sqref="G38:H40">
     <cfRule type="expression" dxfId="46" priority="4437">
       <formula>FIND("Conforter",J35)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18:I24">
+  <conditionalFormatting sqref="G20:I27">
     <cfRule type="expression" dxfId="45" priority="5152" stopIfTrue="1">
       <formula>ISTEXT(G18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G33:I36">
+  <conditionalFormatting sqref="G36:I40">
     <cfRule type="expression" dxfId="44" priority="4594" stopIfTrue="1">
       <formula>ISTEXT(G33)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G35:I36">
+  <conditionalFormatting sqref="G38:I40">
     <cfRule type="expression" dxfId="43" priority="4436" stopIfTrue="1">
       <formula>ISTEXT(G35)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13:H16">
+  <conditionalFormatting sqref="H14:H18">
     <cfRule type="expression" dxfId="42" priority="5327" stopIfTrue="1">
       <formula>ISTEXT(H13)</formula>
     </cfRule>
@@ -20210,7 +20755,7 @@
       <formula>FIND("Conforter",J13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
+  <conditionalFormatting sqref="H29">
     <cfRule type="expression" dxfId="40" priority="4838">
       <formula>FIND("Conforter",J26)</formula>
     </cfRule>
@@ -20218,7 +20763,7 @@
       <formula>ISTEXT(H26)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H36">
+  <conditionalFormatting sqref="H34:H40">
     <cfRule type="expression" dxfId="38" priority="4" stopIfTrue="1">
       <formula>ISTEXT(H31)</formula>
     </cfRule>
@@ -20232,7 +20777,7 @@
       <formula>ISTEXT(H31)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I11">
+  <conditionalFormatting sqref="I5:I12">
     <cfRule type="expression" dxfId="34" priority="2">
       <formula>FIND("Agir",J5)</formula>
     </cfRule>
@@ -20243,12 +20788,12 @@
       <formula>ISTEXT(I5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I13:I16 I18:I24 I26:I29 I31:I36 D18:D24 D26:D29 D31:D36 D13:D16">
+  <conditionalFormatting sqref="I14:I18 I20:I27 I29:I32 I34:I40 D20:D27 D29:D32 D34:D40 D14:D18">
     <cfRule type="expression" dxfId="31" priority="5552" stopIfTrue="1">
       <formula>ISTEXT(D13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18:I24">
+  <conditionalFormatting sqref="I20:I27">
     <cfRule type="expression" dxfId="30" priority="5153">
       <formula>FIND("Agir",J18)</formula>
     </cfRule>
@@ -20256,7 +20801,7 @@
       <formula>FIND("Réagir",J18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I27:I29">
+  <conditionalFormatting sqref="I30:I32">
     <cfRule type="expression" dxfId="28" priority="4876">
       <formula>FIND("Réagir",J27)</formula>
     </cfRule>
@@ -20267,7 +20812,7 @@
       <formula>ISTEXT(I27)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32">
+  <conditionalFormatting sqref="I35">
     <cfRule type="expression" dxfId="25" priority="4586" stopIfTrue="1">
       <formula>ISTEXT(I32)</formula>
     </cfRule>
@@ -20278,7 +20823,7 @@
       <formula>FIND("Agir",J32)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I35:I36">
+  <conditionalFormatting sqref="I38:I40">
     <cfRule type="expression" dxfId="22" priority="4439">
       <formula>FIND("Agir",J35)</formula>
     </cfRule>
@@ -20286,12 +20831,12 @@
       <formula>FIND("Réagir",J35)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:J11 I18:J24 I26:J29 I31:J36 V18:Z24 V26:Z29 V3:Z3 V5:Z11 V13:Z16 V31:Y36 V1:V2 I3:J3 I13:I16">
+  <conditionalFormatting sqref="I5:J12 I20:J27 I29:J32 I34:J40 V20:Z27 V29:Z32 V3:Z3 V5:Z12 V14:Z18 V34:Y40 V1:V2 I3:J3 I14:I18">
     <cfRule type="containsText" dxfId="20" priority="5549" stopIfTrue="1" operator="containsText" text="Première">
       <formula>NOT(ISERROR(SEARCH("Première",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J11 J13:J16 J18:J24 J26:J29 J31:J36">
+  <conditionalFormatting sqref="J5:J12 J14:J18 J20:J27 J29:J32 J34:J40">
     <cfRule type="containsText" dxfId="19" priority="5501" operator="containsText" text="Intervention prioritaire">
       <formula>NOT(ISERROR(SEARCH("Intervention prioritaire",J5)))</formula>
     </cfRule>
@@ -20314,12 +20859,12 @@
       <formula>NOT(ISERROR(SEARCH("long",J5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J11 J18:J24 J26:J29 J31:J36">
+  <conditionalFormatting sqref="J6:J12 J20:J27 J29:J32 J34:J40">
     <cfRule type="containsText" dxfId="12" priority="5541" stopIfTrue="1" operator="containsText" text="Non">
       <formula>NOT(ISERROR(SEARCH("Non",J6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V1:V2 I3:J3 I5:J11 I13:I16 I18:J24 I26:J29 I31:J36">
+  <conditionalFormatting sqref="V1:V2 I3:J3 I5:J12 I14:I18 I20:J27 I29:J32 I34:J40">
     <cfRule type="containsText" dxfId="11" priority="5551" stopIfTrue="1" operator="containsText" text="Terme">
       <formula>NOT(ISERROR(SEARCH("Terme",I1)))</formula>
     </cfRule>
@@ -20327,12 +20872,12 @@
       <formula>NOT(ISERROR(SEARCH("Seconde",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:Z3 V5:Z11 V13:Z16 V18:Z24 V26:Z29 V31:Y36">
+  <conditionalFormatting sqref="V3:Z3 V5:Z12 V14:Z18 V20:Z27 V29:Z32 V34:Y40">
     <cfRule type="containsText" dxfId="9" priority="94" stopIfTrue="1" operator="containsText" text="Terme">
       <formula>NOT(ISERROR(SEARCH("Terme",V3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:Z11 V13:Z16 V31:Z36">
+  <conditionalFormatting sqref="V5:Z12 V14:Z18 V34:Z40">
     <cfRule type="expression" dxfId="8" priority="84">
       <formula>FIND("Agir",#REF!)</formula>
     </cfRule>
@@ -20340,12 +20885,12 @@
       <formula>FIND("Réagir",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V18:Z24 V26:Z29 V5:Z11 V13:Z16 V31:Y36 V3:Z3">
+  <conditionalFormatting sqref="V20:Z27 V29:Z32 V5:Z12 V14:Z18 V34:Y40 V3:Z3">
     <cfRule type="containsText" dxfId="6" priority="93" stopIfTrue="1" operator="containsText" text="Seconde">
       <formula>NOT(ISERROR(SEARCH("Seconde",V3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V18:Z24 V26:Z29">
+  <conditionalFormatting sqref="V20:Z27 V29:Z32">
     <cfRule type="expression" dxfId="5" priority="91">
       <formula>FIND("Réagir",#REF!)</formula>
     </cfRule>
@@ -20353,12 +20898,12 @@
       <formula>FIND("Agir",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V31:Z36 V5:Z11 V13:Z16">
+  <conditionalFormatting sqref="V34:Z40 V5:Z12 V14:Z18">
     <cfRule type="expression" dxfId="3" priority="83" stopIfTrue="1">
       <formula>ISTEXT(V5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z31:Z36">
+  <conditionalFormatting sqref="Z34:Z40">
     <cfRule type="containsText" dxfId="2" priority="17" stopIfTrue="1" operator="containsText" text="Première">
       <formula>NOT(ISERROR(SEARCH("Première",Z31)))</formula>
     </cfRule>
@@ -20370,13 +20915,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences locales" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cibles sont : _x000a__x000a_1 - Exclusives au locale_x000a_2 - Partagées entre local et l'État_x000a_3 - À l'État, supporté par le local_x000a_4 - Exclusives à l'État_x000a_" sqref="H26 H13:H16" xr:uid="{00000000-0002-0000-1400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences locales" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cibles sont : _x000a__x000a_1 - Exclusives au locale_x000a_2 - Partagées entre local et l'État_x000a_3 - À l'État, supporté par le local_x000a_4 - Exclusives à l'État_x000a_" sqref="H29 H14:H18" xr:uid="{00000000-0002-0000-1400-000000000000}">
       <formula1>$M$1:$P$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a__x000a_1 - Loin d'être atteinte_x000a_2 - Partiellement atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F13:F16 F18:F24 F26:F36 F5:F11" xr:uid="{00000000-0002-0000-1400-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a__x000a_1 - Loin d'être atteinte_x000a_2 - Partiellement atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F14:F18 F20:F27 F29:F40 F5:F12" xr:uid="{00000000-0002-0000-1400-000001000000}">
       <formula1>$M$1:$P$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a__x000a_0 - Non applicable_x000a_1 - Importance faible_x000a_2 - Importance moyenne_x000a_3 - Importance forte" sqref="E13:E16 E18:E24 E26:E36 E5:E11" xr:uid="{00000000-0002-0000-1400-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a__x000a_0 - Non applicable_x000a_1 - Importance faible_x000a_2 - Importance moyenne_x000a_3 - Importance forte" sqref="E14:E18 E20:E27 E29:E40 E5:E12" xr:uid="{00000000-0002-0000-1400-000002000000}">
       <formula1>$L$1:$O$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -20591,188 +21136,188 @@
     <row r="5" spans="2:32" ht="31.5" customHeight="1">
       <c r="B5" s="74"/>
       <c r="C5" s="70" t="str">
-        <f>'Résultats détaillés'!AB12</f>
+        <f>'Résultats détaillés'!AB13</f>
         <v>ONR 2  -   INCLUSION : S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
       </c>
       <c r="D5" s="44">
-        <f>IF('Résultats détaillés'!AC12=0,"",'Résultats détaillés'!AC12)</f>
+        <f>IF('Résultats détaillés'!AC13=0,"",'Résultats détaillés'!AC13)</f>
         <v>4</v>
       </c>
       <c r="E5" s="66" t="str">
-        <f>IF('Résultats détaillés'!AD12=0,"",'Résultats détaillés'!AD12)</f>
+        <f>IF('Résultats détaillés'!AD13=0,"",'Résultats détaillés'!AD13)</f>
         <v/>
       </c>
       <c r="F5" s="64">
-        <f>IF('Résultats détaillés'!AE12=0,"",'Résultats détaillés'!AE12)</f>
+        <f>IF('Résultats détaillés'!AE13=0,"",'Résultats détaillés'!AE13)</f>
         <v>4</v>
       </c>
       <c r="G5" s="44" t="str">
-        <f>IF('Résultats détaillés'!AF12=0,"",'Résultats détaillés'!AF12)</f>
+        <f>IF('Résultats détaillés'!AF13=0,"",'Résultats détaillés'!AF13)</f>
         <v/>
       </c>
       <c r="H5" s="44" t="str">
-        <f>IF('Résultats détaillés'!AG12=0,"",'Résultats détaillés'!AG12)</f>
+        <f>IF('Résultats détaillés'!AG13=0,"",'Résultats détaillés'!AG13)</f>
         <v/>
       </c>
       <c r="I5" s="44" t="str">
-        <f>IF('Résultats détaillés'!AH12=0,"",'Résultats détaillés'!AH12)</f>
+        <f>IF('Résultats détaillés'!AH13=0,"",'Résultats détaillés'!AH13)</f>
         <v/>
       </c>
       <c r="J5" s="44" t="str">
-        <f>IF('Résultats détaillés'!AI12=0,"",'Résultats détaillés'!AI12)</f>
+        <f>IF('Résultats détaillés'!AI13=0,"",'Résultats détaillés'!AI13)</f>
         <v/>
       </c>
       <c r="K5" s="44" t="str">
-        <f>IF('Résultats détaillés'!AJ12=0,"",'Résultats détaillés'!AJ12)</f>
+        <f>IF('Résultats détaillés'!AJ13=0,"",'Résultats détaillés'!AJ13)</f>
         <v/>
       </c>
       <c r="L5" s="44" t="str">
-        <f>IF('Résultats détaillés'!AK12=0,"",'Résultats détaillés'!AK12)</f>
+        <f>IF('Résultats détaillés'!AK13=0,"",'Résultats détaillés'!AK13)</f>
         <v/>
       </c>
       <c r="M5" s="71" t="str">
-        <f>IF('Résultats détaillés'!AL12=0,"",'Résultats détaillés'!AL12)</f>
+        <f>IF('Résultats détaillés'!AL13=0,"",'Résultats détaillés'!AL13)</f>
         <v/>
       </c>
     </row>
     <row r="6" spans="2:32" ht="31.5" customHeight="1">
       <c r="B6" s="75"/>
       <c r="C6" s="70" t="str">
-        <f>'Résultats détaillés'!AB17</f>
+        <f>'Résultats détaillés'!AB19</f>
         <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
       </c>
       <c r="D6" s="44">
-        <f>IF('Résultats détaillés'!AC17=0,"",'Résultats détaillés'!AC17)</f>
+        <f>IF('Résultats détaillés'!AC19=0,"",'Résultats détaillés'!AC19)</f>
         <v>7</v>
       </c>
       <c r="E6" s="66" t="str">
-        <f>IF('Résultats détaillés'!AD17=0,"",'Résultats détaillés'!AD17)</f>
+        <f>IF('Résultats détaillés'!AD19=0,"",'Résultats détaillés'!AD19)</f>
         <v/>
       </c>
       <c r="F6" s="64">
-        <f>IF('Résultats détaillés'!AE17=0,"",'Résultats détaillés'!AE17)</f>
+        <f>IF('Résultats détaillés'!AE19=0,"",'Résultats détaillés'!AE19)</f>
         <v>7</v>
       </c>
       <c r="G6" s="44" t="str">
-        <f>IF('Résultats détaillés'!AF17=0,"",'Résultats détaillés'!AF17)</f>
+        <f>IF('Résultats détaillés'!AF19=0,"",'Résultats détaillés'!AF19)</f>
         <v/>
       </c>
       <c r="H6" s="44" t="str">
-        <f>IF('Résultats détaillés'!AG17=0,"",'Résultats détaillés'!AG17)</f>
+        <f>IF('Résultats détaillés'!AG19=0,"",'Résultats détaillés'!AG19)</f>
         <v/>
       </c>
       <c r="I6" s="44" t="str">
-        <f>IF('Résultats détaillés'!AH17=0,"",'Résultats détaillés'!AH17)</f>
+        <f>IF('Résultats détaillés'!AH19=0,"",'Résultats détaillés'!AH19)</f>
         <v/>
       </c>
       <c r="J6" s="44" t="str">
-        <f>IF('Résultats détaillés'!AI17=0,"",'Résultats détaillés'!AI17)</f>
+        <f>IF('Résultats détaillés'!AI19=0,"",'Résultats détaillés'!AI19)</f>
         <v/>
       </c>
       <c r="K6" s="44" t="str">
-        <f>IF('Résultats détaillés'!AJ17=0,"",'Résultats détaillés'!AJ17)</f>
+        <f>IF('Résultats détaillés'!AJ19=0,"",'Résultats détaillés'!AJ19)</f>
         <v/>
       </c>
       <c r="L6" s="44" t="str">
-        <f>IF('Résultats détaillés'!AK17=0,"",'Résultats détaillés'!AK17)</f>
+        <f>IF('Résultats détaillés'!AK19=0,"",'Résultats détaillés'!AK19)</f>
         <v/>
       </c>
       <c r="M6" s="71" t="str">
-        <f>IF('Résultats détaillés'!AL17=0,"",'Résultats détaillés'!AL17)</f>
+        <f>IF('Résultats détaillés'!AL19=0,"",'Résultats détaillés'!AL19)</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="2:32" ht="31.5" customHeight="1">
       <c r="B7" s="76"/>
       <c r="C7" s="70" t="str">
-        <f>'Résultats détaillés'!AB25</f>
+        <f>'Résultats détaillés'!AB28</f>
         <v>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
       </c>
       <c r="D7" s="44">
-        <f>IF('Résultats détaillés'!AC25=0,"",'Résultats détaillés'!AC25)</f>
+        <f>IF('Résultats détaillés'!AC28=0,"",'Résultats détaillés'!AC28)</f>
         <v>4</v>
       </c>
       <c r="E7" s="66" t="str">
-        <f>IF('Résultats détaillés'!AD25=0,"",'Résultats détaillés'!AD25)</f>
+        <f>IF('Résultats détaillés'!AD28=0,"",'Résultats détaillés'!AD28)</f>
         <v/>
       </c>
       <c r="F7" s="64">
-        <f>IF('Résultats détaillés'!AE25=0,"",'Résultats détaillés'!AE25)</f>
+        <f>IF('Résultats détaillés'!AE28=0,"",'Résultats détaillés'!AE28)</f>
         <v>4</v>
       </c>
       <c r="G7" s="44" t="str">
-        <f>IF('Résultats détaillés'!AF25=0,"",'Résultats détaillés'!AF25)</f>
+        <f>IF('Résultats détaillés'!AF28=0,"",'Résultats détaillés'!AF28)</f>
         <v/>
       </c>
       <c r="H7" s="44" t="str">
-        <f>IF('Résultats détaillés'!AG25=0,"",'Résultats détaillés'!AG25)</f>
+        <f>IF('Résultats détaillés'!AG28=0,"",'Résultats détaillés'!AG28)</f>
         <v/>
       </c>
       <c r="I7" s="44" t="str">
-        <f>IF('Résultats détaillés'!AH25=0,"",'Résultats détaillés'!AH25)</f>
+        <f>IF('Résultats détaillés'!AH28=0,"",'Résultats détaillés'!AH28)</f>
         <v/>
       </c>
       <c r="J7" s="44" t="str">
-        <f>IF('Résultats détaillés'!AI25=0,"",'Résultats détaillés'!AI25)</f>
+        <f>IF('Résultats détaillés'!AI28=0,"",'Résultats détaillés'!AI28)</f>
         <v/>
       </c>
       <c r="K7" s="44" t="str">
-        <f>IF('Résultats détaillés'!AJ25=0,"",'Résultats détaillés'!AJ25)</f>
+        <f>IF('Résultats détaillés'!AJ28=0,"",'Résultats détaillés'!AJ28)</f>
         <v/>
       </c>
       <c r="L7" s="44" t="str">
-        <f>IF('Résultats détaillés'!AK25=0,"",'Résultats détaillés'!AK25)</f>
+        <f>IF('Résultats détaillés'!AK28=0,"",'Résultats détaillés'!AK28)</f>
         <v/>
       </c>
       <c r="M7" s="71" t="str">
-        <f>IF('Résultats détaillés'!AL25=0,"",'Résultats détaillés'!AL25)</f>
+        <f>IF('Résultats détaillés'!AL28=0,"",'Résultats détaillés'!AL28)</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="2:32" ht="31.5" customHeight="1">
       <c r="B8" s="77"/>
       <c r="C8" s="70" t="str">
-        <f>'Résultats détaillés'!B30</f>
+        <f>'Résultats détaillés'!B33</f>
         <v>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
       </c>
       <c r="D8" s="44">
-        <f>IF('Résultats détaillés'!AC30=0,"",'Résultats détaillés'!AC30)</f>
+        <f>IF('Résultats détaillés'!AC33=0,"",'Résultats détaillés'!AC33)</f>
         <v>6</v>
       </c>
       <c r="E8" s="66" t="str">
-        <f>IF('Résultats détaillés'!AD30=0,"",'Résultats détaillés'!AD30)</f>
+        <f>IF('Résultats détaillés'!AD33=0,"",'Résultats détaillés'!AD33)</f>
         <v/>
       </c>
       <c r="F8" s="44">
-        <f>IF('Résultats détaillés'!AE30=0,"",'Résultats détaillés'!AE30)</f>
+        <f>IF('Résultats détaillés'!AE33=0,"",'Résultats détaillés'!AE33)</f>
         <v>6</v>
       </c>
       <c r="G8" s="44" t="str">
-        <f>IF('Résultats détaillés'!AF30=0,"",'Résultats détaillés'!AF30)</f>
+        <f>IF('Résultats détaillés'!AF33=0,"",'Résultats détaillés'!AF33)</f>
         <v/>
       </c>
       <c r="H8" s="44" t="str">
-        <f>IF('Résultats détaillés'!AG30=0,"",'Résultats détaillés'!AG30)</f>
+        <f>IF('Résultats détaillés'!AG33=0,"",'Résultats détaillés'!AG33)</f>
         <v/>
       </c>
       <c r="I8" s="44" t="str">
-        <f>IF('Résultats détaillés'!AH30=0,"",'Résultats détaillés'!AH30)</f>
+        <f>IF('Résultats détaillés'!AH33=0,"",'Résultats détaillés'!AH33)</f>
         <v/>
       </c>
       <c r="J8" s="44" t="str">
-        <f>IF('Résultats détaillés'!AI30=0,"",'Résultats détaillés'!AI30)</f>
+        <f>IF('Résultats détaillés'!AI33=0,"",'Résultats détaillés'!AI33)</f>
         <v/>
       </c>
       <c r="K8" s="44" t="str">
-        <f>IF('Résultats détaillés'!AJ30=0,"",'Résultats détaillés'!AJ30)</f>
+        <f>IF('Résultats détaillés'!AJ33=0,"",'Résultats détaillés'!AJ33)</f>
         <v/>
       </c>
       <c r="L8" s="44" t="str">
-        <f>IF('Résultats détaillés'!AK30=0,"",'Résultats détaillés'!AK30)</f>
+        <f>IF('Résultats détaillés'!AK33=0,"",'Résultats détaillés'!AK33)</f>
         <v/>
       </c>
       <c r="M8" s="44" t="str">
-        <f>IF('Résultats détaillés'!AL30=0,"",'Résultats détaillés'!AL30)</f>
+        <f>IF('Résultats détaillés'!AL33=0,"",'Résultats détaillés'!AL33)</f>
         <v/>
       </c>
     </row>
@@ -22839,7 +23384,7 @@
     <tabColor theme="4"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="1.5" style="51" customWidth="1"/>
@@ -23520,6 +24065,75 @@
       <c r="W13" s="306"/>
       <c r="X13" s="299"/>
     </row>
+    <row r="14" spans="1:24" ht="42">
+      <c r="B14" s="154" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="C14" s="323" t="inlineStr">
+        <is>
+          <t>En mesurant ce que consomme l'IA, de son entraînement à son usage, et en le réduisant</t>
+        </is>
+      </c>
+      <c r="D14" s="139"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="282"/>
+      <c r="G14" s="325"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="172"/>
+      <c r="J14" s="147" t="str">
+        <f>S14</f>
+        <v/>
+      </c>
+      <c r="K14" s="96">
+        <f>E14*10+F14</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="96" t="b">
+        <f>OR(K14=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="96" t="b">
+        <f>OR(K14=21,K14=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="96" t="b">
+        <f>OR(K14=22,K14=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="96" t="b">
+        <f>OR(K14=11,K14=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="96" t="b">
+        <f>OR(K14=23,K14=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="96" t="b">
+        <f>OR(K14=13,K14=14,K14=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="96" t="b">
+        <f>OR(K14=1,K14=2,K14=3,K14=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="97" t="str">
+        <f>IF(COUNTA(E14:F14)&lt;2,"",(IF(L14=TRUE,$L$5,IF(M14=TRUE,$M$5,IF(N14=TRUE,$N$5,IF(O14=TRUE,$O$5,IF(P14=TRUE,$P$5,IF(Q14=TRUE,$Q$5,IF(R14=TRUE,$R$5,0)))))))))</f>
+        <v/>
+      </c>
+      <c r="T14" s="98" t="str">
+        <f>IF(COUNTA(E14:F14)&lt;2,"",(IF(L14=TRUE,6,IF(M14=TRUE,5,IF(N14=TRUE,4,IF(O14=TRUE,3,IF(P14=TRUE,2,IF(Q14=TRUE,1,IF(R14=TRUE,0,0)))))))))</f>
+        <v/>
+      </c>
+      <c r="U14" s="99" t="e">
+        <f>T14*10+H14</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V14" s="149"/>
+      <c r="W14" s="306"/>
+      <c r="X14" s="299"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:G2"/>
@@ -23532,7 +24146,7 @@
     <mergeCell ref="V4:X4"/>
   </mergeCells>
   <phoneticPr fontId="42" type="noConversion"/>
-  <conditionalFormatting sqref="A4 I7:I13 G7">
+  <conditionalFormatting sqref="A4 I7:I14 G7">
     <cfRule type="expression" dxfId="405" priority="269">
       <formula>FIND("Agir",B4)</formula>
     </cfRule>
@@ -23540,7 +24154,7 @@
       <formula>FIND("Réagir",B4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4 I7:I13">
+  <conditionalFormatting sqref="A4 I7:I14">
     <cfRule type="expression" dxfId="403" priority="268" stopIfTrue="1">
       <formula>ISTEXT(A4)</formula>
     </cfRule>
@@ -23565,7 +24179,7 @@
       <formula>ISTEXT(A4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D13">
+  <conditionalFormatting sqref="D7:D14">
     <cfRule type="expression" dxfId="396" priority="76">
       <formula>FIND("Conforter",F7)</formula>
     </cfRule>
@@ -23582,12 +24196,12 @@
       <formula>FIND("Réagir",E7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D13 F7">
+  <conditionalFormatting sqref="D8:D14 F7">
     <cfRule type="expression" dxfId="391" priority="77" stopIfTrue="1">
       <formula>ISTEXT(D7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D13">
+  <conditionalFormatting sqref="D9:D14">
     <cfRule type="expression" dxfId="390" priority="68">
       <formula>FIND("Conforter",F9)</formula>
     </cfRule>
@@ -23603,22 +24217,22 @@
       <formula>FIND("Conforter",F10)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7 D8:D13">
+  <conditionalFormatting sqref="F7 D8:D14">
     <cfRule type="expression" dxfId="386" priority="78">
       <formula>FIND("Conforter",F7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F13">
+  <conditionalFormatting sqref="F8:F14">
     <cfRule type="expression" dxfId="385" priority="119">
       <formula>FIND("Conforter",I8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:H7 F8:H13">
+  <conditionalFormatting sqref="G7:H7 F8:H14">
     <cfRule type="expression" dxfId="384" priority="115" stopIfTrue="1">
       <formula>ISTEXT(F7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:H13">
+  <conditionalFormatting sqref="G7:H14">
     <cfRule type="expression" dxfId="383" priority="114">
       <formula>FIND("Conforter",J7)</formula>
     </cfRule>
@@ -23626,7 +24240,7 @@
       <formula>ISTEXT(G7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:H13">
+  <conditionalFormatting sqref="G9:H14">
     <cfRule type="expression" dxfId="381" priority="93">
       <formula>FIND("Conforter",J9)</formula>
     </cfRule>
@@ -23639,12 +24253,12 @@
       <formula>ISTEXT(G10)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:I13">
+  <conditionalFormatting sqref="G9:I14">
     <cfRule type="expression" dxfId="378" priority="92" stopIfTrue="1">
       <formula>ISTEXT(G9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7 G8:H13">
+  <conditionalFormatting sqref="H7 G8:H14">
     <cfRule type="expression" dxfId="377" priority="117">
       <formula>FIND("Réagir",I7)</formula>
     </cfRule>
@@ -23652,7 +24266,7 @@
       <formula>FIND("Agir",I7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H13">
+  <conditionalFormatting sqref="H7:H14">
     <cfRule type="expression" dxfId="375" priority="66">
       <formula>FIND("Réagir",J7)</formula>
     </cfRule>
@@ -23663,12 +24277,12 @@
       <formula>ISTEXT(H7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:I7 H8:J13 V7:W13">
+  <conditionalFormatting sqref="H7:I7 H8:J14 V7:W13">
     <cfRule type="containsText" dxfId="372" priority="120" stopIfTrue="1" operator="containsText" text="Première">
       <formula>NOT(ISERROR(SEARCH("Première",H7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:I7 V7:W13 H8:J13">
+  <conditionalFormatting sqref="H7:I7 V7:W14 H8:J13">
     <cfRule type="containsText" dxfId="371" priority="121" stopIfTrue="1" operator="containsText" text="Seconde">
       <formula>NOT(ISERROR(SEARCH("Seconde",H7)))</formula>
     </cfRule>
@@ -23687,7 +24301,7 @@
       <formula>ISTEXT(I7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:I13">
+  <conditionalFormatting sqref="I9:I14">
     <cfRule type="expression" dxfId="366" priority="96">
       <formula>FIND("Réagir",J9)</formula>
     </cfRule>
@@ -23695,7 +24309,7 @@
       <formula>FIND("Agir",J9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I13">
+  <conditionalFormatting sqref="I12:I14">
     <cfRule type="expression" dxfId="364" priority="1">
       <formula>FIND("Conforter",L12)</formula>
     </cfRule>
@@ -23715,7 +24329,7 @@
       <formula>ISTEXT(I12)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J13">
+  <conditionalFormatting sqref="J7:J14">
     <cfRule type="containsText" dxfId="358" priority="88" stopIfTrue="1" operator="containsText" text="long">
       <formula>NOT(ISERROR(SEARCH("long",J7)))</formula>
     </cfRule>
@@ -23738,7 +24352,7 @@
       <formula>NOT(ISERROR(SEARCH("Non pertinent",J7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J13">
+  <conditionalFormatting sqref="J8:J14">
     <cfRule type="containsText" dxfId="351" priority="112" stopIfTrue="1" operator="containsText" text="Non">
       <formula>NOT(ISERROR(SEARCH("Non",J8)))</formula>
     </cfRule>
@@ -23754,7 +24368,7 @@
       <formula>NOT(ISERROR(SEARCH("Terme",J4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:W13">
+  <conditionalFormatting sqref="V7:W14">
     <cfRule type="expression" dxfId="347" priority="25">
       <formula>FIND("Réagir",#REF!)</formula>
     </cfRule>
@@ -23777,13 +24391,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a_1 - Pas du tout atteinte_x000a_2 - En partie atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F7:F13" xr:uid="{762842EB-0F03-4937-87D1-1AAFC2B5391C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a_1 - Pas du tout atteinte_x000a_2 - En partie atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F7:F14" xr:uid="{762842EB-0F03-4937-87D1-1AAFC2B5391C}">
       <formula1>$M$1:$P$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a_0 - Non applicable_x000a_1 - Peu important_x000a_2 - Important_x000a_3 - Très important" sqref="E7:E13" xr:uid="{E2CB4F99-AC63-4DD0-9426-57C9A27EBE7B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a_0 - Non applicable_x000a_1 - Peu important_x000a_2 - Important_x000a_3 - Très important" sqref="E7:E14" xr:uid="{E2CB4F99-AC63-4DD0-9426-57C9A27EBE7B}">
       <formula1>$L$1:$O$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cible sont : _x000a_1 - Equipe NR / RSE_x000a_2 - NR + implication DSI_x000a_3 - NR + équipe hors DSI _x000a_3 - Intervention extérieure" sqref="H7:H13" xr:uid="{C589538E-36C5-F649-8C27-182B661180B1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cible sont : _x000a_1 - Equipe NR / RSE_x000a_2 - NR + implication DSI_x000a_3 - NR + équipe hors DSI _x000a_3 - Intervention extérieure" sqref="H7:H14" xr:uid="{C589538E-36C5-F649-8C27-182B661180B1}">
       <formula1>$M$1:$O$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -24230,7 +24844,10 @@
       <c r="G10" s="324"/>
       <c r="H10" s="140"/>
       <c r="I10" s="141"/>
-      <c r="J10" s="110"/>
+      <c r="J10" s="110">
+        <f>S10</f>
+        <v>0</v>
+      </c>
       <c r="K10" s="88">
         <f>E10*10+F10</f>
         <v>0</v>
@@ -24279,8 +24896,78 @@
       <c r="W10" s="294"/>
       <c r="X10" s="293"/>
     </row>
-    <row r="11" spans="1:24">
-      <c r="V11" s="78"/>
+    <row r="11" spans="1:24" s="137" customFormat="1" ht="63">
+      <c r="A11" s="136"/>
+      <c r="B11" s="180" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="C11" s="318" t="inlineStr">
+        <is>
+          <t>En vérifiant que l'IA ne discrimine personne et que ses services restent utilisables par tous</t>
+        </is>
+      </c>
+      <c r="D11" s="139"/>
+      <c r="E11" s="169"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="324"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="110">
+        <f>S11</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="88">
+        <f>E11*10+F11</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="88" t="b">
+        <f>OR(K11=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="88" t="b">
+        <f>OR(K11=21,K11=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="88" t="b">
+        <f>OR(K11=22,K11=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="88" t="b">
+        <f>OR(K11=11,K11=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="88" t="b">
+        <f>OR(K11=23,K11=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="88" t="b">
+        <f>OR(K11=13,K11=14,K11=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="88" t="b">
+        <f>OR(K11=1,K11=2,K11=3,K11=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="89" t="str">
+        <f>IF(COUNTA(E11:F11)&lt;2,"",(IF(L11=TRUE,$L$5,IF(M11=TRUE,$M$5,IF(N11=TRUE,$N$5,IF(O11=TRUE,$O$5,IF(P11=TRUE,$P$5,IF(Q11=TRUE,$Q$5,IF(R11=TRUE,$R$5,0)))))))))</f>
+        <v/>
+      </c>
+      <c r="T11" s="90" t="str">
+        <f>IF(COUNTA(E11:F11)&lt;2,"",(IF(L11=TRUE,6,IF(M11=TRUE,5,IF(N11=TRUE,4,IF(O11=TRUE,3,IF(P11=TRUE,2,IF(Q11=TRUE,1,IF(R11=TRUE,0,0)))))))))</f>
+        <v/>
+      </c>
+      <c r="U11" s="91" t="e">
+        <f>T11*10+H11</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V11" s="150"/>
+      <c r="W11" s="294"/>
+      <c r="X11" s="293"/>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="V12" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -24321,7 +25008,7 @@
       <formula>ISTEXT(A4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D10 I7:I10">
+  <conditionalFormatting sqref="D7:D11 I7:I10">
     <cfRule type="expression" dxfId="332" priority="79">
       <formula>FIND("Réagir",E7)</formula>
     </cfRule>
@@ -24329,7 +25016,7 @@
       <formula>FIND("Agir",E7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D10">
+  <conditionalFormatting sqref="D7:D11">
     <cfRule type="expression" dxfId="330" priority="50" stopIfTrue="1">
       <formula>ISTEXT(D7)</formula>
     </cfRule>
@@ -24343,7 +25030,7 @@
       <formula>FIND("Conforter",F7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:H10">
+  <conditionalFormatting sqref="F7:H11">
     <cfRule type="expression" dxfId="326" priority="73">
       <formula>FIND("Conforter",I7)</formula>
     </cfRule>
@@ -24356,7 +25043,7 @@
       <formula>ISTEXT(G7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:H10">
+  <conditionalFormatting sqref="G7:H11">
     <cfRule type="expression" dxfId="323" priority="64" stopIfTrue="1">
       <formula>ISTEXT(G7)</formula>
     </cfRule>
@@ -24378,12 +25065,12 @@
       <formula>FIND("Conforter",J9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H10 G8:H10">
+  <conditionalFormatting sqref="H7:H11 G8:H10">
     <cfRule type="expression" dxfId="317" priority="69" stopIfTrue="1">
       <formula>ISTEXT(G7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H10">
+  <conditionalFormatting sqref="H7:H11">
     <cfRule type="expression" dxfId="316" priority="45" stopIfTrue="1">
       <formula>ISTEXT(H7)</formula>
     </cfRule>
@@ -24391,12 +25078,12 @@
       <formula>FIND("Conforter",J7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I10 D7:D10">
+  <conditionalFormatting sqref="I7:I11 D7:D10">
     <cfRule type="expression" dxfId="314" priority="77" stopIfTrue="1">
       <formula>ISTEXT(D7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:J10">
+  <conditionalFormatting sqref="I7:J11">
     <cfRule type="containsText" dxfId="313" priority="75" stopIfTrue="1" operator="containsText" text="Seconde">
       <formula>NOT(ISERROR(SEARCH("Seconde",I7)))</formula>
     </cfRule>
@@ -24407,7 +25094,7 @@
       <formula>NOT(ISERROR(SEARCH("Terme",I7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J10">
+  <conditionalFormatting sqref="J7:J11">
     <cfRule type="containsText" dxfId="310" priority="68" stopIfTrue="1" operator="containsText" text="Non">
       <formula>NOT(ISERROR(SEARCH("Non",J7)))</formula>
     </cfRule>
@@ -24444,7 +25131,7 @@
       <formula>NOT(ISERROR(SEARCH("Terme",J4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:W10">
+  <conditionalFormatting sqref="V7:W11">
     <cfRule type="containsText" dxfId="299" priority="22" stopIfTrue="1" operator="containsText" text="Terme">
       <formula>NOT(ISERROR(SEARCH("Terme",V7)))</formula>
     </cfRule>
@@ -24476,13 +25163,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a_0 - Non applicable_x000a_1 - Peu important_x000a_2 - Important_x000a_3 - Très important" sqref="E7:E10" xr:uid="{A0964DBD-7852-4917-A775-9DF88395F596}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a_0 - Non applicable_x000a_1 - Peu important_x000a_2 - Important_x000a_3 - Très important" sqref="E7:E11" xr:uid="{A0964DBD-7852-4917-A775-9DF88395F596}">
       <formula1>$L$1:$O$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a_1 - Pas du tout atteinte_x000a_2 - En partie atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F7:F10" xr:uid="{B412C5EB-C982-4DD4-BF6A-C8C1B82A5ABD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a_1 - Pas du tout atteinte_x000a_2 - En partie atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F7:F11" xr:uid="{B412C5EB-C982-4DD4-BF6A-C8C1B82A5ABD}">
       <formula1>$M$1:$P$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cible sont : _x000a_1 - Equipe NR / RSE_x000a_2 - NR + implication DSI_x000a_3 - NR + équipe hors DSI _x000a_3 - Intervention extérieure" sqref="H7:H10" xr:uid="{F3835DF9-F076-9E49-954F-F140CB72AE8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cible sont : _x000a_1 - Equipe NR / RSE_x000a_2 - NR + implication DSI_x000a_3 - NR + équipe hors DSI _x000a_3 - Intervention extérieure" sqref="H7:H11" xr:uid="{F3835DF9-F076-9E49-954F-F140CB72AE8E}">
       <formula1>$M$1:$O$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -24497,7 +25184,7 @@
   <sheetPr codeName="Feuil6">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:QE13"/>
+  <dimension ref="A1:QE14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="1.5" style="51" customWidth="1"/>
@@ -26025,6 +26712,76 @@
       <c r="W13" s="296"/>
       <c r="X13" s="293"/>
     </row>
+    <row r="14" spans="1:447" s="137" customFormat="1" ht="21">
+      <c r="A14" s="136"/>
+      <c r="B14" s="181" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="C14" s="318" t="inlineStr">
+        <is>
+          <t>En disant quand c'est une IA qui répond, en expliquant comment elle décide, et en gardant un humain aux commandes sur les sujets sensibles</t>
+        </is>
+      </c>
+      <c r="D14" s="139"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="141"/>
+      <c r="J14" s="147" t="str">
+        <f>S14</f>
+        <v/>
+      </c>
+      <c r="K14" s="96">
+        <f>E14*10+F14</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="96" t="b">
+        <f>OR(K14=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="96" t="b">
+        <f>OR(K14=21,K14=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="96" t="b">
+        <f>OR(K14=22,K14=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="96" t="b">
+        <f>OR(K14=11,K14=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="96" t="b">
+        <f>OR(K14=23,K14=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="96" t="b">
+        <f>OR(K14=13,K14=14,K14=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="96" t="b">
+        <f>OR(K14=1,K14=2,K14=3,K14=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="97" t="str">
+        <f>IF(COUNTA(E14:F14)&lt;2,"",(IF(L14=TRUE,$L$5,IF(M14=TRUE,$M$5,IF(N14=TRUE,$N$5,IF(O14=TRUE,$O$5,IF(P14=TRUE,$P$5,IF(Q14=TRUE,$Q$5,IF(R14=TRUE,$R$5,0)))))))))</f>
+        <v/>
+      </c>
+      <c r="T14" s="98" t="str">
+        <f>IF(COUNTA(E14:F14)&lt;2,"",(IF(L14=TRUE,6,IF(M14=TRUE,5,IF(N14=TRUE,4,IF(O14=TRUE,3,IF(P14=TRUE,2,IF(Q14=TRUE,1,IF(R14=TRUE,0,0)))))))))</f>
+        <v/>
+      </c>
+      <c r="U14" s="99" t="e">
+        <f>T14*10+H14</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V14" s="149"/>
+      <c r="W14" s="296"/>
+      <c r="X14" s="293"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:G2"/>
@@ -26065,7 +26822,7 @@
       <formula>FIND("Réagir",B4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D13 K10:S10">
+  <conditionalFormatting sqref="D7:D14 K10:S10">
     <cfRule type="expression" dxfId="281" priority="88" stopIfTrue="1">
       <formula>ISTEXT(D7)</formula>
     </cfRule>
@@ -26091,12 +26848,12 @@
       <formula>FIND("Conforter",F7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D13 K10:T10">
+  <conditionalFormatting sqref="D7:D14 K10:T10">
     <cfRule type="expression" dxfId="273" priority="102" stopIfTrue="1">
       <formula>ISTEXT(D7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F13">
+  <conditionalFormatting sqref="F7:F14">
     <cfRule type="expression" dxfId="272" priority="146" stopIfTrue="1">
       <formula>ISTEXT(F7)</formula>
     </cfRule>
@@ -26126,7 +26883,7 @@
       <formula>ISTEXT(G7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
+  <conditionalFormatting sqref="G14">
     <cfRule type="expression" dxfId="264" priority="27">
       <formula>FIND("Conforter",J13)</formula>
     </cfRule>
@@ -26143,7 +26900,7 @@
       <formula>ISTEXT(G13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H13 G8:H9 G10:G12">
+  <conditionalFormatting sqref="H7:H14 G8:H9 G10:G12">
     <cfRule type="expression" dxfId="259" priority="142">
       <formula>FIND("Conforter",J7)</formula>
     </cfRule>
@@ -26151,12 +26908,12 @@
       <formula>ISTEXT(G7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H13 G8:H12">
+  <conditionalFormatting sqref="H7:H14 G8:H12">
     <cfRule type="expression" dxfId="257" priority="121">
       <formula>FIND("Conforter",J7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H13">
+  <conditionalFormatting sqref="H7:H14">
     <cfRule type="expression" dxfId="256" priority="87">
       <formula>FIND("Réagir",J7)</formula>
     </cfRule>
@@ -26173,22 +26930,22 @@
       <formula>ISTEXT(H7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H13 G7:I12 V7:V9 V13">
+  <conditionalFormatting sqref="H8:H14 G7:I12 V7:V9 V13">
     <cfRule type="expression" dxfId="251" priority="120" stopIfTrue="1">
       <formula>ISTEXT(G7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="H14">
     <cfRule type="expression" dxfId="250" priority="116">
       <formula>FIND("Conforter",K13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13:I13">
+  <conditionalFormatting sqref="H13:I14">
     <cfRule type="expression" dxfId="249" priority="115" stopIfTrue="1">
       <formula>ISTEXT(H13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I13">
+  <conditionalFormatting sqref="I7:I14">
     <cfRule type="expression" dxfId="248" priority="124">
       <formula>FIND("Réagir",J7)</formula>
     </cfRule>
@@ -26216,7 +26973,7 @@
       <formula>ISTEXT(I8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
+  <conditionalFormatting sqref="I14">
     <cfRule type="expression" dxfId="240" priority="118">
       <formula>FIND("Agir",J13)</formula>
     </cfRule>
@@ -26227,7 +26984,7 @@
       <formula>ISTEXT(I13)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:J13 V7:V13">
+  <conditionalFormatting sqref="I7:J14 V7:V13">
     <cfRule type="containsText" dxfId="237" priority="148" stopIfTrue="1" operator="containsText" text="Première">
       <formula>NOT(ISERROR(SEARCH("Première",I7)))</formula>
     </cfRule>
@@ -26238,7 +26995,7 @@
       <formula>NOT(ISERROR(SEARCH("Terme",I7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J13">
+  <conditionalFormatting sqref="J7:J14">
     <cfRule type="containsText" dxfId="234" priority="111" stopIfTrue="1" operator="containsText" text="long">
       <formula>NOT(ISERROR(SEARCH("long",J7)))</formula>
     </cfRule>
@@ -26340,7 +27097,7 @@
       <formula>NOT(ISERROR(SEARCH("Première",J4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V13">
+  <conditionalFormatting sqref="V7:V14">
     <cfRule type="expression" dxfId="204" priority="83">
       <formula>FIND("Agir",#REF!)</formula>
     </cfRule>
@@ -26353,7 +27110,7 @@
       <formula>ISTEXT(V10)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W7:W13">
+  <conditionalFormatting sqref="W7:W14">
     <cfRule type="containsText" dxfId="201" priority="444" stopIfTrue="1" operator="containsText" text="Terme">
       <formula>NOT(ISERROR(SEARCH("Terme",W7)))</formula>
     </cfRule>
@@ -26385,13 +27142,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a_0 - Non applicable_x000a_1 - Peu important_x000a_2 - Important_x000a_3 - Très important" sqref="E7:E13" xr:uid="{817E8CCD-C117-47B7-B926-598B6F8A3FD3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a_0 - Non applicable_x000a_1 - Peu important_x000a_2 - Important_x000a_3 - Très important" sqref="E7:E14" xr:uid="{817E8CCD-C117-47B7-B926-598B6F8A3FD3}">
       <formula1>$L$1:$O$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a_1 - Pas du tout atteinte_x000a_2 - En partie atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F7:F13" xr:uid="{B1DB31EF-56C4-4979-B74C-861A60E8CB99}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a_1 - Pas du tout atteinte_x000a_2 - En partie atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F7:F14" xr:uid="{B1DB31EF-56C4-4979-B74C-861A60E8CB99}">
       <formula1>$M$1:$P$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cible sont : _x000a_1 - Equipe NR / RSE_x000a_2 - NR + implication DSI_x000a_3 - NR + équipe hors DSI _x000a_3 - Intervention extérieure" sqref="H7:H13" xr:uid="{1ED8149F-2F3B-5A43-8EC8-9772583F443C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cible sont : _x000a_1 - Equipe NR / RSE_x000a_2 - NR + implication DSI_x000a_3 - NR + équipe hors DSI _x000a_3 - Intervention extérieure" sqref="H7:H14" xr:uid="{1ED8149F-2F3B-5A43-8EC8-9772583F443C}">
       <formula1>$M$1:$O$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -27119,7 +27876,7 @@
   <sheetPr codeName="Feuil8">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="1.5" style="51" customWidth="1"/>
@@ -27732,6 +28489,76 @@
       <c r="W12" s="252"/>
       <c r="X12" s="300"/>
     </row>
+    <row r="13" spans="1:24" s="138" customFormat="1" ht="43" thickBot="1">
+      <c r="A13" s="136"/>
+      <c r="B13" s="180" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="C13" s="318" t="inlineStr">
+        <is>
+          <t>En décidant des usages de l'IA avec les équipes, en les formant à ses limites, et en préservant le sens de leur travail</t>
+        </is>
+      </c>
+      <c r="D13" s="184"/>
+      <c r="E13" s="169"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="324"/>
+      <c r="H13" s="281"/>
+      <c r="I13" s="141"/>
+      <c r="J13" s="110" t="str">
+        <f>S13</f>
+        <v/>
+      </c>
+      <c r="K13" s="88">
+        <f>E13*10+F13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="88" t="b">
+        <f>OR(K13=31)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="88" t="b">
+        <f>OR(K13=21,K13=32)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="88" t="b">
+        <f>OR(K13=22,K13=33)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="88" t="b">
+        <f>OR(K13=11,K13=12)</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="88" t="b">
+        <f>OR(K13=23,K13=34)</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="88" t="b">
+        <f>OR(K13=13,K13=14,K13=24)</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="88" t="b">
+        <f>OR(K13=1,K13=2,K13=3,K13=4)</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="89" t="str">
+        <f>IF(COUNTA(E13:F13)&lt;2,"",(IF(L13=TRUE,$L$5,IF(M13=TRUE,$M$5,IF(N13=TRUE,$N$5,IF(O13=TRUE,$O$5,IF(P13=TRUE,$P$5,IF(Q13=TRUE,$Q$5,IF(R13=TRUE,$R$5,0)))))))))</f>
+        <v/>
+      </c>
+      <c r="T13" s="90" t="str">
+        <f>IF(COUNTA(E13:F13)&lt;2,"",(IF(L13=TRUE,6,IF(M13=TRUE,5,IF(N13=TRUE,4,IF(O13=TRUE,3,IF(P13=TRUE,2,IF(Q13=TRUE,1,IF(R13=TRUE,0,0)))))))))</f>
+        <v/>
+      </c>
+      <c r="U13" s="91" t="e">
+        <f>T13*10+H13</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V13" s="150"/>
+      <c r="W13" s="252"/>
+      <c r="X13" s="300"/>
+    </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="8">
@@ -27745,7 +28572,7 @@
     <mergeCell ref="B3:X3"/>
   </mergeCells>
   <phoneticPr fontId="42" type="noConversion"/>
-  <conditionalFormatting sqref="A4 I7:I12 D7:D12">
+  <conditionalFormatting sqref="A4 I7:I13 D7:D12">
     <cfRule type="expression" dxfId="137" priority="313">
       <formula>FIND("Réagir",B4)</formula>
     </cfRule>
@@ -27753,7 +28580,7 @@
       <formula>FIND("Agir",B4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4 I7:I12">
+  <conditionalFormatting sqref="A4 I7:I13">
     <cfRule type="expression" dxfId="135" priority="311" stopIfTrue="1">
       <formula>ISTEXT(A4)</formula>
     </cfRule>
@@ -27778,7 +28605,7 @@
       <formula>ISTEXT(A4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D12">
+  <conditionalFormatting sqref="D7:D13">
     <cfRule type="expression" dxfId="128" priority="247" stopIfTrue="1">
       <formula>ISTEXT(D7)</formula>
     </cfRule>
@@ -27786,17 +28613,17 @@
       <formula>FIND("Conforter",F7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:G12">
+  <conditionalFormatting sqref="D7:G13">
     <cfRule type="expression" dxfId="126" priority="300" stopIfTrue="1">
       <formula>ISTEXT(D7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:G12">
+  <conditionalFormatting sqref="F7:G13">
     <cfRule type="expression" dxfId="125" priority="301">
       <formula>FIND("Conforter",I7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G12">
+  <conditionalFormatting sqref="G7:G13">
     <cfRule type="expression" dxfId="124" priority="7" stopIfTrue="1">
       <formula>ISTEXT(G7)</formula>
     </cfRule>
@@ -27815,7 +28642,7 @@
       <formula>FIND("Agir",J7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I12">
+  <conditionalFormatting sqref="I7:I13">
     <cfRule type="expression" dxfId="119" priority="261" stopIfTrue="1">
       <formula>ISTEXT(I7)</formula>
     </cfRule>
@@ -27831,12 +28658,12 @@
       <formula>NOT(ISERROR(SEARCH("Seconde",I8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:J7 J8:J10 I11:J12 V7:W12">
+  <conditionalFormatting sqref="I7:J7 J8:J10 I11:J13 V7:W12">
     <cfRule type="containsText" dxfId="115" priority="302" stopIfTrue="1" operator="containsText" text="Première">
       <formula>NOT(ISERROR(SEARCH("Première",I7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:J7 V7:W12 J8:J10 I11:J12">
+  <conditionalFormatting sqref="I7:J7 V7:W13 J8:J10 I11:J12">
     <cfRule type="containsText" dxfId="114" priority="303" stopIfTrue="1" operator="containsText" text="Seconde">
       <formula>NOT(ISERROR(SEARCH("Seconde",I7)))</formula>
     </cfRule>
@@ -27844,7 +28671,7 @@
       <formula>NOT(ISERROR(SEARCH("Terme",I7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J12">
+  <conditionalFormatting sqref="J7:J13">
     <cfRule type="containsText" dxfId="112" priority="259" stopIfTrue="1" operator="containsText" text="moyen">
       <formula>NOT(ISERROR(SEARCH("moyen",J7)))</formula>
     </cfRule>
@@ -27881,7 +28708,7 @@
       <formula>NOT(ISERROR(SEARCH("Première",I4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:W12">
+  <conditionalFormatting sqref="V7:W13">
     <cfRule type="expression" dxfId="101" priority="187">
       <formula>FIND("Réagir",#REF!)</formula>
     </cfRule>
@@ -27904,13 +28731,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a_1 - Pas du tout atteinte_x000a_2 - En partie atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F7:F12" xr:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Performance actuelle" prompt="Valeur comprise entre 1 et 4_x000a_Cette cible est :_x000a_1 - Pas du tout atteinte_x000a_2 - En partie atteinte_x000a_3 - En voie d'être atteinte_x000a_4 - Atteinte" sqref="F7:F13" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>$M$1:$P$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a_0 - Non applicable_x000a_1 - Peu important_x000a_2 - Important_x000a_3 - Très important" sqref="E7:E12" xr:uid="{00000000-0002-0000-0700-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Les valeurs permises pour l'importance sont 0, 1, 2 ou 3" promptTitle="Importance de la cible" prompt="Valeur comprise entre 0 et 3_x000a_L'atteinte de cette cible est :_x000a_0 - Non applicable_x000a_1 - Peu important_x000a_2 - Important_x000a_3 - Très important" sqref="E7:E13" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>$L$1:$O$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences TNRC" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cible sont : _x000a_1 - Equipe NR / RSE_x000a_2 - NR + implication DSI_x000a_3 - NR + équipe hors DSI _x000a_3 - Intervention extérieure" sqref="H7:H12" xr:uid="{502B5581-3061-DF4F-8F38-86706775CF63}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur invalide" error="La valeur doit être contenue entre 1 et 4" promptTitle="Compétences TNRC" prompt="Valeur comprise entre 1 et 4_x000a_Les compétences pour cette cible sont : _x000a_1 - Equipe NR / RSE_x000a_2 - NR + implication DSI_x000a_3 - NR + équipe hors DSI _x000a_3 - Intervention extérieure" sqref="H7:H13" xr:uid="{502B5581-3061-DF4F-8F38-86706775CF63}">
       <formula1>$M$1:$O$1</formula1>
     </dataValidation>
   </dataValidations>

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -22795,231 +22795,391 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673E9F16-76F2-6B44-9F39-A42E5FF7BC5C}">
   <sheetPr codeName="Feuil12"/>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" t="s">
-        <v>132</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>En intégrant le cycle de vie complet des équipements et logiciels pour le mettre au service de la transition énergétique</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>En allongeant la durée d'usage des équipements, même au-delà de leur amortissement comptable</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>En éco-concevant les services numériques, et en choisissant des technologies qui contribuent aux Objectifs de développement durable (ODD)</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>En favorisant des usages et des pratiques limitant les consommations de matériels, de ressources, d’énergies et de consommables</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>44</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>En considérant nos déchets comme une ressource et leur traitement comme une source d’emplois participant au développement de l’économie circulaire.</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>En privilégiant et en favorisant l’utilisation de sources d’énergies renouvelables.</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>En favorisant l'utilisation d'IA lorsque nécessaire uniquement et en privilégiant des IA frugales</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>En mesurant ce que consomme l'IA, de son entraînement à son usage, et en le réduisant</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>En généralisant une démarche d’achats responsables avec l’adoption de clauses sociétales et environnementales.</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>En rendant nos services numériques accessibles à toutes et tous, et en mesurant leur conformité au RGAA</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>En déployant les applications autour des 3 U : Utiles, Utilisables, Utilisées pour en simplifier l’usage en intégrant l’accessibilité universelle pour réussir l’e-inclusion de tous</t>
+        </is>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>En concevant les services avec celles et ceux qui les utiliseront, pour livrer ce dont ils ont besoin et rien de plus</t>
+        </is>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>En vérifiant que l'IA ne discrimine personne et que ses services restent utilisables par tous</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>En développant des usages raisonnés des données et services dans une démarche éthique vis-à-vis des impacts sur l’environnement et les populations.</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>En luttant contre les pratiques trompeuses et présence de dark pattern dans les sites internet et en permettant de se conformer à la réglementation</t>
+        </is>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>En ne collectant que les données utiles et nécessaires au service des utilisateurs, afin de limiter les risques en matière de vie privée et impacts environnementaux en conformité avec le Règlement Général sur la Protection des Données (RGPD).</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>En favorisant la diversité des recrutements des métiers du numérique</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>En améliorant les conditions des travailleurs du numérique</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>En s’inscrivant résolument dans des dispositifs d’éthique algorithmique sur l’utilisation et la protection des données, notamment au regard de l’intelligence artificielle</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>En déployant et valorisant la démarche RSE</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>En disant quand c'est une IA qui répond, en expliquant comment elle décide, et en gardant un humain aux commandes sur les sujets sensibles</t>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>En respectant l'application des normes communes pour collecter, rassembler, analyser et partager les données sur les impacts des Technologies de l’Information et de la Communication (TIC).</t>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>En participant à une démarche collaborative de conception et d’évaluation des services numériques en adéquation avec les réels besoins.</t>
+        </is>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>En restant innovant dans l’utilisation de nouveaux outils numériques et assurer leur analyse d'impact avec transparence et visibilité pour les utilisateurs</t>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>En permettant et en garantissant plus de souveraineté numérique</t>
+        </is>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>En incluant l’innovation sociale dans la définition de nouveaux systèmes et services numériques.</t>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>En valorisant les initiatives internes qui mobilisent l’organisation, favorisent les collaborations transversales et le bien-être au travail.</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>En sollicitant l’engagement et l’expertise des parties prenantes (sur les sujets environnementaux, sociaux et sociétaux)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>En permettant aux générations futures d’innover pour construire un monde ouvert à l’autre soucieux de l’équilibre des écosystèmes et du bien-vivre ensemble.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>En suivant les indicateurs de performances et de conformité</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>En proposant des axes d’amélioration et d'innovation autour du NR ( y compris s'ils ne sont pas numériques )</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>En décidant des usages de l'IA avec les équipes, en les formant à ses limites, et en préservant le sens de leur travail</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -3762,7 +3762,7 @@
     <t>4.2</t>
   </si>
   <si>
-    <t>En participant à une démarche collaborative de conception et d’évaluation des services numériques en adéquation avec les réels besoins.</t>
+    <t>En évaluant nos services numériques dans la durée, et en partageant les résultats de ces évaluations</t>
   </si>
   <si>
     <t>4.3</t>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="C30" s="219" t="str">
         <f>'ONR 4'!C8</f>
-        <v>En participant à une démarche collaborative de conception et d’évaluation des services numériques en adéquation avec les réels besoins.</v>
+        <v>En évaluant nos services numériques dans la durée, et en partageant les résultats de ces évaluations</v>
       </c>
       <c r="D30" s="231">
         <f>'ONR 4'!D8</f>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>En participant à une démarche collaborative de conception et d’évaluation des services numériques en adéquation avec les réels besoins.</t>
+          <t>En évaluant nos services numériques dans la durée, et en partageant les résultats de ces évaluations</t>
         </is>
       </c>
     </row>

--- a/INR_GPC_ONR Template.xlsx
+++ b/INR_GPC_ONR Template.xlsx
@@ -3561,7 +3561,7 @@
     <t>Date de l'analyse</t>
   </si>
   <si>
-    <t xml:space="preserve">ONR 1  -   SOBRIÉTÉ : S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation					</t>
+    <t xml:space="preserve">ONR 1 : Sobriété · S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation</t>
   </si>
   <si>
     <t>Importance de la cible</t>
@@ -3678,7 +3678,7 @@
     <t>En favorisant l'utilisation d'IA lorsque nécessaire uniquement et en privilégiant des IA frugales</t>
   </si>
   <si>
-    <t>ONR 2  -   INCLUSION : S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</t>
+    <t xml:space="preserve">ONR 2 : Inclusion · S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</t>
   </si>
   <si>
     <t>2.1</t>
@@ -3705,7 +3705,7 @@
     <t>En concevant les services avec celles et ceux qui les utiliseront, pour livrer ce dont ils ont besoin et rien de plus</t>
   </si>
   <si>
-    <t xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </t>
+    <t xml:space="preserve">ONR 3 : RSE · S'engager pour des pratiques numériques éthiques et responsables</t>
   </si>
   <si>
     <t>3.1</t>
@@ -3750,7 +3750,7 @@
     <t>En déployant et valorisant la démarche RSE</t>
   </si>
   <si>
-    <t>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</t>
+    <t xml:space="preserve">ONR 4 : Résilience et stratégie · S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</t>
   </si>
   <si>
     <t>4.1</t>
@@ -3777,7 +3777,7 @@
     <t>En permettant et en garantissant plus de souveraineté numérique</t>
   </si>
   <si>
-    <t>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</t>
+    <t xml:space="preserve">ONR 5 : Management · S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</t>
   </si>
   <si>
     <t>5.1</t>
@@ -15829,7 +15829,7 @@
       <c r="A4" s="115"/>
       <c r="B4" s="382" t="str">
         <f>'ONR 1'!B2</f>
-        <v xml:space="preserve">ONR 1  -   SOBRIÉTÉ : S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation					</v>
+        <v xml:space="preserve">ONR 1 : Sobriété · S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation</v>
       </c>
       <c r="C4" s="383"/>
       <c r="D4" s="383"/>
@@ -15857,7 +15857,7 @@
       <c r="Z4" s="384"/>
       <c r="AB4" s="116" t="str">
         <f>B4</f>
-        <v xml:space="preserve">ONR 1  -   SOBRIÉTÉ : S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation					</v>
+        <v xml:space="preserve">ONR 1 : Sobriété · S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation</v>
       </c>
       <c r="AC4" s="116">
         <f>SUMPRODUCT(--(B5:B12&lt;&gt;""))</f>
@@ -16984,7 +16984,7 @@
       <c r="A13" s="115"/>
       <c r="B13" s="362" t="str">
         <f>'ONR 2'!B2</f>
-        <v>ONR 2  -   INCLUSION : S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
+        <v xml:space="preserve">ONR 2 : Inclusion · S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
       </c>
       <c r="C13" s="363"/>
       <c r="D13" s="363"/>
@@ -17012,7 +17012,7 @@
       <c r="Z13" s="380"/>
       <c r="AB13" s="116" t="str">
         <f>B13</f>
-        <v>ONR 2  -   INCLUSION : S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
+        <v xml:space="preserve">ONR 2 : Inclusion · S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
       </c>
       <c r="AC13" s="116">
         <f>SUMPRODUCT(--(B14:B18&lt;&gt;""))</f>
@@ -17734,7 +17734,7 @@
       <c r="A19" s="115"/>
       <c r="B19" s="381" t="str">
         <f>'ONR 3'!B2:C2</f>
-        <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
+        <v xml:space="preserve">ONR 3 : RSE · S'engager pour des pratiques numériques éthiques et responsables</v>
       </c>
       <c r="C19" s="381"/>
       <c r="D19" s="381"/>
@@ -17762,7 +17762,7 @@
       <c r="Z19" s="381"/>
       <c r="AB19" s="116" t="str">
         <f>B19</f>
-        <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
+        <v xml:space="preserve">ONR 3 : RSE · S'engager pour des pratiques numériques éthiques et responsables</v>
       </c>
       <c r="AC19" s="116">
         <f>SUMPRODUCT(--(B20:B27&lt;&gt;""))</f>
@@ -18889,7 +18889,7 @@
       <c r="A28" s="115"/>
       <c r="B28" s="362" t="str">
         <f>'ONR 4'!B2:C2</f>
-        <v>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
+        <v xml:space="preserve">ONR 4 : Résilience et stratégie · S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
       </c>
       <c r="C28" s="363"/>
       <c r="D28" s="363"/>
@@ -18917,7 +18917,7 @@
       <c r="Z28" s="380"/>
       <c r="AB28" s="116" t="str">
         <f>B28</f>
-        <v>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
+        <v xml:space="preserve">ONR 4 : Résilience et stratégie · S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
       </c>
       <c r="AC28" s="116">
         <f>SUMPRODUCT(--(B29:B32&lt;&gt;""))</f>
@@ -19504,7 +19504,7 @@
       <c r="A33" s="115"/>
       <c r="B33" s="362" t="str">
         <f>'ONR 5'!B2:C2</f>
-        <v>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
+        <v xml:space="preserve">ONR 5 : Management · S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
       </c>
       <c r="C33" s="363"/>
       <c r="D33" s="363"/>
@@ -19532,7 +19532,7 @@
       <c r="Z33" s="364"/>
       <c r="AB33" s="116" t="str">
         <f>B33</f>
-        <v>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
+        <v xml:space="preserve">ONR 5 : Management · S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
       </c>
       <c r="AC33" s="116">
         <f>SUMPRODUCT(--(B34:B40&lt;&gt;""))</f>
@@ -21090,7 +21090,7 @@
       <c r="B4" s="73"/>
       <c r="C4" s="72" t="str">
         <f>'Résultats détaillés'!AB4</f>
-        <v xml:space="preserve">ONR 1  -   SOBRIÉTÉ : S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation					</v>
+        <v xml:space="preserve">ONR 1 : Sobriété · S'engager à optimiser les outils numériques pour limiter leurs impacts et consommation</v>
       </c>
       <c r="D4" s="44">
         <f>IF('Résultats détaillés'!AC4=0,"",'Résultats détaillés'!AC4)</f>
@@ -21137,7 +21137,7 @@
       <c r="B5" s="74"/>
       <c r="C5" s="70" t="str">
         <f>'Résultats détaillés'!AB13</f>
-        <v>ONR 2  -   INCLUSION : S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
+        <v xml:space="preserve">ONR 2 : Inclusion · S'engager à développer des services numériques accessibles à toutes et tous, inclusifs et durables</v>
       </c>
       <c r="D5" s="44">
         <f>IF('Résultats détaillés'!AC13=0,"",'Résultats détaillés'!AC13)</f>
@@ -21184,7 +21184,7 @@
       <c r="B6" s="75"/>
       <c r="C6" s="70" t="str">
         <f>'Résultats détaillés'!AB19</f>
-        <v xml:space="preserve">ONR 3  -  RSE : S'engager pour des pratiques numériques éthiques et responsables </v>
+        <v xml:space="preserve">ONR 3 : RSE · S'engager pour des pratiques numériques éthiques et responsables</v>
       </c>
       <c r="D6" s="44">
         <f>IF('Résultats détaillés'!AC19=0,"",'Résultats détaillés'!AC19)</f>
@@ -21231,7 +21231,7 @@
       <c r="B7" s="76"/>
       <c r="C7" s="70" t="str">
         <f>'Résultats détaillés'!AB28</f>
-        <v>ONR 4  -  RESILIENCE ET STRATEGIE :  S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
+        <v xml:space="preserve">ONR 4 : Résilience et stratégie · S'engager vers un numérique responsable, indispensable pour assurer la résilience des organisations</v>
       </c>
       <c r="D7" s="44">
         <f>IF('Résultats détaillés'!AC28=0,"",'Résultats détaillés'!AC28)</f>
@@ -21278,7 +21278,7 @@
       <c r="B8" s="77"/>
       <c r="C8" s="70" t="str">
         <f>'Résultats détaillés'!B33</f>
-        <v>ONR 5  -  MANAGEMENT :  S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
+        <v xml:space="preserve">ONR 5 : Management · S'engager à faire les choses avec sens en respectant et en préservant les ressources qui produisent</v>
       </c>
       <c r="D8" s="44">
         <f>IF('Résultats détaillés'!AC33=0,"",'Résultats détaillés'!AC33)</f>
